--- a/Property_Rent_Data_Model.xlsx
+++ b/Property_Rent_Data_Model.xlsx
@@ -837,7 +837,7 @@
         <v>PaymentReceipts</v>
       </c>
       <c r="B39">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="40">
@@ -845,7 +845,7 @@
         <v>PaymentAllocations</v>
       </c>
       <c r="B40">
-        <v>694</v>
+        <v>705</v>
       </c>
     </row>
     <row r="41">
@@ -853,7 +853,7 @@
         <v>Expenses</v>
       </c>
       <c r="B41">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>TOTAL</v>
       </c>
       <c r="B46">
-        <v>2012</v>
+        <v>2032</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +989,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 290 total records]</v>
+        <v>[Showing 100 of 292 total records]</v>
       </c>
     </row>
     <row r="3">
@@ -1023,13 +1023,7 @@
       <c r="J3">
         <v>11700</v>
       </c>
-      <c r="K3" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v/>
       </c>
       <c r="N3" t="str">
@@ -1082,13 +1076,7 @@
       <c r="J4">
         <v>27000</v>
       </c>
-      <c r="K4" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
@@ -1141,13 +1129,7 @@
       <c r="J5">
         <v>122000</v>
       </c>
-      <c r="K5" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
@@ -1200,13 +1182,7 @@
       <c r="J6">
         <v>3650</v>
       </c>
-      <c r="K6" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
@@ -1259,13 +1235,7 @@
       <c r="J7">
         <v>810000</v>
       </c>
-      <c r="K7" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
@@ -1318,14 +1288,8 @@
       <c r="J8">
         <v>1900000</v>
       </c>
-      <c r="K8" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L8" t="str">
         <v>EXP-REF-777</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Vendor</v>
       </c>
       <c r="N8" t="str">
         <v>Company payment (Note: Marked as zakat in source file)</v>
@@ -1377,14 +1341,8 @@
       <c r="J9">
         <v>273535</v>
       </c>
-      <c r="K9" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L9" t="str">
         <v/>
-      </c>
-      <c r="M9" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N9" t="str">
         <v>Kotak Godaown: Maintainance</v>
@@ -1433,14 +1391,8 @@
       <c r="J10">
         <v>174512</v>
       </c>
-      <c r="K10" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L10" t="str">
         <v/>
-      </c>
-      <c r="M10" t="str">
-        <v>Rent</v>
       </c>
       <c r="N10" t="str">
         <v>Kotak Godaown: Rent</v>
@@ -1489,14 +1441,8 @@
       <c r="J11">
         <v>2800</v>
       </c>
-      <c r="K11" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L11" t="str">
         <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N11" t="str">
         <v>65 Godown, Barankar,dinesh: Maintainance</v>
@@ -1545,14 +1491,8 @@
       <c r="J12">
         <v>3000</v>
       </c>
-      <c r="K12" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L12" t="str">
         <v/>
-      </c>
-      <c r="M12" t="str">
-        <v>Other expenses</v>
       </c>
       <c r="N12" t="str">
         <v>65 Godown, Barankar,dinesh: Other expenses</v>
@@ -1601,14 +1541,8 @@
       <c r="J13">
         <v>14772</v>
       </c>
-      <c r="K13" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L13" t="str">
         <v/>
-      </c>
-      <c r="M13" t="str">
-        <v>Other expenses</v>
       </c>
       <c r="N13" t="str">
         <v>65 Godown, Barankar,dinesh: Other expenses</v>
@@ -1657,14 +1591,8 @@
       <c r="J14">
         <v>15000</v>
       </c>
-      <c r="K14" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L14" t="str">
         <v/>
-      </c>
-      <c r="M14" t="str">
-        <v>Electricity</v>
       </c>
       <c r="N14" t="str">
         <v>Garage snip: Electricity</v>
@@ -1713,14 +1641,8 @@
       <c r="J15">
         <v>3000</v>
       </c>
-      <c r="K15" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L15" t="str">
         <v/>
-      </c>
-      <c r="M15" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N15" t="str">
         <v>Goa Flat: Maintainance</v>
@@ -1769,14 +1691,8 @@
       <c r="J16">
         <v>550000</v>
       </c>
-      <c r="K16" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L16" t="str">
         <v/>
-      </c>
-      <c r="M16" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N16" t="str">
         <v>Goa Flat: Maintainance</v>
@@ -1825,14 +1741,8 @@
       <c r="J17">
         <v>10000</v>
       </c>
-      <c r="K17" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L17" t="str">
         <v/>
-      </c>
-      <c r="M17" t="str">
-        <v>maintainance</v>
       </c>
       <c r="N17" t="str">
         <v>Tonys room: maintainance</v>
@@ -1881,14 +1791,8 @@
       <c r="J18">
         <v>10000</v>
       </c>
-      <c r="K18" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L18" t="str">
         <v/>
-      </c>
-      <c r="M18" t="str">
-        <v>maintainance</v>
       </c>
       <c r="N18" t="str">
         <v>Tonys room: maintainance</v>
@@ -1937,14 +1841,8 @@
       <c r="J19">
         <v>20000</v>
       </c>
-      <c r="K19" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L19" t="str">
         <v/>
-      </c>
-      <c r="M19" t="str">
-        <v>maintainance</v>
       </c>
       <c r="N19" t="str">
         <v>Tonys room: maintainance</v>
@@ -1993,14 +1891,8 @@
       <c r="J20">
         <v>5000</v>
       </c>
-      <c r="K20" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L20" t="str">
         <v/>
-      </c>
-      <c r="M20" t="str">
-        <v>Other expenses</v>
       </c>
       <c r="N20" t="str">
         <v>Tonys room: Other expenses</v>
@@ -2049,14 +1941,8 @@
       <c r="J21">
         <v>96000</v>
       </c>
-      <c r="K21" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L21" t="str">
         <v/>
-      </c>
-      <c r="M21" t="str">
-        <v>Rent</v>
       </c>
       <c r="N21" t="str">
         <v>Buyculla club: Rent</v>
@@ -2105,14 +1991,8 @@
       <c r="J22">
         <v>5500</v>
       </c>
-      <c r="K22" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L22" t="str">
         <v/>
-      </c>
-      <c r="M22" t="str">
-        <v>Maitainance</v>
       </c>
       <c r="N22" t="str">
         <v>Buyculla club: Maitainance</v>
@@ -2161,14 +2041,8 @@
       <c r="J23">
         <v>21500</v>
       </c>
-      <c r="K23" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L23" t="str">
         <v/>
-      </c>
-      <c r="M23" t="str">
-        <v>Maitainance</v>
       </c>
       <c r="N23" t="str">
         <v>Buyculla club: Maitainance</v>
@@ -2217,14 +2091,8 @@
       <c r="J24">
         <v>5000</v>
       </c>
-      <c r="K24" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L24" t="str">
         <v/>
-      </c>
-      <c r="M24" t="str">
-        <v>Maitainance</v>
       </c>
       <c r="N24" t="str">
         <v>Buyculla club: Maitainance</v>
@@ -2273,14 +2141,8 @@
       <c r="J25">
         <v>19000</v>
       </c>
-      <c r="K25" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L25" t="str">
         <v/>
-      </c>
-      <c r="M25" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N25" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -2329,14 +2191,8 @@
       <c r="J26">
         <v>5000</v>
       </c>
-      <c r="K26" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L26" t="str">
         <v/>
-      </c>
-      <c r="M26" t="str">
-        <v>Donations</v>
       </c>
       <c r="N26" t="str">
         <v>Other Expenses: Donations</v>
@@ -2385,14 +2241,8 @@
       <c r="J27">
         <v>8000</v>
       </c>
-      <c r="K27" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L27" t="str">
         <v/>
-      </c>
-      <c r="M27" t="str">
-        <v>Donations</v>
       </c>
       <c r="N27" t="str">
         <v>Other Expenses: Donations</v>
@@ -2441,14 +2291,8 @@
       <c r="J28">
         <v>2000</v>
       </c>
-      <c r="K28" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L28" t="str">
         <v/>
-      </c>
-      <c r="M28" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N28" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -2497,14 +2341,8 @@
       <c r="J29">
         <v>1600</v>
       </c>
-      <c r="K29" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L29" t="str">
         <v/>
-      </c>
-      <c r="M29" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N29" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -2553,14 +2391,8 @@
       <c r="J30">
         <v>6900</v>
       </c>
-      <c r="K30" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L30" t="str">
         <v/>
-      </c>
-      <c r="M30" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N30" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -2609,14 +2441,8 @@
       <c r="J31">
         <v>17000</v>
       </c>
-      <c r="K31" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L31" t="str">
         <v/>
-      </c>
-      <c r="M31" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N31" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -2665,14 +2491,8 @@
       <c r="J32">
         <v>16500</v>
       </c>
-      <c r="K32" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L32" t="str">
         <v/>
-      </c>
-      <c r="M32" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N32" t="str">
         <v>Other Expenses: Margaret</v>
@@ -2721,14 +2541,8 @@
       <c r="J33">
         <v>16500</v>
       </c>
-      <c r="K33" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L33" t="str">
         <v/>
-      </c>
-      <c r="M33" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N33" t="str">
         <v>Other Expenses: Margaret</v>
@@ -2777,14 +2591,8 @@
       <c r="J34">
         <v>16500</v>
       </c>
-      <c r="K34" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L34" t="str">
         <v/>
-      </c>
-      <c r="M34" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N34" t="str">
         <v>Other Expenses: Margaret</v>
@@ -2833,14 +2641,8 @@
       <c r="J35">
         <v>16500</v>
       </c>
-      <c r="K35" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L35" t="str">
         <v/>
-      </c>
-      <c r="M35" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N35" t="str">
         <v>Other Expenses: Margaret</v>
@@ -2889,14 +2691,8 @@
       <c r="J36">
         <v>150000</v>
       </c>
-      <c r="K36" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L36" t="str">
         <v/>
-      </c>
-      <c r="M36" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N36" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -2945,14 +2741,8 @@
       <c r="J37">
         <v>8840</v>
       </c>
-      <c r="K37" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L37" t="str">
         <v/>
-      </c>
-      <c r="M37" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N37" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -3001,14 +2791,8 @@
       <c r="J38">
         <v>18500</v>
       </c>
-      <c r="K38" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L38" t="str">
         <v/>
-      </c>
-      <c r="M38" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N38" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -3057,14 +2841,8 @@
       <c r="J39">
         <v>10000</v>
       </c>
-      <c r="K39" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L39" t="str">
         <v/>
-      </c>
-      <c r="M39" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N39" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -3113,14 +2891,8 @@
       <c r="J40">
         <v>30000</v>
       </c>
-      <c r="K40" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L40" t="str">
         <v/>
-      </c>
-      <c r="M40" t="str">
-        <v>Micellaneous Expenses</v>
       </c>
       <c r="N40" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
@@ -3169,14 +2941,8 @@
       <c r="J41">
         <v>46338</v>
       </c>
-      <c r="K41" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L41" t="str">
         <v/>
-      </c>
-      <c r="M41" t="str">
-        <v>Mom</v>
       </c>
       <c r="N41" t="str">
         <v>Other Expenses: Mom</v>
@@ -3225,14 +2991,8 @@
       <c r="J42">
         <v>700000</v>
       </c>
-      <c r="K42" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L42" t="str">
         <v/>
-      </c>
-      <c r="M42" t="str">
-        <v>Mom</v>
       </c>
       <c r="N42" t="str">
         <v>Other Expenses: Mom</v>
@@ -3281,14 +3041,8 @@
       <c r="J43">
         <v>13001</v>
       </c>
-      <c r="K43" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L43" t="str">
         <v/>
-      </c>
-      <c r="M43" t="str">
-        <v>Mom</v>
       </c>
       <c r="N43" t="str">
         <v>Other Expenses: Mom</v>
@@ -3337,14 +3091,8 @@
       <c r="J44">
         <v>12190</v>
       </c>
-      <c r="K44" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L44" t="str">
         <v/>
-      </c>
-      <c r="M44" t="str">
-        <v>Mom</v>
       </c>
       <c r="N44" t="str">
         <v>Other Expenses: Mom</v>
@@ -3393,14 +3141,8 @@
       <c r="J45">
         <v>7292</v>
       </c>
-      <c r="K45" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L45" t="str">
         <v/>
-      </c>
-      <c r="M45" t="str">
-        <v>Mom</v>
       </c>
       <c r="N45" t="str">
         <v>Other Expenses: Mom</v>
@@ -3449,14 +3191,8 @@
       <c r="J46">
         <v>38163</v>
       </c>
-      <c r="K46" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L46" t="str">
         <v/>
-      </c>
-      <c r="M46" t="str">
-        <v>Mom</v>
       </c>
       <c r="N46" t="str">
         <v>Other Expenses: Mom</v>
@@ -3505,14 +3241,8 @@
       <c r="J47">
         <v>8620</v>
       </c>
-      <c r="K47" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L47" t="str">
         <v/>
-      </c>
-      <c r="M47" t="str">
-        <v>Mom</v>
       </c>
       <c r="N47" t="str">
         <v>Other Expenses: Mom</v>
@@ -3561,14 +3291,8 @@
       <c r="J48">
         <v>8576</v>
       </c>
-      <c r="K48" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L48" t="str">
         <v/>
-      </c>
-      <c r="M48" t="str">
-        <v>Mom</v>
       </c>
       <c r="N48" t="str">
         <v>Other Expenses: Mom</v>
@@ -3617,14 +3341,8 @@
       <c r="J49">
         <v>9720</v>
       </c>
-      <c r="K49" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L49" t="str">
         <v/>
-      </c>
-      <c r="M49" t="str">
-        <v>Mom</v>
       </c>
       <c r="N49" t="str">
         <v>Other Expenses: Mom</v>
@@ -3673,14 +3391,8 @@
       <c r="J50">
         <v>10500</v>
       </c>
-      <c r="K50" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L50" t="str">
         <v/>
-      </c>
-      <c r="M50" t="str">
-        <v>Mom</v>
       </c>
       <c r="N50" t="str">
         <v>Other Expenses: Mom</v>
@@ -3729,14 +3441,8 @@
       <c r="J51">
         <v>5330</v>
       </c>
-      <c r="K51" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L51" t="str">
         <v/>
-      </c>
-      <c r="M51" t="str">
-        <v>Mom</v>
       </c>
       <c r="N51" t="str">
         <v>Other Expenses: Mom</v>
@@ -3785,14 +3491,8 @@
       <c r="J52">
         <v>4940</v>
       </c>
-      <c r="K52" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L52" t="str">
         <v/>
-      </c>
-      <c r="M52" t="str">
-        <v>Mom</v>
       </c>
       <c r="N52" t="str">
         <v>Other Expenses: Mom</v>
@@ -3841,14 +3541,8 @@
       <c r="J53">
         <v>1000000</v>
       </c>
-      <c r="K53" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L53" t="str">
         <v/>
-      </c>
-      <c r="M53" t="str">
-        <v>Islamic &amp; Zakat</v>
       </c>
       <c r="N53" t="str">
         <v>Other Expenses: Islamic &amp; Zakat</v>
@@ -3897,14 +3591,8 @@
       <c r="J54">
         <v>823000</v>
       </c>
-      <c r="K54" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L54" t="str">
         <v/>
-      </c>
-      <c r="M54" t="str">
-        <v>Akbar</v>
       </c>
       <c r="N54" t="str">
         <v>Other Expenses: Akbar</v>
@@ -3953,14 +3641,8 @@
       <c r="J55">
         <v>2000000</v>
       </c>
-      <c r="K55" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L55" t="str">
         <v/>
-      </c>
-      <c r="M55" t="str">
-        <v>Akbar</v>
       </c>
       <c r="N55" t="str">
         <v>Other Expenses: Akbar</v>
@@ -4009,14 +3691,8 @@
       <c r="J56">
         <v>350000</v>
       </c>
-      <c r="K56" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L56" t="str">
         <v/>
-      </c>
-      <c r="M56" t="str">
-        <v>Akbar</v>
       </c>
       <c r="N56" t="str">
         <v>Other Expenses: Akbar</v>
@@ -4065,14 +3741,8 @@
       <c r="J57">
         <v>1500000</v>
       </c>
-      <c r="K57" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L57" t="str">
         <v/>
-      </c>
-      <c r="M57" t="str">
-        <v>Loan</v>
       </c>
       <c r="N57" t="str">
         <v>Other Expenses: Loan</v>
@@ -4121,14 +3791,8 @@
       <c r="J58">
         <v>1400000</v>
       </c>
-      <c r="K58" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L58" t="str">
         <v/>
-      </c>
-      <c r="M58" t="str">
-        <v>Loan</v>
       </c>
       <c r="N58" t="str">
         <v>Other Expenses: Loan</v>
@@ -4177,14 +3841,8 @@
       <c r="J59">
         <v>20000</v>
       </c>
-      <c r="K59" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L59" t="str">
         <v/>
-      </c>
-      <c r="M59" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N59" t="str">
         <v>65 no godown: Maintainance</v>
@@ -4233,14 +3891,8 @@
       <c r="J60">
         <v>9100</v>
       </c>
-      <c r="K60" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L60" t="str">
         <v/>
-      </c>
-      <c r="M60" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N60" t="str">
         <v>65 no godown: Maintainance</v>
@@ -4289,14 +3941,8 @@
       <c r="J61">
         <v>75000</v>
       </c>
-      <c r="K61" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L61" t="str">
         <v/>
-      </c>
-      <c r="M61" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N61" t="str">
         <v>65 no godown: Maintainance</v>
@@ -4345,14 +3991,8 @@
       <c r="J62">
         <v>46248</v>
       </c>
-      <c r="K62" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L62" t="str">
         <v/>
-      </c>
-      <c r="M62" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N62" t="str">
         <v>65 no godown: Maintainance</v>
@@ -4401,14 +4041,8 @@
       <c r="J63">
         <v>10000</v>
       </c>
-      <c r="K63" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L63" t="str">
         <v/>
-      </c>
-      <c r="M63" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N63" t="str">
         <v>65 no godown: Maintainance</v>
@@ -4457,14 +4091,8 @@
       <c r="J64">
         <v>14561</v>
       </c>
-      <c r="K64" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L64" t="str">
         <v/>
-      </c>
-      <c r="M64" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N64" t="str">
         <v>65 no godown: Maintainance</v>
@@ -4513,14 +4141,8 @@
       <c r="J65">
         <v>41433</v>
       </c>
-      <c r="K65" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L65" t="str">
         <v/>
-      </c>
-      <c r="M65" t="str">
-        <v>Rent</v>
       </c>
       <c r="N65" t="str">
         <v>65 no godown: Rent</v>
@@ -4569,14 +4191,8 @@
       <c r="J66">
         <v>20000</v>
       </c>
-      <c r="K66" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L66" t="str">
         <v/>
-      </c>
-      <c r="M66" t="str">
-        <v>Rent</v>
       </c>
       <c r="N66" t="str">
         <v>65 no godown: Rent</v>
@@ -4625,14 +4241,8 @@
       <c r="J67">
         <v>20000</v>
       </c>
-      <c r="K67" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L67" t="str">
         <v/>
-      </c>
-      <c r="M67" t="str">
-        <v>Other expenses</v>
       </c>
       <c r="N67" t="str">
         <v>65 no godown: Other expenses</v>
@@ -4681,14 +4291,8 @@
       <c r="J68">
         <v>177044</v>
       </c>
-      <c r="K68" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L68" t="str">
         <v/>
-      </c>
-      <c r="M68" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N68" t="str">
         <v>Garage: Maintainance</v>
@@ -4737,14 +4341,8 @@
       <c r="J69">
         <v>20900</v>
       </c>
-      <c r="K69" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L69" t="str">
         <v/>
-      </c>
-      <c r="M69" t="str">
-        <v>Maintainance</v>
       </c>
       <c r="N69" t="str">
         <v>Mani Mansion: Maintainance</v>
@@ -4793,14 +4391,8 @@
       <c r="J70">
         <v>3698</v>
       </c>
-      <c r="K70" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L70" t="str">
         <v/>
-      </c>
-      <c r="M70" t="str">
-        <v>Rent</v>
       </c>
       <c r="N70" t="str">
         <v>Goa Flat: Rent</v>
@@ -4849,14 +4441,8 @@
       <c r="J71">
         <v>3000</v>
       </c>
-      <c r="K71" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L71" t="str">
         <v/>
-      </c>
-      <c r="M71" t="str">
-        <v>Rent</v>
       </c>
       <c r="N71" t="str">
         <v>Byculla Club: Rent</v>
@@ -4905,14 +4491,8 @@
       <c r="J72">
         <v>9000</v>
       </c>
-      <c r="K72" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L72" t="str">
         <v/>
-      </c>
-      <c r="M72" t="str">
-        <v>Maitainance</v>
       </c>
       <c r="N72" t="str">
         <v>Byculla Club: Maitainance</v>
@@ -4961,14 +4541,8 @@
       <c r="J73">
         <v>6300</v>
       </c>
-      <c r="K73" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L73" t="str">
         <v/>
-      </c>
-      <c r="M73" t="str">
-        <v>Micellaneous</v>
       </c>
       <c r="N73" t="str">
         <v>Micellaneous</v>
@@ -5017,14 +4591,8 @@
       <c r="J74">
         <v>3000</v>
       </c>
-      <c r="K74" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L74" t="str">
         <v/>
-      </c>
-      <c r="M74" t="str">
-        <v>Micellaneous</v>
       </c>
       <c r="N74" t="str">
         <v>Micellaneous</v>
@@ -5073,14 +4641,8 @@
       <c r="J75">
         <v>16500</v>
       </c>
-      <c r="K75" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L75" t="str">
         <v/>
-      </c>
-      <c r="M75" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N75" t="str">
         <v>Margaret</v>
@@ -5129,14 +4691,8 @@
       <c r="J76">
         <v>16500</v>
       </c>
-      <c r="K76" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L76" t="str">
         <v/>
-      </c>
-      <c r="M76" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N76" t="str">
         <v>Margaret</v>
@@ -5185,14 +4741,8 @@
       <c r="J77">
         <v>16500</v>
       </c>
-      <c r="K77" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L77" t="str">
         <v/>
-      </c>
-      <c r="M77" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N77" t="str">
         <v>Margaret</v>
@@ -5241,14 +4791,8 @@
       <c r="J78">
         <v>600</v>
       </c>
-      <c r="K78" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L78" t="str">
         <v/>
-      </c>
-      <c r="M78" t="str">
-        <v>Margaret</v>
       </c>
       <c r="N78" t="str">
         <v>Margaret</v>
@@ -5297,14 +4841,8 @@
       <c r="J79">
         <v>22940</v>
       </c>
-      <c r="K79" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L79" t="str">
         <v/>
-      </c>
-      <c r="M79" t="str">
-        <v>Micellaneous</v>
       </c>
       <c r="N79" t="str">
         <v>Micellaneous</v>
@@ -5353,14 +4891,8 @@
       <c r="J80">
         <v>25300</v>
       </c>
-      <c r="K80" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L80" t="str">
         <v/>
-      </c>
-      <c r="M80" t="str">
-        <v>Micellaneous</v>
       </c>
       <c r="N80" t="str">
         <v>Micellaneous</v>
@@ -5409,14 +4941,8 @@
       <c r="J81">
         <v>30240</v>
       </c>
-      <c r="K81" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L81" t="str">
         <v/>
-      </c>
-      <c r="M81" t="str">
-        <v>Micellaneous</v>
       </c>
       <c r="N81" t="str">
         <v>Micellaneous</v>
@@ -5465,14 +4991,8 @@
       <c r="J82">
         <v>4800</v>
       </c>
-      <c r="K82" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L82" t="str">
         <v/>
-      </c>
-      <c r="M82" t="str">
-        <v>Micellaneous</v>
       </c>
       <c r="N82" t="str">
         <v>Micellaneous</v>
@@ -5521,14 +5041,8 @@
       <c r="J83">
         <v>179283.26</v>
       </c>
-      <c r="K83" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L83" t="str">
         <v/>
-      </c>
-      <c r="M83" t="str">
-        <v>Mom</v>
       </c>
       <c r="N83" t="str">
         <v>Mom</v>
@@ -5577,14 +5091,8 @@
       <c r="J84">
         <v>20000</v>
       </c>
-      <c r="K84" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L84" t="str">
         <v/>
-      </c>
-      <c r="M84" t="str">
-        <v>Mom</v>
       </c>
       <c r="N84" t="str">
         <v>Mom</v>
@@ -5633,14 +5141,8 @@
       <c r="J85">
         <v>400</v>
       </c>
-      <c r="K85" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L85" t="str">
         <v/>
-      </c>
-      <c r="M85" t="str">
-        <v>Mom</v>
       </c>
       <c r="N85" t="str">
         <v>Mom</v>
@@ -5689,14 +5191,8 @@
       <c r="J86">
         <v>4770</v>
       </c>
-      <c r="K86" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L86" t="str">
         <v/>
-      </c>
-      <c r="M86" t="str">
-        <v>Mom</v>
       </c>
       <c r="N86" t="str">
         <v>Mom</v>
@@ -5745,14 +5241,8 @@
       <c r="J87">
         <v>2030000</v>
       </c>
-      <c r="K87" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L87" t="str">
         <v/>
-      </c>
-      <c r="M87" t="str">
-        <v>Islamic &amp; Zakat</v>
       </c>
       <c r="N87" t="str">
         <v>Islamic &amp; Zakat</v>
@@ -5801,14 +5291,8 @@
       <c r="J88">
         <v>2600000</v>
       </c>
-      <c r="K88" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L88" t="str">
         <v/>
-      </c>
-      <c r="M88" t="str">
-        <v>Send to dubai</v>
       </c>
       <c r="N88" t="str">
         <v>Send to dubai</v>
@@ -5857,14 +5341,8 @@
       <c r="J89">
         <v>4800</v>
       </c>
-      <c r="K89" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L89" t="str">
         <v/>
-      </c>
-      <c r="M89" t="str">
-        <v>65 no godown</v>
       </c>
       <c r="N89" t="str">
         <v>FY23 Summary: 65 Godown - Maintenance for 2023-04</v>
@@ -5913,14 +5391,8 @@
       <c r="J90">
         <v>2100</v>
       </c>
-      <c r="K90" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L90" t="str">
         <v/>
-      </c>
-      <c r="M90" t="str">
-        <v>65 no godown</v>
       </c>
       <c r="N90" t="str">
         <v>FY23 Summary: 65 Godown - Rent for 2023-10</v>
@@ -5969,14 +5441,8 @@
       <c r="J91">
         <v>2800</v>
       </c>
-      <c r="K91" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L91" t="str">
         <v/>
-      </c>
-      <c r="M91" t="str">
-        <v>65 no godown</v>
       </c>
       <c r="N91" t="str">
         <v>FY23 Summary: 65 Godown - Other expenses for 2023-09</v>
@@ -6025,14 +5491,8 @@
       <c r="J92">
         <v>184068</v>
       </c>
-      <c r="K92" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L92" t="str">
         <v/>
-      </c>
-      <c r="M92" t="str">
-        <v>Garage</v>
       </c>
       <c r="N92" t="str">
         <v>FY23 Summary: Garage - Rent for 2023-09</v>
@@ -6081,14 +5541,8 @@
       <c r="J93">
         <v>50000</v>
       </c>
-      <c r="K93" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L93" t="str">
         <v/>
-      </c>
-      <c r="M93" t="str">
-        <v>Garage</v>
       </c>
       <c r="N93" t="str">
         <v>FY23 Summary: Garage - Other expenses for 2023-12</v>
@@ -6137,14 +5591,8 @@
       <c r="J94">
         <v>2500</v>
       </c>
-      <c r="K94" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L94" t="str">
         <v/>
-      </c>
-      <c r="M94" t="str">
-        <v>Ennas Room</v>
       </c>
       <c r="N94" t="str">
         <v>FY23 Summary: Ennas Room - Rent for 2023-05</v>
@@ -6193,14 +5641,8 @@
       <c r="J95">
         <v>33000</v>
       </c>
-      <c r="K95" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L95" t="str">
         <v/>
-      </c>
-      <c r="M95" t="str">
-        <v>Mani Mansion</v>
       </c>
       <c r="N95" t="str">
         <v>FY23 Summary: Mani Mansion - Maintenance for 2023-10</v>
@@ -6249,14 +5691,8 @@
       <c r="J96">
         <v>7500</v>
       </c>
-      <c r="K96" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L96" t="str">
         <v/>
-      </c>
-      <c r="M96" t="str">
-        <v>Mani Mansion</v>
       </c>
       <c r="N96" t="str">
         <v>FY23 Summary: Mani Mansion - Other expenses for 2023-12</v>
@@ -6305,14 +5741,8 @@
       <c r="J97">
         <v>7000</v>
       </c>
-      <c r="K97" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L97" t="str">
         <v/>
-      </c>
-      <c r="M97" t="str">
-        <v>Goa Flat</v>
       </c>
       <c r="N97" t="str">
         <v>FY23 Summary: Goa Flat - Electricity for 2023-04</v>
@@ -6361,14 +5791,8 @@
       <c r="J98">
         <v>1338</v>
       </c>
-      <c r="K98" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L98" t="str">
         <v/>
-      </c>
-      <c r="M98" t="str">
-        <v>Tony room (Roshan Manzil)</v>
       </c>
       <c r="N98" t="str">
         <v>FY23 Summary: Tonys room - Maintenance for 2023-12</v>
@@ -6417,14 +5841,8 @@
       <c r="J99">
         <v>96940</v>
       </c>
-      <c r="K99" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L99" t="str">
         <v/>
-      </c>
-      <c r="M99" t="str">
-        <v>Byculla Club</v>
       </c>
       <c r="N99" t="str">
         <v>FY23 Summary: Byculla Club - Rent for 2023-04</v>
@@ -6473,14 +5891,8 @@
       <c r="J100">
         <v>11000</v>
       </c>
-      <c r="K100" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L100" t="str">
         <v/>
-      </c>
-      <c r="M100" t="str">
-        <v>Byculla Club</v>
       </c>
       <c r="N100" t="str">
         <v>FY23 Summary: Byculla Club - Maintenance Sep for 2023-09</v>
@@ -6529,14 +5941,8 @@
       <c r="J101">
         <v>2500</v>
       </c>
-      <c r="K101" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L101" t="str">
         <v/>
-      </c>
-      <c r="M101" t="str">
-        <v>Byculla Club</v>
       </c>
       <c r="N101" t="str">
         <v>FY23 Summary: Byculla Club - Maintenance Dec for 2023-12</v>
@@ -6585,14 +5991,8 @@
       <c r="J102">
         <v>4600</v>
       </c>
-      <c r="K102" t="str">
-        <v>Cash</v>
-      </c>
       <c r="L102" t="str">
         <v/>
-      </c>
-      <c r="M102" t="str">
-        <v>Misscellanous exp</v>
       </c>
       <c r="N102" t="str">
         <v>FY23 Summary: Misscellanous exp for 2023-12</v>
@@ -6701,7 +6101,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K2" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="3">
@@ -6736,7 +6136,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K3" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="4">
@@ -6771,7 +6171,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K4" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="5">
@@ -6806,7 +6206,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K5" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="6">
@@ -6841,7 +6241,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K6" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="7">
@@ -6876,7 +6276,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K7" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="8">
@@ -6911,7 +6311,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K8" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="9">
@@ -6946,7 +6346,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K9" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="10">
@@ -6981,7 +6381,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K10" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="11">
@@ -7016,7 +6416,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K11" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="12">
@@ -7051,7 +6451,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K12" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="13">
@@ -7086,7 +6486,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K13" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="14">
@@ -7121,7 +6521,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K14" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="15">
@@ -7156,7 +6556,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K15" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="16">
@@ -7191,7 +6591,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K16" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="17">
@@ -7226,7 +6626,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K17" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="18">
@@ -7261,7 +6661,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K18" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="19">
@@ -7296,7 +6696,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K19" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="20">
@@ -7331,7 +6731,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K20" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="21">
@@ -7366,7 +6766,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K21" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="22">
@@ -7401,7 +6801,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K22" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="23">
@@ -7436,7 +6836,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K23" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="24">
@@ -7471,7 +6871,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K24" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="25">
@@ -7506,7 +6906,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K25" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="26">
@@ -7541,7 +6941,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K26" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="27">
@@ -7576,7 +6976,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K27" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="28">
@@ -7611,7 +7011,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K28" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="29">
@@ -7646,7 +7046,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K29" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="30">
@@ -7681,7 +7081,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K30" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="31">
@@ -7716,7 +7116,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K31" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="32">
@@ -7751,7 +7151,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K32" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="33">
@@ -7786,7 +7186,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K33" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="34">
@@ -7821,7 +7221,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K34" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="35">
@@ -7856,7 +7256,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K35" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="36">
@@ -7891,7 +7291,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K36" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="37">
@@ -7926,7 +7326,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K37" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="38">
@@ -7961,7 +7361,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K38" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="39">
@@ -7996,7 +7396,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K39" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="40">
@@ -8031,7 +7431,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K40" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="41">
@@ -8066,7 +7466,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K41" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="42">
@@ -8101,7 +7501,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K42" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="43">
@@ -8136,7 +7536,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K43" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="44">
@@ -8171,7 +7571,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K44" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="45">
@@ -8206,7 +7606,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K45" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="46">
@@ -8241,7 +7641,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K46" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="47">
@@ -8276,7 +7676,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K47" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="48">
@@ -8311,7 +7711,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K48" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="49">
@@ -8346,7 +7746,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K49" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="50">
@@ -8381,7 +7781,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K50" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="51">
@@ -8416,7 +7816,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K51" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="52">
@@ -8451,7 +7851,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K52" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="53">
@@ -8486,7 +7886,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K53" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="54">
@@ -8521,7 +7921,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K54" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="55">
@@ -8556,7 +7956,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K55" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="56">
@@ -8591,7 +7991,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K56" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="57">
@@ -8626,7 +8026,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K57" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="58">
@@ -8661,7 +8061,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K58" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="59">
@@ -8696,7 +8096,7 @@
         <v>25/10/2026</v>
       </c>
       <c r="K59" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="60">
@@ -8731,7 +8131,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K60" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="61">
@@ -8766,7 +8166,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K61" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="62">
@@ -8801,7 +8201,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K62" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="63">
@@ -8836,7 +8236,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K63" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="64">
@@ -8871,7 +8271,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K64" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="65">
@@ -8906,7 +8306,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K65" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="66">
@@ -8941,7 +8341,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K66" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="67">
@@ -8976,7 +8376,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K67" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="68">
@@ -9011,7 +8411,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K68" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="69">
@@ -9046,7 +8446,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K69" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="70">
@@ -9081,7 +8481,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K70" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="71">
@@ -9116,7 +8516,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K71" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="72">
@@ -9151,7 +8551,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K72" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="73">
@@ -9186,7 +8586,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K73" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="74">
@@ -9221,7 +8621,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K74" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="75">
@@ -9256,7 +8656,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K75" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="76">
@@ -9291,7 +8691,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K76" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="77">
@@ -9326,7 +8726,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K77" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="78">
@@ -9361,7 +8761,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K78" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="79">
@@ -9396,7 +8796,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K79" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="80">
@@ -9431,7 +8831,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K80" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="81">
@@ -9466,7 +8866,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="K81" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="82">
@@ -9480,16 +8880,16 @@
         <v>5643188.74</v>
       </c>
       <c r="D82">
-        <v>506050</v>
+        <v>581050</v>
       </c>
       <c r="E82">
         <v>13670</v>
       </c>
       <c r="F82">
-        <v>492380</v>
+        <v>567380</v>
       </c>
       <c r="G82">
-        <v>6135568.74</v>
+        <v>6210568.74</v>
       </c>
       <c r="H82" t="str">
         <v>Yes</v>
@@ -9501,7 +8901,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K82" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="83">
@@ -9512,19 +8912,19 @@
         <v>2026-02</v>
       </c>
       <c r="C83">
-        <v>6135568.74</v>
+        <v>6210568.74</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>-4800</v>
       </c>
       <c r="G83">
-        <v>6135568.74</v>
+        <v>6205768.74</v>
       </c>
       <c r="H83" t="str">
         <v>Yes</v>
@@ -9536,7 +8936,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K83" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="84">
@@ -9547,19 +8947,19 @@
         <v>2026-03</v>
       </c>
       <c r="C84">
-        <v>6135568.74</v>
+        <v>6205768.74</v>
       </c>
       <c r="D84">
-        <v>228000</v>
+        <v>240000</v>
       </c>
       <c r="E84">
         <v>2874350</v>
       </c>
       <c r="F84">
-        <v>-2646350</v>
+        <v>-2634350</v>
       </c>
       <c r="G84">
-        <v>3489218.74</v>
+        <v>3571418.74</v>
       </c>
       <c r="H84" t="str">
         <v>Yes</v>
@@ -9571,7 +8971,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K84" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="85">
@@ -9582,19 +8982,19 @@
         <v>2026-04</v>
       </c>
       <c r="C85">
-        <v>3489218.74</v>
+        <v>3571418.74</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>-171500</v>
       </c>
       <c r="G85">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="H85" t="str">
         <v>Yes</v>
@@ -9606,7 +9006,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K85" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="86">
@@ -9617,7 +9017,7 @@
         <v>2026-05</v>
       </c>
       <c r="C86">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -9629,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="H86" t="str">
         <v>Yes</v>
@@ -9641,7 +9041,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K86" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="87">
@@ -9652,7 +9052,7 @@
         <v>2026-06</v>
       </c>
       <c r="C87">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -9664,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="H87" t="str">
         <v>Yes</v>
@@ -9676,7 +9076,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K87" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="88">
@@ -9687,7 +9087,7 @@
         <v>2026-07</v>
       </c>
       <c r="C88">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -9699,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="H88" t="str">
         <v>Yes</v>
@@ -9711,7 +9111,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K88" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="89">
@@ -9722,7 +9122,7 @@
         <v>2026-08</v>
       </c>
       <c r="C89">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -9734,7 +9134,7 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="H89" t="str">
         <v>Yes</v>
@@ -9746,7 +9146,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K89" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="90">
@@ -9757,7 +9157,7 @@
         <v>2026-09</v>
       </c>
       <c r="C90">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -9769,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="H90" t="str">
         <v>Yes</v>
@@ -9781,7 +9181,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K90" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="91">
@@ -9792,19 +9192,19 @@
         <v>2026-10</v>
       </c>
       <c r="C91">
-        <v>3489218.74</v>
+        <v>3399918.74</v>
       </c>
       <c r="D91">
-        <v>3051676</v>
+        <v>3215926</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>3051676</v>
+        <v>3215926</v>
       </c>
       <c r="G91">
-        <v>6540894.74</v>
+        <v>6615844.74</v>
       </c>
       <c r="H91" t="str">
         <v>Yes</v>
@@ -9816,7 +9216,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="K91" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
   </sheetData>
@@ -10167,13 +9567,13 @@
         <v>No</v>
       </c>
       <c r="I2" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
       <c r="J2" t="str">
         <v>22/10/2026</v>
       </c>
       <c r="K2" t="str">
-        <v>25/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
   </sheetData>
@@ -10946,7 +10346,7 @@
         <v>20250</v>
       </c>
       <c r="L3" t="str">
-        <v>Occupied</v>
+        <v>Vacant</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -10961,7 +10361,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="Q3" t="str">
-        <v>23/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="4">
@@ -11067,7 +10467,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="Q5" t="str">
-        <v>23/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="6">
@@ -14391,10 +13791,10 @@
         <v>1/1/2018</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>31/12/2025</v>
       </c>
       <c r="K3" t="str">
-        <v>Active</v>
+        <v>Ended</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -14412,7 +13812,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="Q3" t="str">
-        <v>22/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="4">
@@ -14547,7 +13947,7 @@
         <v>6ada066dd7c483f46dca037e</v>
       </c>
       <c r="I6" t="str">
-        <v>1/2/2026</v>
+        <v>1/1/2026</v>
       </c>
       <c r="J6" t="str">
         <v>30/9/2026</v>
@@ -14571,7 +13971,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="Q6" t="str">
-        <v>23/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="7">
@@ -14621,7 +14021,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="Q7" t="str">
-        <v>22/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="8">
@@ -17942,7 +17342,7 @@
         <v>1/1/2018</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>31/12/2025</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -17951,7 +17351,7 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S3" t="str">
         <v>from Jan 2018 rent increased to 17250, feb 2022 to 20250. Paid till Nov 25</v>
@@ -17960,7 +17360,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="U3" t="str">
-        <v>22/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="4">
@@ -18134,7 +17534,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="str">
-        <v>1/2/2026</v>
+        <v>1/1/2026</v>
       </c>
       <c r="O6" t="str">
         <v>30/9/2026</v>
@@ -18155,7 +17555,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="U6" t="str">
-        <v>23/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="7">
@@ -18220,7 +17620,7 @@
         <v>22/10/2026</v>
       </c>
       <c r="U7" t="str">
-        <v>24/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="8">
@@ -22270,7 +21670,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 694 total records]</v>
+        <v>[Showing 100 of 701 total records]</v>
       </c>
     </row>
     <row r="3">
@@ -22301,13 +21701,7 @@
       <c r="I3">
         <v>75000</v>
       </c>
-      <c r="J3" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
@@ -22351,13 +21745,7 @@
       <c r="I4">
         <v>32000</v>
       </c>
-      <c r="J4" t="str">
-        <v>Cash</v>
-      </c>
       <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
@@ -22383,6 +21771,9 @@
       <c r="B5" t="str">
         <v>REC-MAR26-0025</v>
       </c>
+      <c r="C5" t="str">
+        <v>Bengali-2025</v>
+      </c>
       <c r="D5" t="str">
         <v>10/3/2026</v>
       </c>
@@ -22399,19 +21790,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="I5">
-        <v>10000</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Cash</v>
+        <v>22000</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
       <c r="M5" t="str">
-        <v>Imported from MAR26 sheet: jan part payment (10k paid, 12k bal)</v>
+        <v>Rent collection for Nov 2025</v>
       </c>
       <c r="N5" t="str">
         <v>No</v>
@@ -22423,7 +21808,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="Q5" t="str">
-        <v>23/10/2026</v>
+        <v>27/10/2026</v>
       </c>
     </row>
     <row r="6">
@@ -22451,13 +21836,7 @@
       <c r="I6">
         <v>15000</v>
       </c>
-      <c r="J6" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
@@ -22501,13 +21880,7 @@
       <c r="I7">
         <v>10000</v>
       </c>
-      <c r="J7" t="str">
-        <v>Cash</v>
-      </c>
       <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
         <v/>
       </c>
       <c r="M7" t="str">
@@ -22551,13 +21924,7 @@
       <c r="I8">
         <v>40000</v>
       </c>
-      <c r="J8" t="str">
-        <v>Cheque</v>
-      </c>
       <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
         <v/>
       </c>
       <c r="M8" t="str">
@@ -22601,13 +21968,7 @@
       <c r="I9">
         <v>12000</v>
       </c>
-      <c r="J9" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
@@ -22651,13 +22012,7 @@
       <c r="I10">
         <v>12000</v>
       </c>
-      <c r="J10" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
         <v/>
       </c>
       <c r="M10" t="str">
@@ -22683,6 +22038,9 @@
       <c r="B11" t="str">
         <v>REC-MAR26-0031</v>
       </c>
+      <c r="C11" t="str">
+        <v>Asif-2025</v>
+      </c>
       <c r="D11" t="str">
         <v>10/3/2026</v>
       </c>
@@ -22701,13 +22059,7 @@
       <c r="I11">
         <v>22000</v>
       </c>
-      <c r="J11" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
@@ -22723,7 +22075,7 @@
         <v>23/10/2026</v>
       </c>
       <c r="Q11" t="str">
-        <v>23/10/2026</v>
+        <v>26/10/2026</v>
       </c>
     </row>
     <row r="12">
@@ -22751,13 +22103,7 @@
       <c r="I12">
         <v>81561</v>
       </c>
-      <c r="J12" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
@@ -22801,13 +22147,7 @@
       <c r="I13">
         <v>110462</v>
       </c>
-      <c r="J13" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
         <v/>
       </c>
       <c r="M13" t="str">
@@ -22851,13 +22191,7 @@
       <c r="I14">
         <v>225573</v>
       </c>
-      <c r="J14" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
         <v/>
       </c>
       <c r="M14" t="str">
@@ -22901,13 +22235,7 @@
       <c r="I15">
         <v>79452</v>
       </c>
-      <c r="J15" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
@@ -22951,13 +22279,7 @@
       <c r="I16">
         <v>200000</v>
       </c>
-      <c r="J16" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
         <v/>
       </c>
       <c r="M16" t="str">
@@ -23001,13 +22323,7 @@
       <c r="I17">
         <v>179576</v>
       </c>
-      <c r="J17" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
         <v/>
       </c>
       <c r="M17" t="str">
@@ -23051,13 +22367,7 @@
       <c r="I18">
         <v>20250</v>
       </c>
-      <c r="J18" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
         <v/>
       </c>
       <c r="M18" t="str">
@@ -23101,13 +22411,7 @@
       <c r="I19">
         <v>20250</v>
       </c>
-      <c r="J19" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
         <v/>
       </c>
       <c r="M19" t="str">
@@ -23151,13 +22455,7 @@
       <c r="I20">
         <v>60750</v>
       </c>
-      <c r="J20" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
         <v/>
       </c>
       <c r="M20" t="str">
@@ -23201,13 +22499,7 @@
       <c r="I21">
         <v>20250</v>
       </c>
-      <c r="J21" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
         <v/>
       </c>
       <c r="M21" t="str">
@@ -23251,13 +22543,7 @@
       <c r="I22">
         <v>60750</v>
       </c>
-      <c r="J22" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
         <v/>
       </c>
       <c r="M22" t="str">
@@ -23301,13 +22587,7 @@
       <c r="I23">
         <v>100000</v>
       </c>
-      <c r="J23" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
         <v/>
       </c>
       <c r="M23" t="str">
@@ -23351,13 +22631,7 @@
       <c r="I24">
         <v>100000</v>
       </c>
-      <c r="J24" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
         <v/>
       </c>
       <c r="M24" t="str">
@@ -23401,13 +22675,7 @@
       <c r="I25">
         <v>100000</v>
       </c>
-      <c r="J25" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
         <v/>
       </c>
       <c r="M25" t="str">
@@ -23451,13 +22719,7 @@
       <c r="I26">
         <v>100000</v>
       </c>
-      <c r="J26" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
         <v/>
       </c>
       <c r="M26" t="str">
@@ -23501,13 +22763,7 @@
       <c r="I27">
         <v>41000</v>
       </c>
-      <c r="J27" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
         <v/>
       </c>
       <c r="M27" t="str">
@@ -23551,13 +22807,7 @@
       <c r="I28">
         <v>25000</v>
       </c>
-      <c r="J28" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
         <v/>
       </c>
       <c r="M28" t="str">
@@ -23601,13 +22851,7 @@
       <c r="I29">
         <v>20000</v>
       </c>
-      <c r="J29" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
         <v/>
       </c>
       <c r="M29" t="str">
@@ -23651,13 +22895,7 @@
       <c r="I30">
         <v>1650</v>
       </c>
-      <c r="J30" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
         <v/>
       </c>
       <c r="M30" t="str">
@@ -23701,13 +22939,7 @@
       <c r="I31">
         <v>16500</v>
       </c>
-      <c r="J31" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
         <v/>
       </c>
       <c r="M31" t="str">
@@ -23751,13 +22983,7 @@
       <c r="I32">
         <v>16500</v>
       </c>
-      <c r="J32" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
         <v/>
       </c>
       <c r="M32" t="str">
@@ -23801,13 +23027,7 @@
       <c r="I33">
         <v>16500</v>
       </c>
-      <c r="J33" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
         <v/>
       </c>
       <c r="M33" t="str">
@@ -23851,13 +23071,7 @@
       <c r="I34">
         <v>11000</v>
       </c>
-      <c r="J34" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K34" t="str">
-        <v/>
-      </c>
-      <c r="L34" t="str">
         <v/>
       </c>
       <c r="M34" t="str">
@@ -23901,13 +23115,7 @@
       <c r="I35">
         <v>5500</v>
       </c>
-      <c r="J35" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
         <v/>
       </c>
       <c r="M35" t="str">
@@ -23951,13 +23159,7 @@
       <c r="I36">
         <v>7000</v>
       </c>
-      <c r="J36" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K36" t="str">
-        <v/>
-      </c>
-      <c r="L36" t="str">
         <v/>
       </c>
       <c r="M36" t="str">
@@ -24001,13 +23203,7 @@
       <c r="I37">
         <v>7000</v>
       </c>
-      <c r="J37" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
         <v/>
       </c>
       <c r="M37" t="str">
@@ -24051,13 +23247,7 @@
       <c r="I38">
         <v>7000</v>
       </c>
-      <c r="J38" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
         <v/>
       </c>
       <c r="M38" t="str">
@@ -24101,13 +23291,7 @@
       <c r="I39">
         <v>7000</v>
       </c>
-      <c r="J39" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
         <v/>
       </c>
       <c r="M39" t="str">
@@ -24151,13 +23335,7 @@
       <c r="I40">
         <v>7000</v>
       </c>
-      <c r="J40" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K40" t="str">
-        <v/>
-      </c>
-      <c r="L40" t="str">
         <v/>
       </c>
       <c r="M40" t="str">
@@ -24201,13 +23379,7 @@
       <c r="I41">
         <v>7000</v>
       </c>
-      <c r="J41" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
         <v/>
       </c>
       <c r="M41" t="str">
@@ -24251,13 +23423,7 @@
       <c r="I42">
         <v>7000</v>
       </c>
-      <c r="J42" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
         <v/>
       </c>
       <c r="M42" t="str">
@@ -24301,13 +23467,7 @@
       <c r="I43">
         <v>7000</v>
       </c>
-      <c r="J43" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
         <v/>
       </c>
       <c r="M43" t="str">
@@ -24351,13 +23511,7 @@
       <c r="I44">
         <v>7000</v>
       </c>
-      <c r="J44" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K44" t="str">
-        <v/>
-      </c>
-      <c r="L44" t="str">
         <v/>
       </c>
       <c r="M44" t="str">
@@ -24401,13 +23555,7 @@
       <c r="I45">
         <v>7000</v>
       </c>
-      <c r="J45" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
         <v/>
       </c>
       <c r="M45" t="str">
@@ -24451,13 +23599,7 @@
       <c r="I46">
         <v>7000</v>
       </c>
-      <c r="J46" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
         <v/>
       </c>
       <c r="M46" t="str">
@@ -24501,13 +23643,7 @@
       <c r="I47">
         <v>7000</v>
       </c>
-      <c r="J47" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K47" t="str">
-        <v/>
-      </c>
-      <c r="L47" t="str">
         <v/>
       </c>
       <c r="M47" t="str">
@@ -24551,13 +23687,7 @@
       <c r="I48">
         <v>10000</v>
       </c>
-      <c r="J48" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K48" t="str">
-        <v/>
-      </c>
-      <c r="L48" t="str">
         <v/>
       </c>
       <c r="M48" t="str">
@@ -24601,13 +23731,7 @@
       <c r="I49">
         <v>10000</v>
       </c>
-      <c r="J49" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K49" t="str">
-        <v/>
-      </c>
-      <c r="L49" t="str">
         <v/>
       </c>
       <c r="M49" t="str">
@@ -24651,13 +23775,7 @@
       <c r="I50">
         <v>10000</v>
       </c>
-      <c r="J50" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K50" t="str">
-        <v/>
-      </c>
-      <c r="L50" t="str">
         <v/>
       </c>
       <c r="M50" t="str">
@@ -24701,13 +23819,7 @@
       <c r="I51">
         <v>10000</v>
       </c>
-      <c r="J51" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K51" t="str">
-        <v/>
-      </c>
-      <c r="L51" t="str">
         <v/>
       </c>
       <c r="M51" t="str">
@@ -24751,13 +23863,7 @@
       <c r="I52">
         <v>10000</v>
       </c>
-      <c r="J52" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K52" t="str">
-        <v/>
-      </c>
-      <c r="L52" t="str">
         <v/>
       </c>
       <c r="M52" t="str">
@@ -24801,13 +23907,7 @@
       <c r="I53">
         <v>40000</v>
       </c>
-      <c r="J53" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K53" t="str">
-        <v/>
-      </c>
-      <c r="L53" t="str">
         <v/>
       </c>
       <c r="M53" t="str">
@@ -24851,13 +23951,7 @@
       <c r="I54">
         <v>10000</v>
       </c>
-      <c r="J54" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K54" t="str">
-        <v/>
-      </c>
-      <c r="L54" t="str">
         <v/>
       </c>
       <c r="M54" t="str">
@@ -24901,13 +23995,7 @@
       <c r="I55">
         <v>10000</v>
       </c>
-      <c r="J55" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K55" t="str">
-        <v/>
-      </c>
-      <c r="L55" t="str">
         <v/>
       </c>
       <c r="M55" t="str">
@@ -24951,13 +24039,7 @@
       <c r="I56">
         <v>10000</v>
       </c>
-      <c r="J56" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K56" t="str">
-        <v/>
-      </c>
-      <c r="L56" t="str">
         <v/>
       </c>
       <c r="M56" t="str">
@@ -25001,13 +24083,7 @@
       <c r="I57">
         <v>10000</v>
       </c>
-      <c r="J57" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K57" t="str">
-        <v/>
-      </c>
-      <c r="L57" t="str">
         <v/>
       </c>
       <c r="M57" t="str">
@@ -25051,13 +24127,7 @@
       <c r="I58">
         <v>10000</v>
       </c>
-      <c r="J58" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K58" t="str">
-        <v/>
-      </c>
-      <c r="L58" t="str">
         <v/>
       </c>
       <c r="M58" t="str">
@@ -25101,13 +24171,7 @@
       <c r="I59">
         <v>30000</v>
       </c>
-      <c r="J59" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K59" t="str">
-        <v/>
-      </c>
-      <c r="L59" t="str">
         <v/>
       </c>
       <c r="M59" t="str">
@@ -25151,13 +24215,7 @@
       <c r="I60">
         <v>30000</v>
       </c>
-      <c r="J60" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K60" t="str">
-        <v/>
-      </c>
-      <c r="L60" t="str">
         <v/>
       </c>
       <c r="M60" t="str">
@@ -25201,13 +24259,7 @@
       <c r="I61">
         <v>30000</v>
       </c>
-      <c r="J61" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K61" t="str">
-        <v/>
-      </c>
-      <c r="L61" t="str">
         <v/>
       </c>
       <c r="M61" t="str">
@@ -25251,13 +24303,7 @@
       <c r="I62">
         <v>30000</v>
       </c>
-      <c r="J62" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K62" t="str">
-        <v/>
-      </c>
-      <c r="L62" t="str">
         <v/>
       </c>
       <c r="M62" t="str">
@@ -25301,13 +24347,7 @@
       <c r="I63">
         <v>30000</v>
       </c>
-      <c r="J63" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K63" t="str">
-        <v/>
-      </c>
-      <c r="L63" t="str">
         <v/>
       </c>
       <c r="M63" t="str">
@@ -25351,13 +24391,7 @@
       <c r="I64">
         <v>30000</v>
       </c>
-      <c r="J64" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K64" t="str">
-        <v/>
-      </c>
-      <c r="L64" t="str">
         <v/>
       </c>
       <c r="M64" t="str">
@@ -25401,13 +24435,7 @@
       <c r="I65">
         <v>30000</v>
       </c>
-      <c r="J65" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K65" t="str">
-        <v/>
-      </c>
-      <c r="L65" t="str">
         <v/>
       </c>
       <c r="M65" t="str">
@@ -25451,13 +24479,7 @@
       <c r="I66">
         <v>30000</v>
       </c>
-      <c r="J66" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K66" t="str">
-        <v/>
-      </c>
-      <c r="L66" t="str">
         <v/>
       </c>
       <c r="M66" t="str">
@@ -25501,13 +24523,7 @@
       <c r="I67">
         <v>30000</v>
       </c>
-      <c r="J67" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K67" t="str">
-        <v/>
-      </c>
-      <c r="L67" t="str">
         <v/>
       </c>
       <c r="M67" t="str">
@@ -25551,13 +24567,7 @@
       <c r="I68">
         <v>30000</v>
       </c>
-      <c r="J68" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K68" t="str">
-        <v/>
-      </c>
-      <c r="L68" t="str">
         <v/>
       </c>
       <c r="M68" t="str">
@@ -25601,13 +24611,7 @@
       <c r="I69">
         <v>30000</v>
       </c>
-      <c r="J69" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K69" t="str">
-        <v/>
-      </c>
-      <c r="L69" t="str">
         <v/>
       </c>
       <c r="M69" t="str">
@@ -25651,13 +24655,7 @@
       <c r="I70">
         <v>30000</v>
       </c>
-      <c r="J70" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K70" t="str">
-        <v/>
-      </c>
-      <c r="L70" t="str">
         <v/>
       </c>
       <c r="M70" t="str">
@@ -25701,13 +24699,7 @@
       <c r="I71">
         <v>30000</v>
       </c>
-      <c r="J71" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K71" t="str">
-        <v/>
-      </c>
-      <c r="L71" t="str">
         <v/>
       </c>
       <c r="M71" t="str">
@@ -25751,13 +24743,7 @@
       <c r="I72">
         <v>30000</v>
       </c>
-      <c r="J72" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K72" t="str">
-        <v/>
-      </c>
-      <c r="L72" t="str">
         <v/>
       </c>
       <c r="M72" t="str">
@@ -25801,13 +24787,7 @@
       <c r="I73">
         <v>30000</v>
       </c>
-      <c r="J73" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K73" t="str">
-        <v/>
-      </c>
-      <c r="L73" t="str">
         <v/>
       </c>
       <c r="M73" t="str">
@@ -25851,13 +24831,7 @@
       <c r="I74">
         <v>30000</v>
       </c>
-      <c r="J74" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K74" t="str">
-        <v/>
-      </c>
-      <c r="L74" t="str">
         <v/>
       </c>
       <c r="M74" t="str">
@@ -25901,13 +24875,7 @@
       <c r="I75">
         <v>60000</v>
       </c>
-      <c r="J75" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K75" t="str">
-        <v/>
-      </c>
-      <c r="L75" t="str">
         <v/>
       </c>
       <c r="M75" t="str">
@@ -25951,13 +24919,7 @@
       <c r="I76">
         <v>60000</v>
       </c>
-      <c r="J76" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K76" t="str">
-        <v/>
-      </c>
-      <c r="L76" t="str">
         <v/>
       </c>
       <c r="M76" t="str">
@@ -26001,13 +24963,7 @@
       <c r="I77">
         <v>35000</v>
       </c>
-      <c r="J77" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K77" t="str">
-        <v/>
-      </c>
-      <c r="L77" t="str">
         <v/>
       </c>
       <c r="M77" t="str">
@@ -26051,13 +25007,7 @@
       <c r="I78">
         <v>35000</v>
       </c>
-      <c r="J78" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K78" t="str">
-        <v/>
-      </c>
-      <c r="L78" t="str">
         <v/>
       </c>
       <c r="M78" t="str">
@@ -26101,13 +25051,7 @@
       <c r="I79">
         <v>70000</v>
       </c>
-      <c r="J79" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K79" t="str">
-        <v/>
-      </c>
-      <c r="L79" t="str">
         <v/>
       </c>
       <c r="M79" t="str">
@@ -26151,13 +25095,7 @@
       <c r="I80">
         <v>10000</v>
       </c>
-      <c r="J80" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K80" t="str">
-        <v/>
-      </c>
-      <c r="L80" t="str">
         <v/>
       </c>
       <c r="M80" t="str">
@@ -26201,13 +25139,7 @@
       <c r="I81">
         <v>10000</v>
       </c>
-      <c r="J81" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K81" t="str">
-        <v/>
-      </c>
-      <c r="L81" t="str">
         <v/>
       </c>
       <c r="M81" t="str">
@@ -26251,13 +25183,7 @@
       <c r="I82">
         <v>30000</v>
       </c>
-      <c r="J82" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K82" t="str">
-        <v/>
-      </c>
-      <c r="L82" t="str">
         <v/>
       </c>
       <c r="M82" t="str">
@@ -26301,13 +25227,7 @@
       <c r="I83">
         <v>10000</v>
       </c>
-      <c r="J83" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K83" t="str">
-        <v/>
-      </c>
-      <c r="L83" t="str">
         <v/>
       </c>
       <c r="M83" t="str">
@@ -26351,13 +25271,7 @@
       <c r="I84">
         <v>30000</v>
       </c>
-      <c r="J84" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K84" t="str">
-        <v/>
-      </c>
-      <c r="L84" t="str">
         <v/>
       </c>
       <c r="M84" t="str">
@@ -26401,13 +25315,7 @@
       <c r="I85">
         <v>22000</v>
       </c>
-      <c r="J85" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K85" t="str">
-        <v/>
-      </c>
-      <c r="L85" t="str">
         <v/>
       </c>
       <c r="M85" t="str">
@@ -26451,13 +25359,7 @@
       <c r="I86">
         <v>22000</v>
       </c>
-      <c r="J86" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K86" t="str">
-        <v/>
-      </c>
-      <c r="L86" t="str">
         <v/>
       </c>
       <c r="M86" t="str">
@@ -26501,13 +25403,7 @@
       <c r="I87">
         <v>66000</v>
       </c>
-      <c r="J87" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K87" t="str">
-        <v/>
-      </c>
-      <c r="L87" t="str">
         <v/>
       </c>
       <c r="M87" t="str">
@@ -26551,13 +25447,7 @@
       <c r="I88">
         <v>22000</v>
       </c>
-      <c r="J88" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K88" t="str">
-        <v/>
-      </c>
-      <c r="L88" t="str">
         <v/>
       </c>
       <c r="M88" t="str">
@@ -26601,13 +25491,7 @@
       <c r="I89">
         <v>66000</v>
       </c>
-      <c r="J89" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K89" t="str">
-        <v/>
-      </c>
-      <c r="L89" t="str">
         <v/>
       </c>
       <c r="M89" t="str">
@@ -26651,13 +25535,7 @@
       <c r="I90">
         <v>20000</v>
       </c>
-      <c r="J90" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K90" t="str">
-        <v/>
-      </c>
-      <c r="L90" t="str">
         <v/>
       </c>
       <c r="M90" t="str">
@@ -26701,13 +25579,7 @@
       <c r="I91">
         <v>20000</v>
       </c>
-      <c r="J91" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K91" t="str">
-        <v/>
-      </c>
-      <c r="L91" t="str">
         <v/>
       </c>
       <c r="M91" t="str">
@@ -26751,13 +25623,7 @@
       <c r="I92">
         <v>20000</v>
       </c>
-      <c r="J92" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K92" t="str">
-        <v/>
-      </c>
-      <c r="L92" t="str">
         <v/>
       </c>
       <c r="M92" t="str">
@@ -26801,13 +25667,7 @@
       <c r="I93">
         <v>20000</v>
       </c>
-      <c r="J93" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K93" t="str">
-        <v/>
-      </c>
-      <c r="L93" t="str">
         <v/>
       </c>
       <c r="M93" t="str">
@@ -26851,13 +25711,7 @@
       <c r="I94">
         <v>40000</v>
       </c>
-      <c r="J94" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K94" t="str">
-        <v/>
-      </c>
-      <c r="L94" t="str">
         <v/>
       </c>
       <c r="M94" t="str">
@@ -26901,13 +25755,7 @@
       <c r="I95">
         <v>20000</v>
       </c>
-      <c r="J95" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K95" t="str">
-        <v/>
-      </c>
-      <c r="L95" t="str">
         <v/>
       </c>
       <c r="M95" t="str">
@@ -26951,13 +25799,7 @@
       <c r="I96">
         <v>30000</v>
       </c>
-      <c r="J96" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K96" t="str">
-        <v/>
-      </c>
-      <c r="L96" t="str">
         <v/>
       </c>
       <c r="M96" t="str">
@@ -27001,13 +25843,7 @@
       <c r="I97">
         <v>20000</v>
       </c>
-      <c r="J97" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K97" t="str">
-        <v/>
-      </c>
-      <c r="L97" t="str">
         <v/>
       </c>
       <c r="M97" t="str">
@@ -27051,13 +25887,7 @@
       <c r="I98">
         <v>20000</v>
       </c>
-      <c r="J98" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K98" t="str">
-        <v/>
-      </c>
-      <c r="L98" t="str">
         <v/>
       </c>
       <c r="M98" t="str">
@@ -27101,13 +25931,7 @@
       <c r="I99">
         <v>20000</v>
       </c>
-      <c r="J99" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K99" t="str">
-        <v/>
-      </c>
-      <c r="L99" t="str">
         <v/>
       </c>
       <c r="M99" t="str">
@@ -27151,13 +25975,7 @@
       <c r="I100">
         <v>20000</v>
       </c>
-      <c r="J100" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K100" t="str">
-        <v/>
-      </c>
-      <c r="L100" t="str">
         <v/>
       </c>
       <c r="M100" t="str">
@@ -27201,13 +26019,7 @@
       <c r="I101">
         <v>15000</v>
       </c>
-      <c r="J101" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K101" t="str">
-        <v/>
-      </c>
-      <c r="L101" t="str">
         <v/>
       </c>
       <c r="M101" t="str">
@@ -27251,13 +26063,7 @@
       <c r="I102">
         <v>15000</v>
       </c>
-      <c r="J102" t="str">
-        <v>Bank Transfer / NEFT / RTGS</v>
-      </c>
       <c r="K102" t="str">
-        <v/>
-      </c>
-      <c r="L102" t="str">
         <v/>
       </c>
       <c r="M102" t="str">
@@ -27345,7 +26151,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 694 total records]</v>
+        <v>[Showing 100 of 705 total records]</v>
       </c>
     </row>
     <row r="3">
@@ -27377,7 +26183,7 @@
         <v>75000</v>
       </c>
       <c r="J3" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v>Imported from MAR26 sheet: Paid till Mar 26</v>
@@ -27418,7 +26224,7 @@
         <v>32000</v>
       </c>
       <c r="J4" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K4" t="str">
         <v>Imported from MAR26 sheet: Paid Mar 26</v>
@@ -27432,37 +26238,37 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6adb05a80fc1b8508a9dfa87</v>
+        <v>6adb05a80fc1b8508a9dfa89</v>
       </c>
       <c r="B5" t="str">
-        <v>REC-MAR26-0025</v>
+        <v>REC-MAR26-0026</v>
       </c>
       <c r="C5" t="str">
-        <v>6adb05a80fc1b8508a9dfa86</v>
+        <v>6adb05a80fc1b8508a9dfa88</v>
       </c>
       <c r="D5" t="str">
-        <v>Bengali</v>
+        <v>Aswini Derad Monga</v>
       </c>
       <c r="E5" t="str">
-        <v>6ada066dd7c483f46dca03b1</v>
+        <v>6ada066dd7c483f46dca03bc</v>
       </c>
       <c r="F5" t="str">
-        <v>Ennas Room</v>
+        <v>Mani Mansion -Room 1</v>
       </c>
       <c r="G5" t="str">
-        <v>6ada066dd7c483f46dca0386</v>
+        <v>6ada066dd7c483f46dca0387</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-01</v>
+        <v>2026-03</v>
       </c>
       <c r="I5">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="J5" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>Imported from MAR26 sheet: jan part payment (10k paid, 12k bal)</v>
+        <v>Imported from MAR26 sheet: Paid Mar 26</v>
       </c>
       <c r="L5" t="str">
         <v>23/10/2026</v>
@@ -27473,37 +26279,37 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>6adb05a80fc1b8508a9dfa89</v>
+        <v>6adb05a80fc1b8508a9dfa8b</v>
       </c>
       <c r="B6" t="str">
-        <v>REC-MAR26-0026</v>
+        <v>REC-MAR26-0027</v>
       </c>
       <c r="C6" t="str">
-        <v>6adb05a80fc1b8508a9dfa88</v>
+        <v>6adb05a80fc1b8508a9dfa8a</v>
       </c>
       <c r="D6" t="str">
-        <v>Aswini Derad Monga</v>
+        <v>Santu Hajra</v>
       </c>
       <c r="E6" t="str">
-        <v>6ada066dd7c483f46dca03bc</v>
+        <v>6ada066dd7c483f46dca03cc</v>
       </c>
       <c r="F6" t="str">
-        <v>Mani Mansion -Room 1</v>
+        <v>Tony Room 2</v>
       </c>
       <c r="G6" t="str">
-        <v>6ada066dd7c483f46dca0387</v>
+        <v>6ada066dd7c483f46dca038a</v>
       </c>
       <c r="H6" t="str">
         <v>2026-03</v>
       </c>
       <c r="I6">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="J6" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>Imported from MAR26 sheet: Paid Mar 26</v>
+        <v>Imported from MAR26 sheet: Paid till Mar 26 (she left)</v>
       </c>
       <c r="L6" t="str">
         <v>23/10/2026</v>
@@ -27514,37 +26320,37 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6adb05a80fc1b8508a9dfa8b</v>
+        <v>6adb05a80fc1b8508a9dfa8d</v>
       </c>
       <c r="B7" t="str">
-        <v>REC-MAR26-0027</v>
+        <v>REC-MAR26-0028</v>
       </c>
       <c r="C7" t="str">
-        <v>6adb05a80fc1b8508a9dfa8a</v>
+        <v>6adb05a80fc1b8508a9dfa8c</v>
       </c>
       <c r="D7" t="str">
-        <v>Santu Hajra</v>
+        <v>Amir Kids</v>
       </c>
       <c r="E7" t="str">
-        <v>6ada066dd7c483f46dca03cc</v>
+        <v>6ada066dd7c483f46dca03d5</v>
       </c>
       <c r="F7" t="str">
-        <v>Tony Room 2</v>
+        <v>1st Floor</v>
       </c>
       <c r="G7" t="str">
-        <v>6ada066dd7c483f46dca038a</v>
+        <v>6ada066dd7c483f46dca038b</v>
       </c>
       <c r="H7" t="str">
         <v>2026-03</v>
       </c>
       <c r="I7">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="J7" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>Imported from MAR26 sheet: Paid till Mar 26 (she left)</v>
+        <v>Imported from MAR26 sheet: Monthly cheque portion</v>
       </c>
       <c r="L7" t="str">
         <v>23/10/2026</v>
@@ -27555,37 +26361,37 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>6adb05a80fc1b8508a9dfa8d</v>
+        <v>6adb05a80fc1b8508a9dfa8f</v>
       </c>
       <c r="B8" t="str">
-        <v>REC-MAR26-0028</v>
+        <v>REC-MAR26-0029</v>
       </c>
       <c r="C8" t="str">
-        <v>6adb05a80fc1b8508a9dfa8c</v>
+        <v>6adb05a80fc1b8508a9dfa8e</v>
       </c>
       <c r="D8" t="str">
-        <v>Amir Kids</v>
+        <v>Tenant 2108 (Fatu)</v>
       </c>
       <c r="E8" t="str">
-        <v>6ada066dd7c483f46dca03d5</v>
+        <v>6ada066dd7c483f46dca03ee</v>
       </c>
       <c r="F8" t="str">
-        <v>1st Floor</v>
+        <v>Flat No 2108</v>
       </c>
       <c r="G8" t="str">
-        <v>6ada066dd7c483f46dca038b</v>
+        <v>6ada066dd7c483f46dca038d</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-03</v>
+        <v>2026-02</v>
       </c>
       <c r="I8">
-        <v>40000</v>
+        <v>12000</v>
       </c>
       <c r="J8" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>Imported from MAR26 sheet: Monthly cheque portion</v>
+        <v>Imported from MAR26 sheet: Pd Feb 26</v>
       </c>
       <c r="L8" t="str">
         <v>23/10/2026</v>
@@ -27596,25 +26402,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6adb05a80fc1b8508a9dfa8f</v>
+        <v>6adb05a80fc1b8508a9dfa91</v>
       </c>
       <c r="B9" t="str">
-        <v>REC-MAR26-0029</v>
+        <v>REC-MAR26-0030</v>
       </c>
       <c r="C9" t="str">
-        <v>6adb05a80fc1b8508a9dfa8e</v>
+        <v>6adb05a80fc1b8508a9dfa90</v>
       </c>
       <c r="D9" t="str">
-        <v>Tenant 2108 (Fatu)</v>
+        <v>Tenant 2109</v>
       </c>
       <c r="E9" t="str">
-        <v>6ada066dd7c483f46dca03ee</v>
+        <v>6ada06f3d794c56d87c6f142</v>
       </c>
       <c r="F9" t="str">
-        <v>Flat No 2108</v>
+        <v>Flat No 2109</v>
       </c>
       <c r="G9" t="str">
-        <v>6ada066dd7c483f46dca038d</v>
+        <v>6ada066dd7c483f46dca038e</v>
       </c>
       <c r="H9" t="str">
         <v>2026-02</v>
@@ -27623,7 +26429,7 @@
         <v>12000</v>
       </c>
       <c r="J9" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K9" t="str">
         <v>Imported from MAR26 sheet: Pd Feb 26</v>
@@ -27637,37 +26443,37 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6adb05a80fc1b8508a9dfa91</v>
+        <v>6adb14208783148b24ac1509</v>
       </c>
       <c r="B10" t="str">
-        <v>REC-MAR26-0030</v>
+        <v>REC-202403-0100</v>
       </c>
       <c r="C10" t="str">
-        <v>6adb05a80fc1b8508a9dfa90</v>
+        <v>6adb14208783148b24ac1508</v>
       </c>
       <c r="D10" t="str">
-        <v>Tenant 2109</v>
+        <v>PG</v>
       </c>
       <c r="E10" t="str">
-        <v>6ada06f3d794c56d87c6f142</v>
+        <v>6ada066dd7c483f46dca0391</v>
       </c>
       <c r="F10" t="str">
-        <v>Flat No 2109</v>
+        <v>PG</v>
       </c>
       <c r="G10" t="str">
-        <v>6ada066dd7c483f46dca038e</v>
+        <v>6ada066dd7c483f46dca037b</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-02</v>
+        <v>2024-03</v>
       </c>
       <c r="I10">
-        <v>12000</v>
+        <v>81561</v>
       </c>
       <c r="J10" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>Imported from MAR26 sheet: Pd Feb 26</v>
+        <v>Kotak PG Rent</v>
       </c>
       <c r="L10" t="str">
         <v>23/10/2026</v>
@@ -27678,37 +26484,37 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6adb05a80fc1b8508a9dfa93</v>
+        <v>6adb14208783148b24ac150b</v>
       </c>
       <c r="B11" t="str">
-        <v>REC-MAR26-0031</v>
+        <v>REC-202404-0101</v>
       </c>
       <c r="C11" t="str">
-        <v>6adb05a80fc1b8508a9dfa92</v>
+        <v>6adb14208783148b24ac150a</v>
       </c>
       <c r="D11" t="str">
-        <v>Asif</v>
+        <v>PG</v>
       </c>
       <c r="E11" t="str">
-        <v>6ada066dd7c483f46dca03c4</v>
+        <v>6ada066dd7c483f46dca0391</v>
       </c>
       <c r="F11" t="str">
-        <v>Flat no 1</v>
+        <v>PG</v>
       </c>
       <c r="G11" t="str">
-        <v>6ada066dd7c483f46dca038f</v>
+        <v>6ada066dd7c483f46dca037b</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-03</v>
+        <v>2024-04</v>
       </c>
       <c r="I11">
-        <v>22000</v>
+        <v>110462</v>
       </c>
       <c r="J11" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>Imported from MAR26 sheet: Paid Mar 26</v>
+        <v>Kotak PG Rent</v>
       </c>
       <c r="L11" t="str">
         <v>23/10/2026</v>
@@ -27719,13 +26525,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>6adb14208783148b24ac1509</v>
+        <v>6adb14208783148b24ac150d</v>
       </c>
       <c r="B12" t="str">
-        <v>REC-202403-0100</v>
+        <v>REC-202407-0102</v>
       </c>
       <c r="C12" t="str">
-        <v>6adb14208783148b24ac1508</v>
+        <v>6adb14208783148b24ac150c</v>
       </c>
       <c r="D12" t="str">
         <v>PG</v>
@@ -27740,13 +26546,13 @@
         <v>6ada066dd7c483f46dca037b</v>
       </c>
       <c r="H12" t="str">
-        <v>2024-03</v>
+        <v>2024-07</v>
       </c>
       <c r="I12">
-        <v>81561</v>
+        <v>225573</v>
       </c>
       <c r="J12" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K12" t="str">
         <v>Kotak PG Rent</v>
@@ -27760,13 +26566,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>6adb14208783148b24ac150b</v>
+        <v>6adb14208783148b24ac150f</v>
       </c>
       <c r="B13" t="str">
-        <v>REC-202404-0101</v>
+        <v>REC-202408-0103</v>
       </c>
       <c r="C13" t="str">
-        <v>6adb14208783148b24ac150a</v>
+        <v>6adb14208783148b24ac150e</v>
       </c>
       <c r="D13" t="str">
         <v>PG</v>
@@ -27781,13 +26587,13 @@
         <v>6ada066dd7c483f46dca037b</v>
       </c>
       <c r="H13" t="str">
-        <v>2024-04</v>
+        <v>2024-08</v>
       </c>
       <c r="I13">
-        <v>110462</v>
+        <v>79452</v>
       </c>
       <c r="J13" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K13" t="str">
         <v>Kotak PG Rent</v>
@@ -27801,13 +26607,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>6adb14208783148b24ac150d</v>
+        <v>6adb14208783148b24ac1511</v>
       </c>
       <c r="B14" t="str">
-        <v>REC-202407-0102</v>
+        <v>REC-202501-0104</v>
       </c>
       <c r="C14" t="str">
-        <v>6adb14208783148b24ac150c</v>
+        <v>6adb14208783148b24ac1510</v>
       </c>
       <c r="D14" t="str">
         <v>PG</v>
@@ -27822,13 +26628,13 @@
         <v>6ada066dd7c483f46dca037b</v>
       </c>
       <c r="H14" t="str">
-        <v>2024-07</v>
+        <v>2025-01</v>
       </c>
       <c r="I14">
-        <v>225573</v>
+        <v>200000</v>
       </c>
       <c r="J14" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K14" t="str">
         <v>Kotak PG Rent</v>
@@ -27842,13 +26648,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6adb14208783148b24ac150f</v>
+        <v>6adb14208783148b24ac1513</v>
       </c>
       <c r="B15" t="str">
-        <v>REC-202408-0103</v>
+        <v>REC-202502-0105</v>
       </c>
       <c r="C15" t="str">
-        <v>6adb14208783148b24ac150e</v>
+        <v>6adb14208783148b24ac1512</v>
       </c>
       <c r="D15" t="str">
         <v>PG</v>
@@ -27863,13 +26669,13 @@
         <v>6ada066dd7c483f46dca037b</v>
       </c>
       <c r="H15" t="str">
-        <v>2024-08</v>
+        <v>2025-02</v>
       </c>
       <c r="I15">
-        <v>79452</v>
+        <v>179576</v>
       </c>
       <c r="J15" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K15" t="str">
         <v>Kotak PG Rent</v>
@@ -27883,37 +26689,37 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>6adb14208783148b24ac1511</v>
+        <v>6adb14208783148b24ac1515</v>
       </c>
       <c r="B16" t="str">
-        <v>REC-202501-0104</v>
+        <v>REC-202403-0106</v>
       </c>
       <c r="C16" t="str">
-        <v>6adb14208783148b24ac1510</v>
+        <v>6adb14208783148b24ac1514</v>
       </c>
       <c r="D16" t="str">
-        <v>PG</v>
+        <v>Water Wala</v>
       </c>
       <c r="E16" t="str">
-        <v>6ada066dd7c483f46dca0391</v>
+        <v>6ada066dd7c483f46dca0394</v>
       </c>
       <c r="F16" t="str">
-        <v>PG</v>
+        <v>Small Godown</v>
       </c>
       <c r="G16" t="str">
-        <v>6ada066dd7c483f46dca037b</v>
+        <v>6ada066dd7c483f46dca037c</v>
       </c>
       <c r="H16" t="str">
-        <v>2025-01</v>
+        <v>2024-03</v>
       </c>
       <c r="I16">
-        <v>200000</v>
+        <v>20250</v>
       </c>
       <c r="J16" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>Kotak PG Rent</v>
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="L16" t="str">
         <v>23/10/2026</v>
@@ -27924,37 +26730,37 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>6adb14208783148b24ac1513</v>
+        <v>6adb14208783148b24ac1517</v>
       </c>
       <c r="B17" t="str">
-        <v>REC-202502-0105</v>
+        <v>REC-202404-0107</v>
       </c>
       <c r="C17" t="str">
-        <v>6adb14208783148b24ac1512</v>
+        <v>6adb14208783148b24ac1516</v>
       </c>
       <c r="D17" t="str">
-        <v>PG</v>
+        <v>Water Wala</v>
       </c>
       <c r="E17" t="str">
-        <v>6ada066dd7c483f46dca0391</v>
+        <v>6ada066dd7c483f46dca0394</v>
       </c>
       <c r="F17" t="str">
-        <v>PG</v>
+        <v>Small Godown</v>
       </c>
       <c r="G17" t="str">
-        <v>6ada066dd7c483f46dca037b</v>
+        <v>6ada066dd7c483f46dca037c</v>
       </c>
       <c r="H17" t="str">
-        <v>2025-02</v>
+        <v>2024-04</v>
       </c>
       <c r="I17">
-        <v>179576</v>
+        <v>20250</v>
       </c>
       <c r="J17" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>Kotak PG Rent</v>
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="L17" t="str">
         <v>23/10/2026</v>
@@ -27965,13 +26771,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>6adb14208783148b24ac1515</v>
+        <v>6adb14208783148b24ac1519</v>
       </c>
       <c r="B18" t="str">
-        <v>REC-202403-0106</v>
+        <v>REC-202407-0108</v>
       </c>
       <c r="C18" t="str">
-        <v>6adb14208783148b24ac1514</v>
+        <v>6adb14208783148b24ac1518</v>
       </c>
       <c r="D18" t="str">
         <v>Water Wala</v>
@@ -27986,13 +26792,13 @@
         <v>6ada066dd7c483f46dca037c</v>
       </c>
       <c r="H18" t="str">
-        <v>2024-03</v>
+        <v>2024-07</v>
       </c>
       <c r="I18">
-        <v>20250</v>
+        <v>60750</v>
       </c>
       <c r="J18" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K18" t="str">
         <v>Small Godown Water Wala</v>
@@ -28006,13 +26812,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>6adb14208783148b24ac1517</v>
+        <v>6adb14208783148b24ac151b</v>
       </c>
       <c r="B19" t="str">
-        <v>REC-202404-0107</v>
+        <v>REC-202408-0109</v>
       </c>
       <c r="C19" t="str">
-        <v>6adb14208783148b24ac1516</v>
+        <v>6adb14208783148b24ac151a</v>
       </c>
       <c r="D19" t="str">
         <v>Water Wala</v>
@@ -28027,13 +26833,13 @@
         <v>6ada066dd7c483f46dca037c</v>
       </c>
       <c r="H19" t="str">
-        <v>2024-04</v>
+        <v>2024-08</v>
       </c>
       <c r="I19">
         <v>20250</v>
       </c>
       <c r="J19" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K19" t="str">
         <v>Small Godown Water Wala</v>
@@ -28047,13 +26853,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>6adb14208783148b24ac1519</v>
+        <v>6adb14208783148b24ac151d</v>
       </c>
       <c r="B20" t="str">
-        <v>REC-202407-0108</v>
+        <v>REC-202502-0110</v>
       </c>
       <c r="C20" t="str">
-        <v>6adb14208783148b24ac1518</v>
+        <v>6adb14208783148b24ac151c</v>
       </c>
       <c r="D20" t="str">
         <v>Water Wala</v>
@@ -28068,13 +26874,13 @@
         <v>6ada066dd7c483f46dca037c</v>
       </c>
       <c r="H20" t="str">
-        <v>2024-07</v>
+        <v>2025-02</v>
       </c>
       <c r="I20">
         <v>60750</v>
       </c>
       <c r="J20" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K20" t="str">
         <v>Small Godown Water Wala</v>
@@ -28088,37 +26894,37 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>6adb14208783148b24ac151b</v>
+        <v>6adb14208783148b24ac1521</v>
       </c>
       <c r="B21" t="str">
-        <v>REC-202408-0109</v>
+        <v>REC-202404-0112</v>
       </c>
       <c r="C21" t="str">
-        <v>6adb14208783148b24ac151a</v>
+        <v>6adb14208783148b24ac1520</v>
       </c>
       <c r="D21" t="str">
-        <v>Water Wala</v>
+        <v>Mahendra Bhai</v>
       </c>
       <c r="E21" t="str">
-        <v>6ada066dd7c483f46dca0394</v>
+        <v>6adb13df8de06f124e136716</v>
       </c>
       <c r="F21" t="str">
-        <v>Small Godown</v>
+        <v>65 Large Godown</v>
       </c>
       <c r="G21" t="str">
-        <v>6ada066dd7c483f46dca037c</v>
+        <v>6ada066dd7c483f46dca037d</v>
       </c>
       <c r="H21" t="str">
-        <v>2024-08</v>
+        <v>2024-04</v>
       </c>
       <c r="I21">
-        <v>20250</v>
+        <v>100000</v>
       </c>
       <c r="J21" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K21" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>65 Large Godown Mahendra Bhai</v>
       </c>
       <c r="L21" t="str">
         <v>23/10/2026</v>
@@ -28129,37 +26935,37 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>6adb14208783148b24ac151d</v>
+        <v>6adb14208783148b24ac1523</v>
       </c>
       <c r="B22" t="str">
-        <v>REC-202502-0110</v>
+        <v>REC-202406-0113</v>
       </c>
       <c r="C22" t="str">
-        <v>6adb14208783148b24ac151c</v>
+        <v>6adb14208783148b24ac1522</v>
       </c>
       <c r="D22" t="str">
-        <v>Water Wala</v>
+        <v>Mahendra Bhai</v>
       </c>
       <c r="E22" t="str">
-        <v>6ada066dd7c483f46dca0394</v>
+        <v>6adb13df8de06f124e136716</v>
       </c>
       <c r="F22" t="str">
-        <v>Small Godown</v>
+        <v>65 Large Godown</v>
       </c>
       <c r="G22" t="str">
-        <v>6ada066dd7c483f46dca037c</v>
+        <v>6ada066dd7c483f46dca037d</v>
       </c>
       <c r="H22" t="str">
-        <v>2025-02</v>
+        <v>2024-06</v>
       </c>
       <c r="I22">
-        <v>60750</v>
+        <v>100000</v>
       </c>
       <c r="J22" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K22" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>65 Large Godown Mahendra Bhai</v>
       </c>
       <c r="L22" t="str">
         <v>23/10/2026</v>
@@ -28170,13 +26976,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>6adb14208783148b24ac1521</v>
+        <v>6adb14208783148b24ac1525</v>
       </c>
       <c r="B23" t="str">
-        <v>REC-202404-0112</v>
+        <v>REC-202408-0114</v>
       </c>
       <c r="C23" t="str">
-        <v>6adb14208783148b24ac1520</v>
+        <v>6adb14208783148b24ac1524</v>
       </c>
       <c r="D23" t="str">
         <v>Mahendra Bhai</v>
@@ -28191,13 +26997,13 @@
         <v>6ada066dd7c483f46dca037d</v>
       </c>
       <c r="H23" t="str">
-        <v>2024-04</v>
+        <v>2024-08</v>
       </c>
       <c r="I23">
         <v>100000</v>
       </c>
       <c r="J23" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K23" t="str">
         <v>65 Large Godown Mahendra Bhai</v>
@@ -28211,37 +27017,37 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>6adb14208783148b24ac1523</v>
+        <v>6adb14208783148b24ac1527</v>
       </c>
       <c r="B24" t="str">
-        <v>REC-202406-0113</v>
+        <v>REC-202407-0115</v>
       </c>
       <c r="C24" t="str">
-        <v>6adb14208783148b24ac1522</v>
+        <v>6adb14208783148b24ac1526</v>
       </c>
       <c r="D24" t="str">
-        <v>Mahendra Bhai</v>
+        <v>Alka Industry</v>
       </c>
       <c r="E24" t="str">
-        <v>6adb13df8de06f124e136716</v>
+        <v>6adb13df8de06f124e136717</v>
       </c>
       <c r="F24" t="str">
-        <v>65 Large Godown</v>
+        <v>65 Small Godown</v>
       </c>
       <c r="G24" t="str">
-        <v>6ada066dd7c483f46dca037d</v>
+        <v>6ada066dd7c483f46dca037e</v>
       </c>
       <c r="H24" t="str">
-        <v>2024-06</v>
+        <v>2024-07</v>
       </c>
       <c r="I24">
-        <v>100000</v>
+        <v>41000</v>
       </c>
       <c r="J24" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v>65 Large Godown Mahendra Bhai</v>
+        <v>65 Small Godown Alka Industry</v>
       </c>
       <c r="L24" t="str">
         <v>23/10/2026</v>
@@ -28252,37 +27058,37 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>6adb14208783148b24ac1525</v>
+        <v>6adb14208783148b24ac1529</v>
       </c>
       <c r="B25" t="str">
-        <v>REC-202408-0114</v>
+        <v>REC-202408-0116</v>
       </c>
       <c r="C25" t="str">
-        <v>6adb14208783148b24ac1524</v>
+        <v>6adb14208783148b24ac1528</v>
       </c>
       <c r="D25" t="str">
-        <v>Mahendra Bhai</v>
+        <v>Alka Industry</v>
       </c>
       <c r="E25" t="str">
-        <v>6adb13df8de06f124e136716</v>
+        <v>6adb13df8de06f124e136717</v>
       </c>
       <c r="F25" t="str">
-        <v>65 Large Godown</v>
+        <v>65 Small Godown</v>
       </c>
       <c r="G25" t="str">
-        <v>6ada066dd7c483f46dca037d</v>
+        <v>6ada066dd7c483f46dca037e</v>
       </c>
       <c r="H25" t="str">
         <v>2024-08</v>
       </c>
       <c r="I25">
-        <v>100000</v>
+        <v>25000</v>
       </c>
       <c r="J25" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>65 Large Godown Mahendra Bhai</v>
+        <v>65 Small Godown Alka Industry</v>
       </c>
       <c r="L25" t="str">
         <v>23/10/2026</v>
@@ -28293,37 +27099,37 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>6adb14208783148b24ac1527</v>
+        <v>6adb14208783148b24ac152b</v>
       </c>
       <c r="B26" t="str">
-        <v>REC-202407-0115</v>
+        <v>REC-202403-0117</v>
       </c>
       <c r="C26" t="str">
-        <v>6adb14208783148b24ac1526</v>
+        <v>6adb14208783148b24ac152a</v>
       </c>
       <c r="D26" t="str">
-        <v>Alka Industry</v>
+        <v>Baranker Room Tenant</v>
       </c>
       <c r="E26" t="str">
-        <v>6adb13df8de06f124e136717</v>
+        <v>6adb13df8de06f124e136719</v>
       </c>
       <c r="F26" t="str">
-        <v>65 Small Godown</v>
+        <v>1st Floor</v>
       </c>
       <c r="G26" t="str">
-        <v>6ada066dd7c483f46dca037e</v>
+        <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H26" t="str">
-        <v>2024-07</v>
+        <v>2024-03</v>
       </c>
       <c r="I26">
-        <v>41000</v>
+        <v>20000</v>
       </c>
       <c r="J26" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>65 Small Godown Alka Industry</v>
+        <v>Baranker room direct receipt</v>
       </c>
       <c r="L26" t="str">
         <v>23/10/2026</v>
@@ -28334,37 +27140,37 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>6adb14208783148b24ac1529</v>
+        <v>6adb14208783148b24ac152d</v>
       </c>
       <c r="B27" t="str">
-        <v>REC-202408-0116</v>
+        <v>REC-202403-0118</v>
       </c>
       <c r="C27" t="str">
-        <v>6adb14208783148b24ac1528</v>
+        <v>6adb14208783148b24ac152c</v>
       </c>
       <c r="D27" t="str">
-        <v>Alka Industry</v>
+        <v>Uttam</v>
       </c>
       <c r="E27" t="str">
-        <v>6adb13df8de06f124e136717</v>
+        <v>6adb13df8de06f124e136718</v>
       </c>
       <c r="F27" t="str">
-        <v>65 Small Godown</v>
+        <v>Mezzanine</v>
       </c>
       <c r="G27" t="str">
-        <v>6ada066dd7c483f46dca037e</v>
+        <v>6ada066dd7c483f46dca0380</v>
       </c>
       <c r="H27" t="str">
-        <v>2024-08</v>
+        <v>2024-03</v>
       </c>
       <c r="I27">
-        <v>25000</v>
+        <v>1650</v>
       </c>
       <c r="J27" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>65 Small Godown Alka Industry</v>
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="L27" t="str">
         <v>23/10/2026</v>
@@ -28375,37 +27181,37 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>6adb14208783148b24ac152b</v>
+        <v>6adb14208783148b24ac152f</v>
       </c>
       <c r="B28" t="str">
-        <v>REC-202403-0117</v>
+        <v>REC-202405-0119</v>
       </c>
       <c r="C28" t="str">
-        <v>6adb14208783148b24ac152a</v>
+        <v>6adb14208783148b24ac152e</v>
       </c>
       <c r="D28" t="str">
-        <v>Baranker Room Tenant</v>
+        <v>Uttam</v>
       </c>
       <c r="E28" t="str">
-        <v>6adb13df8de06f124e136719</v>
+        <v>6adb13df8de06f124e136718</v>
       </c>
       <c r="F28" t="str">
-        <v>1st Floor</v>
+        <v>Mezzanine</v>
       </c>
       <c r="G28" t="str">
-        <v>6ada066dd7c483f46dca037f</v>
+        <v>6ada066dd7c483f46dca0380</v>
       </c>
       <c r="H28" t="str">
-        <v>2024-03</v>
+        <v>2024-05</v>
       </c>
       <c r="I28">
-        <v>20000</v>
+        <v>16500</v>
       </c>
       <c r="J28" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K28" t="str">
-        <v>Baranker room direct receipt</v>
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="L28" t="str">
         <v>23/10/2026</v>
@@ -28416,13 +27222,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6adb14208783148b24ac152d</v>
+        <v>6adb14208783148b24ac1531</v>
       </c>
       <c r="B29" t="str">
-        <v>REC-202403-0118</v>
+        <v>REC-202407-0120</v>
       </c>
       <c r="C29" t="str">
-        <v>6adb14208783148b24ac152c</v>
+        <v>6adb14208783148b24ac1530</v>
       </c>
       <c r="D29" t="str">
         <v>Uttam</v>
@@ -28437,13 +27243,13 @@
         <v>6ada066dd7c483f46dca0380</v>
       </c>
       <c r="H29" t="str">
-        <v>2024-03</v>
+        <v>2024-07</v>
       </c>
       <c r="I29">
-        <v>1650</v>
+        <v>16500</v>
       </c>
       <c r="J29" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K29" t="str">
         <v>Baranker Mezzanine Uttam</v>
@@ -28457,13 +27263,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6adb14208783148b24ac152f</v>
+        <v>6adb14208783148b24ac1533</v>
       </c>
       <c r="B30" t="str">
-        <v>REC-202405-0119</v>
+        <v>REC-202410-0121</v>
       </c>
       <c r="C30" t="str">
-        <v>6adb14208783148b24ac152e</v>
+        <v>6adb14208783148b24ac1532</v>
       </c>
       <c r="D30" t="str">
         <v>Uttam</v>
@@ -28478,13 +27284,13 @@
         <v>6ada066dd7c483f46dca0380</v>
       </c>
       <c r="H30" t="str">
-        <v>2024-05</v>
+        <v>2024-10</v>
       </c>
       <c r="I30">
         <v>16500</v>
       </c>
       <c r="J30" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K30" t="str">
         <v>Baranker Mezzanine Uttam</v>
@@ -28498,13 +27304,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6adb14208783148b24ac1531</v>
+        <v>6adb14208783148b24ac1535</v>
       </c>
       <c r="B31" t="str">
-        <v>REC-202407-0120</v>
+        <v>REC-202412-0122</v>
       </c>
       <c r="C31" t="str">
-        <v>6adb14208783148b24ac1530</v>
+        <v>6adb14208783148b24ac1534</v>
       </c>
       <c r="D31" t="str">
         <v>Uttam</v>
@@ -28519,13 +27325,13 @@
         <v>6ada066dd7c483f46dca0380</v>
       </c>
       <c r="H31" t="str">
-        <v>2024-07</v>
+        <v>2024-12</v>
       </c>
       <c r="I31">
-        <v>16500</v>
+        <v>11000</v>
       </c>
       <c r="J31" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K31" t="str">
         <v>Baranker Mezzanine Uttam</v>
@@ -28539,13 +27345,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6adb14208783148b24ac1533</v>
+        <v>6adb14208783148b24ac1537</v>
       </c>
       <c r="B32" t="str">
-        <v>REC-202410-0121</v>
+        <v>REC-202502-0123</v>
       </c>
       <c r="C32" t="str">
-        <v>6adb14208783148b24ac1532</v>
+        <v>6adb14208783148b24ac1536</v>
       </c>
       <c r="D32" t="str">
         <v>Uttam</v>
@@ -28560,13 +27366,13 @@
         <v>6ada066dd7c483f46dca0380</v>
       </c>
       <c r="H32" t="str">
-        <v>2024-10</v>
+        <v>2025-02</v>
       </c>
       <c r="I32">
-        <v>16500</v>
+        <v>5500</v>
       </c>
       <c r="J32" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K32" t="str">
         <v>Baranker Mezzanine Uttam</v>
@@ -28580,37 +27386,37 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6adb14208783148b24ac1535</v>
+        <v>6adb14208783148b24ac1539</v>
       </c>
       <c r="B33" t="str">
-        <v>REC-202412-0122</v>
+        <v>REC-202403-0124</v>
       </c>
       <c r="C33" t="str">
-        <v>6adb14208783148b24ac1534</v>
+        <v>6adb14208783148b24ac1538</v>
       </c>
       <c r="D33" t="str">
-        <v>Uttam</v>
+        <v>Anjana Ashok Salunke</v>
       </c>
       <c r="E33" t="str">
-        <v>6adb13df8de06f124e136718</v>
+        <v>6ada066dd7c483f46dca03e0</v>
       </c>
       <c r="F33" t="str">
-        <v>Mezzanine</v>
+        <v>1st Floor</v>
       </c>
       <c r="G33" t="str">
-        <v>6ada066dd7c483f46dca0380</v>
+        <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H33" t="str">
-        <v>2024-12</v>
+        <v>2024-03</v>
       </c>
       <c r="I33">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="J33" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K33" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="L33" t="str">
         <v>23/10/2026</v>
@@ -28621,37 +27427,37 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>6adb14208783148b24ac1537</v>
+        <v>6adb14208783148b24ac153b</v>
       </c>
       <c r="B34" t="str">
-        <v>REC-202502-0123</v>
+        <v>REC-202404-0125</v>
       </c>
       <c r="C34" t="str">
-        <v>6adb14208783148b24ac1536</v>
+        <v>6adb14208783148b24ac153a</v>
       </c>
       <c r="D34" t="str">
-        <v>Uttam</v>
+        <v>Anjana Ashok Salunke</v>
       </c>
       <c r="E34" t="str">
-        <v>6adb13df8de06f124e136718</v>
+        <v>6ada066dd7c483f46dca03e0</v>
       </c>
       <c r="F34" t="str">
-        <v>Mezzanine</v>
+        <v>1st Floor</v>
       </c>
       <c r="G34" t="str">
-        <v>6ada066dd7c483f46dca0380</v>
+        <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H34" t="str">
-        <v>2025-02</v>
+        <v>2024-04</v>
       </c>
       <c r="I34">
-        <v>5500</v>
+        <v>7000</v>
       </c>
       <c r="J34" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K34" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="L34" t="str">
         <v>23/10/2026</v>
@@ -28662,13 +27468,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6adb14208783148b24ac1539</v>
+        <v>6adb14208783148b24ac153d</v>
       </c>
       <c r="B35" t="str">
-        <v>REC-202403-0124</v>
+        <v>REC-202405-0126</v>
       </c>
       <c r="C35" t="str">
-        <v>6adb14208783148b24ac1538</v>
+        <v>6adb14208783148b24ac153c</v>
       </c>
       <c r="D35" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28683,13 +27489,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H35" t="str">
-        <v>2024-03</v>
+        <v>2024-05</v>
       </c>
       <c r="I35">
         <v>7000</v>
       </c>
       <c r="J35" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K35" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28703,13 +27509,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6adb14208783148b24ac153b</v>
+        <v>6adb14208783148b24ac153f</v>
       </c>
       <c r="B36" t="str">
-        <v>REC-202404-0125</v>
+        <v>REC-202406-0127</v>
       </c>
       <c r="C36" t="str">
-        <v>6adb14208783148b24ac153a</v>
+        <v>6adb14208783148b24ac153e</v>
       </c>
       <c r="D36" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28724,13 +27530,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H36" t="str">
-        <v>2024-04</v>
+        <v>2024-06</v>
       </c>
       <c r="I36">
         <v>7000</v>
       </c>
       <c r="J36" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K36" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28744,13 +27550,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6adb14208783148b24ac153d</v>
+        <v>6adb14208783148b24ac1541</v>
       </c>
       <c r="B37" t="str">
-        <v>REC-202405-0126</v>
+        <v>REC-202407-0128</v>
       </c>
       <c r="C37" t="str">
-        <v>6adb14208783148b24ac153c</v>
+        <v>6adb14208783148b24ac1540</v>
       </c>
       <c r="D37" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28765,13 +27571,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H37" t="str">
-        <v>2024-05</v>
+        <v>2024-07</v>
       </c>
       <c r="I37">
         <v>7000</v>
       </c>
       <c r="J37" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K37" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28785,13 +27591,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>6adb14208783148b24ac153f</v>
+        <v>6adb14208783148b24ac1543</v>
       </c>
       <c r="B38" t="str">
-        <v>REC-202406-0127</v>
+        <v>REC-202408-0129</v>
       </c>
       <c r="C38" t="str">
-        <v>6adb14208783148b24ac153e</v>
+        <v>6adb14208783148b24ac1542</v>
       </c>
       <c r="D38" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28806,13 +27612,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H38" t="str">
-        <v>2024-06</v>
+        <v>2024-08</v>
       </c>
       <c r="I38">
         <v>7000</v>
       </c>
       <c r="J38" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K38" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28826,13 +27632,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>6adb14208783148b24ac1541</v>
+        <v>6adb14208783148b24ac1545</v>
       </c>
       <c r="B39" t="str">
-        <v>REC-202407-0128</v>
+        <v>REC-202409-0130</v>
       </c>
       <c r="C39" t="str">
-        <v>6adb14208783148b24ac1540</v>
+        <v>6adb14208783148b24ac1544</v>
       </c>
       <c r="D39" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28847,13 +27653,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H39" t="str">
-        <v>2024-07</v>
+        <v>2024-09</v>
       </c>
       <c r="I39">
         <v>7000</v>
       </c>
       <c r="J39" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28867,13 +27673,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>6adb14208783148b24ac1543</v>
+        <v>6adb14208783148b24ac1547</v>
       </c>
       <c r="B40" t="str">
-        <v>REC-202408-0129</v>
+        <v>REC-202410-0131</v>
       </c>
       <c r="C40" t="str">
-        <v>6adb14208783148b24ac1542</v>
+        <v>6adb14208783148b24ac1546</v>
       </c>
       <c r="D40" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28888,13 +27694,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H40" t="str">
-        <v>2024-08</v>
+        <v>2024-10</v>
       </c>
       <c r="I40">
         <v>7000</v>
       </c>
       <c r="J40" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K40" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28908,13 +27714,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6adb14208783148b24ac1545</v>
+        <v>6adb14208783148b24ac1549</v>
       </c>
       <c r="B41" t="str">
-        <v>REC-202409-0130</v>
+        <v>REC-202411-0132</v>
       </c>
       <c r="C41" t="str">
-        <v>6adb14208783148b24ac1544</v>
+        <v>6adb14208783148b24ac1548</v>
       </c>
       <c r="D41" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28929,13 +27735,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H41" t="str">
-        <v>2024-09</v>
+        <v>2024-11</v>
       </c>
       <c r="I41">
         <v>7000</v>
       </c>
       <c r="J41" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K41" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28949,13 +27755,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6adb14208783148b24ac1547</v>
+        <v>6adb14208783148b24ac154b</v>
       </c>
       <c r="B42" t="str">
-        <v>REC-202410-0131</v>
+        <v>REC-202412-0133</v>
       </c>
       <c r="C42" t="str">
-        <v>6adb14208783148b24ac1546</v>
+        <v>6adb14208783148b24ac154a</v>
       </c>
       <c r="D42" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -28970,13 +27776,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H42" t="str">
-        <v>2024-10</v>
+        <v>2024-12</v>
       </c>
       <c r="I42">
         <v>7000</v>
       </c>
       <c r="J42" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K42" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -28990,13 +27796,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>6adb14208783148b24ac1549</v>
+        <v>6adb14208783148b24ac154d</v>
       </c>
       <c r="B43" t="str">
-        <v>REC-202411-0132</v>
+        <v>REC-202501-0134</v>
       </c>
       <c r="C43" t="str">
-        <v>6adb14208783148b24ac1548</v>
+        <v>6adb14208783148b24ac154c</v>
       </c>
       <c r="D43" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -29011,13 +27817,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H43" t="str">
-        <v>2024-11</v>
+        <v>2025-01</v>
       </c>
       <c r="I43">
         <v>7000</v>
       </c>
       <c r="J43" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K43" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -29031,13 +27837,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>6adb14208783148b24ac154b</v>
+        <v>6adb14208783148b24ac154f</v>
       </c>
       <c r="B44" t="str">
-        <v>REC-202412-0133</v>
+        <v>REC-202502-0135</v>
       </c>
       <c r="C44" t="str">
-        <v>6adb14208783148b24ac154a</v>
+        <v>6adb14208783148b24ac154e</v>
       </c>
       <c r="D44" t="str">
         <v>Anjana Ashok Salunke</v>
@@ -29052,13 +27858,13 @@
         <v>6ada066dd7c483f46dca037f</v>
       </c>
       <c r="H44" t="str">
-        <v>2024-12</v>
+        <v>2025-02</v>
       </c>
       <c r="I44">
         <v>7000</v>
       </c>
       <c r="J44" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K44" t="str">
         <v>1st Floor Anjana Ashok Salunke</v>
@@ -29072,37 +27878,37 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>6adb14208783148b24ac154d</v>
+        <v>6adb14208783148b24ac1551</v>
       </c>
       <c r="B45" t="str">
-        <v>REC-202501-0134</v>
+        <v>REC-202410-0136</v>
       </c>
       <c r="C45" t="str">
-        <v>6adb14208783148b24ac154c</v>
+        <v>6adb14208783148b24ac1550</v>
       </c>
       <c r="D45" t="str">
-        <v>Anjana Ashok Salunke</v>
+        <v>Santosh</v>
       </c>
       <c r="E45" t="str">
-        <v>6ada066dd7c483f46dca03e0</v>
+        <v>6ada066dd7c483f46dca03eb</v>
       </c>
       <c r="F45" t="str">
-        <v>1st Floor</v>
+        <v>Room No 10 - Building 65 No</v>
       </c>
       <c r="G45" t="str">
-        <v>6ada066dd7c483f46dca037f</v>
+        <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H45" t="str">
-        <v>2025-01</v>
+        <v>2024-10</v>
       </c>
       <c r="I45">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="J45" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K45" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>Room 10 Santosh</v>
       </c>
       <c r="L45" t="str">
         <v>23/10/2026</v>
@@ -29113,37 +27919,37 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>6adb14208783148b24ac154f</v>
+        <v>6adb14208783148b24ac1553</v>
       </c>
       <c r="B46" t="str">
-        <v>REC-202502-0135</v>
+        <v>REC-202411-0137</v>
       </c>
       <c r="C46" t="str">
-        <v>6adb14208783148b24ac154e</v>
+        <v>6adb14208783148b24ac1552</v>
       </c>
       <c r="D46" t="str">
-        <v>Anjana Ashok Salunke</v>
+        <v>Santosh</v>
       </c>
       <c r="E46" t="str">
-        <v>6ada066dd7c483f46dca03e0</v>
+        <v>6ada066dd7c483f46dca03eb</v>
       </c>
       <c r="F46" t="str">
-        <v>1st Floor</v>
+        <v>Room No 10 - Building 65 No</v>
       </c>
       <c r="G46" t="str">
-        <v>6ada066dd7c483f46dca037f</v>
+        <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H46" t="str">
-        <v>2025-02</v>
+        <v>2024-11</v>
       </c>
       <c r="I46">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="J46" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K46" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>Room 10 Santosh</v>
       </c>
       <c r="L46" t="str">
         <v>23/10/2026</v>
@@ -29154,13 +27960,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>6adb14208783148b24ac1551</v>
+        <v>6adb14208783148b24ac1555</v>
       </c>
       <c r="B47" t="str">
-        <v>REC-202410-0136</v>
+        <v>REC-202412-0138</v>
       </c>
       <c r="C47" t="str">
-        <v>6adb14208783148b24ac1550</v>
+        <v>6adb14208783148b24ac1554</v>
       </c>
       <c r="D47" t="str">
         <v>Santosh</v>
@@ -29175,13 +27981,13 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H47" t="str">
-        <v>2024-10</v>
+        <v>2024-12</v>
       </c>
       <c r="I47">
         <v>10000</v>
       </c>
       <c r="J47" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <v>Room 10 Santosh</v>
@@ -29195,13 +28001,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>6adb14208783148b24ac1553</v>
+        <v>6adb14208783148b24ac1557</v>
       </c>
       <c r="B48" t="str">
-        <v>REC-202411-0137</v>
+        <v>REC-202501-0139</v>
       </c>
       <c r="C48" t="str">
-        <v>6adb14208783148b24ac1552</v>
+        <v>6adb14208783148b24ac1556</v>
       </c>
       <c r="D48" t="str">
         <v>Santosh</v>
@@ -29216,13 +28022,13 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H48" t="str">
-        <v>2024-11</v>
+        <v>2025-01</v>
       </c>
       <c r="I48">
         <v>10000</v>
       </c>
       <c r="J48" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K48" t="str">
         <v>Room 10 Santosh</v>
@@ -29236,13 +28042,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>6adb14208783148b24ac1555</v>
+        <v>6adb14208783148b24ac1559</v>
       </c>
       <c r="B49" t="str">
-        <v>REC-202412-0138</v>
+        <v>REC-202502-0140</v>
       </c>
       <c r="C49" t="str">
-        <v>6adb14208783148b24ac1554</v>
+        <v>6adb14208783148b24ac1558</v>
       </c>
       <c r="D49" t="str">
         <v>Santosh</v>
@@ -29257,13 +28063,13 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H49" t="str">
-        <v>2024-12</v>
+        <v>2025-02</v>
       </c>
       <c r="I49">
         <v>10000</v>
       </c>
       <c r="J49" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K49" t="str">
         <v>Room 10 Santosh</v>
@@ -29277,19 +28083,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>6adb14208783148b24ac1557</v>
+        <v>6adb14208783148b24ac155b</v>
       </c>
       <c r="B50" t="str">
-        <v>REC-202501-0139</v>
+        <v>REC-202404-0141</v>
       </c>
       <c r="C50" t="str">
-        <v>6adb14208783148b24ac1556</v>
+        <v>6adb14208783148b24ac155a</v>
       </c>
       <c r="D50" t="str">
-        <v>Santosh</v>
+        <v>Kamlesh</v>
       </c>
       <c r="E50" t="str">
-        <v>6ada066dd7c483f46dca03eb</v>
+        <v>6ada066dd7c483f46dca03e8</v>
       </c>
       <c r="F50" t="str">
         <v>Room No 10 - Building 65 No</v>
@@ -29298,16 +28104,16 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H50" t="str">
-        <v>2025-01</v>
+        <v>2024-04</v>
       </c>
       <c r="I50">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="J50" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>Room 10 Santosh</v>
+        <v>Room 10 Kamlesh (4 months rent)</v>
       </c>
       <c r="L50" t="str">
         <v>23/10/2026</v>
@@ -29318,19 +28124,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>6adb14208783148b24ac1559</v>
+        <v>6adb14208783148b24ac155d</v>
       </c>
       <c r="B51" t="str">
-        <v>REC-202502-0140</v>
+        <v>REC-202405-0142</v>
       </c>
       <c r="C51" t="str">
-        <v>6adb14208783148b24ac1558</v>
+        <v>6adb14208783148b24ac155c</v>
       </c>
       <c r="D51" t="str">
-        <v>Santosh</v>
+        <v>Kamlesh</v>
       </c>
       <c r="E51" t="str">
-        <v>6ada066dd7c483f46dca03eb</v>
+        <v>6ada066dd7c483f46dca03e8</v>
       </c>
       <c r="F51" t="str">
         <v>Room No 10 - Building 65 No</v>
@@ -29339,16 +28145,16 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H51" t="str">
-        <v>2025-02</v>
+        <v>2024-05</v>
       </c>
       <c r="I51">
         <v>10000</v>
       </c>
       <c r="J51" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K51" t="str">
-        <v>Room 10 Santosh</v>
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="L51" t="str">
         <v>23/10/2026</v>
@@ -29359,13 +28165,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>6adb14208783148b24ac155b</v>
+        <v>6adb14208783148b24ac155f</v>
       </c>
       <c r="B52" t="str">
-        <v>REC-202404-0141</v>
+        <v>REC-202406-0143</v>
       </c>
       <c r="C52" t="str">
-        <v>6adb14208783148b24ac155a</v>
+        <v>6adb14208783148b24ac155e</v>
       </c>
       <c r="D52" t="str">
         <v>Kamlesh</v>
@@ -29380,16 +28186,16 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H52" t="str">
-        <v>2024-04</v>
+        <v>2024-06</v>
       </c>
       <c r="I52">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="J52" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K52" t="str">
-        <v>Room 10 Kamlesh (4 months rent)</v>
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="L52" t="str">
         <v>23/10/2026</v>
@@ -29400,13 +28206,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>6adb14208783148b24ac155d</v>
+        <v>6adb14208783148b24ac1561</v>
       </c>
       <c r="B53" t="str">
-        <v>REC-202405-0142</v>
+        <v>REC-202407-0144</v>
       </c>
       <c r="C53" t="str">
-        <v>6adb14208783148b24ac155c</v>
+        <v>6adb14208783148b24ac1560</v>
       </c>
       <c r="D53" t="str">
         <v>Kamlesh</v>
@@ -29421,13 +28227,13 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H53" t="str">
-        <v>2024-05</v>
+        <v>2024-07</v>
       </c>
       <c r="I53">
         <v>10000</v>
       </c>
       <c r="J53" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K53" t="str">
         <v>Room 10 Kamlesh</v>
@@ -29441,13 +28247,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>6adb14208783148b24ac155f</v>
+        <v>6adb14208783148b24ac1563</v>
       </c>
       <c r="B54" t="str">
-        <v>REC-202406-0143</v>
+        <v>REC-202408-0145</v>
       </c>
       <c r="C54" t="str">
-        <v>6adb14208783148b24ac155e</v>
+        <v>6adb14208783148b24ac1562</v>
       </c>
       <c r="D54" t="str">
         <v>Kamlesh</v>
@@ -29462,13 +28268,13 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H54" t="str">
-        <v>2024-06</v>
+        <v>2024-08</v>
       </c>
       <c r="I54">
         <v>10000</v>
       </c>
       <c r="J54" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K54" t="str">
         <v>Room 10 Kamlesh</v>
@@ -29482,13 +28288,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>6adb14208783148b24ac1561</v>
+        <v>6adb14208783148b24ac1565</v>
       </c>
       <c r="B55" t="str">
-        <v>REC-202407-0144</v>
+        <v>REC-202409-0146</v>
       </c>
       <c r="C55" t="str">
-        <v>6adb14208783148b24ac1560</v>
+        <v>6adb14208783148b24ac1564</v>
       </c>
       <c r="D55" t="str">
         <v>Kamlesh</v>
@@ -29503,13 +28309,13 @@
         <v>6ada066dd7c483f46dca0381</v>
       </c>
       <c r="H55" t="str">
-        <v>2024-07</v>
+        <v>2024-09</v>
       </c>
       <c r="I55">
         <v>10000</v>
       </c>
       <c r="J55" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K55" t="str">
         <v>Room 10 Kamlesh</v>
@@ -29523,37 +28329,37 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>6adb14208783148b24ac1563</v>
+        <v>6adb14208783148b24ac1567</v>
       </c>
       <c r="B56" t="str">
-        <v>REC-202408-0145</v>
+        <v>REC-202406-0147</v>
       </c>
       <c r="C56" t="str">
-        <v>6adb14208783148b24ac1562</v>
+        <v>6adb14208783148b24ac1566</v>
       </c>
       <c r="D56" t="str">
-        <v>Kamlesh</v>
+        <v>Garage Commercial Tenant</v>
       </c>
       <c r="E56" t="str">
-        <v>6ada066dd7c483f46dca03e8</v>
+        <v>6adb13df8de06f124e13671a</v>
       </c>
       <c r="F56" t="str">
-        <v>Room No 10 - Building 65 No</v>
+        <v>Shop 1</v>
       </c>
       <c r="G56" t="str">
-        <v>6ada066dd7c483f46dca0381</v>
+        <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H56" t="str">
-        <v>2024-08</v>
+        <v>2024-06</v>
       </c>
       <c r="I56">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="J56" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K56" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>Garage commercial rent</v>
       </c>
       <c r="L56" t="str">
         <v>23/10/2026</v>
@@ -29564,37 +28370,37 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>6adb14208783148b24ac1565</v>
+        <v>6adb14208783148b24ac1569</v>
       </c>
       <c r="B57" t="str">
-        <v>REC-202409-0146</v>
+        <v>REC-202407-0148</v>
       </c>
       <c r="C57" t="str">
-        <v>6adb14208783148b24ac1564</v>
+        <v>6adb14208783148b24ac1568</v>
       </c>
       <c r="D57" t="str">
-        <v>Kamlesh</v>
+        <v>Garage Commercial Tenant</v>
       </c>
       <c r="E57" t="str">
-        <v>6ada066dd7c483f46dca03e8</v>
+        <v>6adb13df8de06f124e13671a</v>
       </c>
       <c r="F57" t="str">
-        <v>Room No 10 - Building 65 No</v>
+        <v>Shop 1</v>
       </c>
       <c r="G57" t="str">
-        <v>6ada066dd7c483f46dca0381</v>
+        <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H57" t="str">
-        <v>2024-09</v>
+        <v>2024-07</v>
       </c>
       <c r="I57">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="J57" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K57" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>Garage commercial rent</v>
       </c>
       <c r="L57" t="str">
         <v>23/10/2026</v>
@@ -29605,37 +28411,37 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>6adb14208783148b24ac1567</v>
+        <v>6adb14208783148b24ac156b</v>
       </c>
       <c r="B58" t="str">
-        <v>REC-202406-0147</v>
+        <v>REC-202403-0149</v>
       </c>
       <c r="C58" t="str">
-        <v>6adb14208783148b24ac1566</v>
+        <v>6adb14208783148b24ac156a</v>
       </c>
       <c r="D58" t="str">
-        <v>Garage Commercial Tenant</v>
+        <v>Snip - Irfan Ansari</v>
       </c>
       <c r="E58" t="str">
-        <v>6adb13df8de06f124e13671a</v>
+        <v>6ada066dd7c483f46dca03a5</v>
       </c>
       <c r="F58" t="str">
-        <v>Shop 1</v>
+        <v>Shop 2</v>
       </c>
       <c r="G58" t="str">
-        <v>6ada066dd7c483f46dca0382</v>
+        <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H58" t="str">
-        <v>2024-06</v>
+        <v>2024-03</v>
       </c>
       <c r="I58">
         <v>30000</v>
       </c>
       <c r="J58" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K58" t="str">
-        <v>Garage commercial rent</v>
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="L58" t="str">
         <v>23/10/2026</v>
@@ -29646,37 +28452,37 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>6adb14208783148b24ac1569</v>
+        <v>6adb14208783148b24ac156d</v>
       </c>
       <c r="B59" t="str">
-        <v>REC-202407-0148</v>
+        <v>REC-202404-0150</v>
       </c>
       <c r="C59" t="str">
-        <v>6adb14208783148b24ac1568</v>
+        <v>6adb14208783148b24ac156c</v>
       </c>
       <c r="D59" t="str">
-        <v>Garage Commercial Tenant</v>
+        <v>Snip - Irfan Ansari</v>
       </c>
       <c r="E59" t="str">
-        <v>6adb13df8de06f124e13671a</v>
+        <v>6ada066dd7c483f46dca03a5</v>
       </c>
       <c r="F59" t="str">
-        <v>Shop 1</v>
+        <v>Shop 2</v>
       </c>
       <c r="G59" t="str">
-        <v>6ada066dd7c483f46dca0382</v>
+        <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H59" t="str">
-        <v>2024-07</v>
+        <v>2024-04</v>
       </c>
       <c r="I59">
         <v>30000</v>
       </c>
       <c r="J59" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K59" t="str">
-        <v>Garage commercial rent</v>
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="L59" t="str">
         <v>23/10/2026</v>
@@ -29687,13 +28493,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>6adb14208783148b24ac156b</v>
+        <v>6adb14208783148b24ac156f</v>
       </c>
       <c r="B60" t="str">
-        <v>REC-202403-0149</v>
+        <v>REC-202405-0151</v>
       </c>
       <c r="C60" t="str">
-        <v>6adb14208783148b24ac156a</v>
+        <v>6adb14208783148b24ac156e</v>
       </c>
       <c r="D60" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29708,13 +28514,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H60" t="str">
-        <v>2024-03</v>
+        <v>2024-05</v>
       </c>
       <c r="I60">
         <v>30000</v>
       </c>
       <c r="J60" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K60" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29728,13 +28534,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>6adb14208783148b24ac156d</v>
+        <v>6adb14208783148b24ac1571</v>
       </c>
       <c r="B61" t="str">
-        <v>REC-202404-0150</v>
+        <v>REC-202406-0152</v>
       </c>
       <c r="C61" t="str">
-        <v>6adb14208783148b24ac156c</v>
+        <v>6adb14208783148b24ac1570</v>
       </c>
       <c r="D61" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29749,13 +28555,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H61" t="str">
-        <v>2024-04</v>
+        <v>2024-06</v>
       </c>
       <c r="I61">
         <v>30000</v>
       </c>
       <c r="J61" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K61" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29769,13 +28575,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>6adb14208783148b24ac156f</v>
+        <v>6adb14208783148b24ac1573</v>
       </c>
       <c r="B62" t="str">
-        <v>REC-202405-0151</v>
+        <v>REC-202408-0153</v>
       </c>
       <c r="C62" t="str">
-        <v>6adb14208783148b24ac156e</v>
+        <v>6adb14208783148b24ac1572</v>
       </c>
       <c r="D62" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29790,13 +28596,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H62" t="str">
-        <v>2024-05</v>
+        <v>2024-08</v>
       </c>
       <c r="I62">
         <v>30000</v>
       </c>
       <c r="J62" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K62" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29810,13 +28616,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>6adb14208783148b24ac1571</v>
+        <v>6adb14208783148b24ac1575</v>
       </c>
       <c r="B63" t="str">
-        <v>REC-202406-0152</v>
+        <v>REC-202409-0154</v>
       </c>
       <c r="C63" t="str">
-        <v>6adb14208783148b24ac1570</v>
+        <v>6adb14208783148b24ac1574</v>
       </c>
       <c r="D63" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29831,13 +28637,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H63" t="str">
-        <v>2024-06</v>
+        <v>2024-09</v>
       </c>
       <c r="I63">
         <v>30000</v>
       </c>
       <c r="J63" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K63" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29851,13 +28657,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>6adb14208783148b24ac1573</v>
+        <v>6adb14208783148b24ac1577</v>
       </c>
       <c r="B64" t="str">
-        <v>REC-202408-0153</v>
+        <v>REC-202410-0155</v>
       </c>
       <c r="C64" t="str">
-        <v>6adb14208783148b24ac1572</v>
+        <v>6adb14208783148b24ac1576</v>
       </c>
       <c r="D64" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29872,13 +28678,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H64" t="str">
-        <v>2024-08</v>
+        <v>2024-10</v>
       </c>
       <c r="I64">
         <v>30000</v>
       </c>
       <c r="J64" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K64" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29892,13 +28698,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>6adb14208783148b24ac1575</v>
+        <v>6adb14208783148b24ac1579</v>
       </c>
       <c r="B65" t="str">
-        <v>REC-202409-0154</v>
+        <v>REC-202411-0156</v>
       </c>
       <c r="C65" t="str">
-        <v>6adb14208783148b24ac1574</v>
+        <v>6adb14208783148b24ac1578</v>
       </c>
       <c r="D65" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29913,13 +28719,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H65" t="str">
-        <v>2024-09</v>
+        <v>2024-11</v>
       </c>
       <c r="I65">
         <v>30000</v>
       </c>
       <c r="J65" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K65" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29933,13 +28739,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>6adb14208783148b24ac1577</v>
+        <v>6adb14208783148b24ac157b</v>
       </c>
       <c r="B66" t="str">
-        <v>REC-202410-0155</v>
+        <v>REC-202412-0157</v>
       </c>
       <c r="C66" t="str">
-        <v>6adb14208783148b24ac1576</v>
+        <v>6adb14208783148b24ac157a</v>
       </c>
       <c r="D66" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29954,13 +28760,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H66" t="str">
-        <v>2024-10</v>
+        <v>2024-12</v>
       </c>
       <c r="I66">
         <v>30000</v>
       </c>
       <c r="J66" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K66" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -29974,13 +28780,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>6adb14208783148b24ac1579</v>
+        <v>6adb14208783148b24ac157d</v>
       </c>
       <c r="B67" t="str">
-        <v>REC-202411-0156</v>
+        <v>REC-202501-0158</v>
       </c>
       <c r="C67" t="str">
-        <v>6adb14208783148b24ac1578</v>
+        <v>6adb14208783148b24ac157c</v>
       </c>
       <c r="D67" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -29995,13 +28801,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H67" t="str">
-        <v>2024-11</v>
+        <v>2025-01</v>
       </c>
       <c r="I67">
         <v>30000</v>
       </c>
       <c r="J67" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K67" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -30015,13 +28821,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>6adb14208783148b24ac157b</v>
+        <v>6adb14208783148b24ac157f</v>
       </c>
       <c r="B68" t="str">
-        <v>REC-202412-0157</v>
+        <v>REC-202502-0159</v>
       </c>
       <c r="C68" t="str">
-        <v>6adb14208783148b24ac157a</v>
+        <v>6adb14208783148b24ac157e</v>
       </c>
       <c r="D68" t="str">
         <v>Snip - Irfan Ansari</v>
@@ -30036,13 +28842,13 @@
         <v>6ada066dd7c483f46dca0383</v>
       </c>
       <c r="H68" t="str">
-        <v>2024-12</v>
+        <v>2025-02</v>
       </c>
       <c r="I68">
         <v>30000</v>
       </c>
       <c r="J68" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K68" t="str">
         <v>Shop 2 Snip Salon</v>
@@ -30056,37 +28862,37 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>6adb14208783148b24ac157d</v>
+        <v>6adb14208783148b24ac1581</v>
       </c>
       <c r="B69" t="str">
-        <v>REC-202501-0158</v>
+        <v>REC-202403-0160</v>
       </c>
       <c r="C69" t="str">
-        <v>6adb14208783148b24ac157c</v>
+        <v>6adb14208783148b24ac1580</v>
       </c>
       <c r="D69" t="str">
-        <v>Snip - Irfan Ansari</v>
+        <v>DG Cable</v>
       </c>
       <c r="E69" t="str">
-        <v>6ada066dd7c483f46dca03a5</v>
+        <v>6ada066dd7c483f46dca03a2</v>
       </c>
       <c r="F69" t="str">
-        <v>Shop 2</v>
+        <v>Shop 1</v>
       </c>
       <c r="G69" t="str">
-        <v>6ada066dd7c483f46dca0383</v>
+        <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H69" t="str">
-        <v>2025-01</v>
+        <v>2024-03</v>
       </c>
       <c r="I69">
         <v>30000</v>
       </c>
       <c r="J69" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K69" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="L69" t="str">
         <v>23/10/2026</v>
@@ -30097,37 +28903,37 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>6adb14208783148b24ac157f</v>
+        <v>6adb14208783148b24ac1583</v>
       </c>
       <c r="B70" t="str">
-        <v>REC-202502-0159</v>
+        <v>REC-202404-0161</v>
       </c>
       <c r="C70" t="str">
-        <v>6adb14208783148b24ac157e</v>
+        <v>6adb14208783148b24ac1582</v>
       </c>
       <c r="D70" t="str">
-        <v>Snip - Irfan Ansari</v>
+        <v>DG Cable</v>
       </c>
       <c r="E70" t="str">
-        <v>6ada066dd7c483f46dca03a5</v>
+        <v>6ada066dd7c483f46dca03a2</v>
       </c>
       <c r="F70" t="str">
-        <v>Shop 2</v>
+        <v>Shop 1</v>
       </c>
       <c r="G70" t="str">
-        <v>6ada066dd7c483f46dca0383</v>
+        <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H70" t="str">
-        <v>2025-02</v>
+        <v>2024-04</v>
       </c>
       <c r="I70">
         <v>30000</v>
       </c>
       <c r="J70" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K70" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="L70" t="str">
         <v>23/10/2026</v>
@@ -30138,13 +28944,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>6adb14208783148b24ac1581</v>
+        <v>6adb14208783148b24ac1585</v>
       </c>
       <c r="B71" t="str">
-        <v>REC-202403-0160</v>
+        <v>REC-202405-0162</v>
       </c>
       <c r="C71" t="str">
-        <v>6adb14208783148b24ac1580</v>
+        <v>6adb14208783148b24ac1584</v>
       </c>
       <c r="D71" t="str">
         <v>DG Cable</v>
@@ -30159,13 +28965,13 @@
         <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H71" t="str">
-        <v>2024-03</v>
+        <v>2024-05</v>
       </c>
       <c r="I71">
         <v>30000</v>
       </c>
       <c r="J71" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K71" t="str">
         <v>Shop 1 DG Cable</v>
@@ -30179,13 +28985,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>6adb14208783148b24ac1583</v>
+        <v>6adb14208783148b24ac1587</v>
       </c>
       <c r="B72" t="str">
-        <v>REC-202404-0161</v>
+        <v>REC-202408-0163</v>
       </c>
       <c r="C72" t="str">
-        <v>6adb14208783148b24ac1582</v>
+        <v>6adb14208783148b24ac1586</v>
       </c>
       <c r="D72" t="str">
         <v>DG Cable</v>
@@ -30200,13 +29006,13 @@
         <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H72" t="str">
-        <v>2024-04</v>
+        <v>2024-08</v>
       </c>
       <c r="I72">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="J72" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K72" t="str">
         <v>Shop 1 DG Cable</v>
@@ -30220,13 +29026,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>6adb14208783148b24ac1585</v>
+        <v>6adb14208783148b24ac1589</v>
       </c>
       <c r="B73" t="str">
-        <v>REC-202405-0162</v>
+        <v>REC-202409-0164</v>
       </c>
       <c r="C73" t="str">
-        <v>6adb14208783148b24ac1584</v>
+        <v>6adb14208783148b24ac1588</v>
       </c>
       <c r="D73" t="str">
         <v>DG Cable</v>
@@ -30241,13 +29047,13 @@
         <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H73" t="str">
-        <v>2024-05</v>
+        <v>2024-09</v>
       </c>
       <c r="I73">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="J73" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K73" t="str">
         <v>Shop 1 DG Cable</v>
@@ -30261,13 +29067,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>6adb14208783148b24ac1587</v>
+        <v>6adb14208783148b24ac158b</v>
       </c>
       <c r="B74" t="str">
-        <v>REC-202408-0163</v>
+        <v>REC-202411-0165</v>
       </c>
       <c r="C74" t="str">
-        <v>6adb14208783148b24ac1586</v>
+        <v>6adb14208783148b24ac158a</v>
       </c>
       <c r="D74" t="str">
         <v>DG Cable</v>
@@ -30282,13 +29088,13 @@
         <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H74" t="str">
-        <v>2024-08</v>
+        <v>2024-11</v>
       </c>
       <c r="I74">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="J74" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K74" t="str">
         <v>Shop 1 DG Cable</v>
@@ -30302,13 +29108,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>6adb14208783148b24ac1589</v>
+        <v>6adb14208783148b24ac158d</v>
       </c>
       <c r="B75" t="str">
-        <v>REC-202409-0164</v>
+        <v>REC-202412-0166</v>
       </c>
       <c r="C75" t="str">
-        <v>6adb14208783148b24ac1588</v>
+        <v>6adb14208783148b24ac158c</v>
       </c>
       <c r="D75" t="str">
         <v>DG Cable</v>
@@ -30323,13 +29129,13 @@
         <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H75" t="str">
-        <v>2024-09</v>
+        <v>2024-12</v>
       </c>
       <c r="I75">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="J75" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <v>Shop 1 DG Cable</v>
@@ -30343,13 +29149,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>6adb14208783148b24ac158b</v>
+        <v>6adb14208783148b24ac158f</v>
       </c>
       <c r="B76" t="str">
-        <v>REC-202411-0165</v>
+        <v>REC-202501-0167</v>
       </c>
       <c r="C76" t="str">
-        <v>6adb14208783148b24ac158a</v>
+        <v>6adb14208783148b24ac158e</v>
       </c>
       <c r="D76" t="str">
         <v>DG Cable</v>
@@ -30364,13 +29170,13 @@
         <v>6ada066dd7c483f46dca0382</v>
       </c>
       <c r="H76" t="str">
-        <v>2024-11</v>
+        <v>2025-01</v>
       </c>
       <c r="I76">
-        <v>35000</v>
+        <v>70000</v>
       </c>
       <c r="J76" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K76" t="str">
         <v>Shop 1 DG Cable</v>
@@ -30384,37 +29190,37 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>6adb14208783148b24ac158d</v>
+        <v>6adb14208783148b24ac1591</v>
       </c>
       <c r="B77" t="str">
-        <v>REC-202412-0166</v>
+        <v>REC-202403-0168</v>
       </c>
       <c r="C77" t="str">
-        <v>6adb14208783148b24ac158c</v>
+        <v>6adb14208783148b24ac1590</v>
       </c>
       <c r="D77" t="str">
-        <v>DG Cable</v>
+        <v>Anand</v>
       </c>
       <c r="E77" t="str">
-        <v>6ada066dd7c483f46dca03a2</v>
+        <v>6ada066dd7c483f46dca03ab</v>
       </c>
       <c r="F77" t="str">
-        <v>Shop 1</v>
+        <v>Godown</v>
       </c>
       <c r="G77" t="str">
-        <v>6ada066dd7c483f46dca0382</v>
+        <v>6ada066dd7c483f46dca0384</v>
       </c>
       <c r="H77" t="str">
-        <v>2024-12</v>
+        <v>2024-03</v>
       </c>
       <c r="I77">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="J77" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K77" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>Godown Anand</v>
       </c>
       <c r="L77" t="str">
         <v>23/10/2026</v>
@@ -30425,37 +29231,37 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>6adb14208783148b24ac158f</v>
+        <v>6adb14208783148b24ac1593</v>
       </c>
       <c r="B78" t="str">
-        <v>REC-202501-0167</v>
+        <v>REC-202404-0169</v>
       </c>
       <c r="C78" t="str">
-        <v>6adb14208783148b24ac158e</v>
+        <v>6adb14208783148b24ac1592</v>
       </c>
       <c r="D78" t="str">
-        <v>DG Cable</v>
+        <v>Anand</v>
       </c>
       <c r="E78" t="str">
-        <v>6ada066dd7c483f46dca03a2</v>
+        <v>6ada066dd7c483f46dca03ab</v>
       </c>
       <c r="F78" t="str">
-        <v>Shop 1</v>
+        <v>Godown</v>
       </c>
       <c r="G78" t="str">
-        <v>6ada066dd7c483f46dca0382</v>
+        <v>6ada066dd7c483f46dca0384</v>
       </c>
       <c r="H78" t="str">
-        <v>2025-01</v>
+        <v>2024-04</v>
       </c>
       <c r="I78">
-        <v>70000</v>
+        <v>10000</v>
       </c>
       <c r="J78" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K78" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>Godown Anand</v>
       </c>
       <c r="L78" t="str">
         <v>23/10/2026</v>
@@ -30466,13 +29272,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>6adb14208783148b24ac1591</v>
+        <v>6adb14208783148b24ac1595</v>
       </c>
       <c r="B79" t="str">
-        <v>REC-202403-0168</v>
+        <v>REC-202407-0170</v>
       </c>
       <c r="C79" t="str">
-        <v>6adb14208783148b24ac1590</v>
+        <v>6adb14208783148b24ac1594</v>
       </c>
       <c r="D79" t="str">
         <v>Anand</v>
@@ -30487,13 +29293,13 @@
         <v>6ada066dd7c483f46dca0384</v>
       </c>
       <c r="H79" t="str">
-        <v>2024-03</v>
+        <v>2024-07</v>
       </c>
       <c r="I79">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="J79" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K79" t="str">
         <v>Godown Anand</v>
@@ -30507,13 +29313,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>6adb14208783148b24ac1593</v>
+        <v>6adb14208783148b24ac1597</v>
       </c>
       <c r="B80" t="str">
-        <v>REC-202404-0169</v>
+        <v>REC-202408-0171</v>
       </c>
       <c r="C80" t="str">
-        <v>6adb14208783148b24ac1592</v>
+        <v>6adb14208783148b24ac1596</v>
       </c>
       <c r="D80" t="str">
         <v>Anand</v>
@@ -30528,13 +29334,13 @@
         <v>6ada066dd7c483f46dca0384</v>
       </c>
       <c r="H80" t="str">
-        <v>2024-04</v>
+        <v>2024-08</v>
       </c>
       <c r="I80">
         <v>10000</v>
       </c>
       <c r="J80" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K80" t="str">
         <v>Godown Anand</v>
@@ -30548,13 +29354,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>6adb14208783148b24ac1595</v>
+        <v>6adb14208783148b24ac1599</v>
       </c>
       <c r="B81" t="str">
-        <v>REC-202407-0170</v>
+        <v>REC-202502-0172</v>
       </c>
       <c r="C81" t="str">
-        <v>6adb14208783148b24ac1594</v>
+        <v>6adb14208783148b24ac1598</v>
       </c>
       <c r="D81" t="str">
         <v>Anand</v>
@@ -30569,13 +29375,13 @@
         <v>6ada066dd7c483f46dca0384</v>
       </c>
       <c r="H81" t="str">
-        <v>2024-07</v>
+        <v>2025-02</v>
       </c>
       <c r="I81">
         <v>30000</v>
       </c>
       <c r="J81" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K81" t="str">
         <v>Godown Anand</v>
@@ -30589,37 +29395,37 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>6adb14208783148b24ac1597</v>
+        <v>6adb14208783148b24ac159b</v>
       </c>
       <c r="B82" t="str">
-        <v>REC-202408-0171</v>
+        <v>REC-202403-0173</v>
       </c>
       <c r="C82" t="str">
-        <v>6adb14208783148b24ac1596</v>
+        <v>6adb14208783148b24ac159a</v>
       </c>
       <c r="D82" t="str">
-        <v>Anand</v>
+        <v>Altaf</v>
       </c>
       <c r="E82" t="str">
-        <v>6ada066dd7c483f46dca03ab</v>
+        <v>6ada066dd7c483f46dca03ae</v>
       </c>
       <c r="F82" t="str">
-        <v>Godown</v>
+        <v>Chira Bazar House</v>
       </c>
       <c r="G82" t="str">
-        <v>6ada066dd7c483f46dca0384</v>
+        <v>6ada066dd7c483f46dca0385</v>
       </c>
       <c r="H82" t="str">
-        <v>2024-08</v>
+        <v>2024-03</v>
       </c>
       <c r="I82">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="J82" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K82" t="str">
-        <v>Godown Anand</v>
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="L82" t="str">
         <v>23/10/2026</v>
@@ -30630,37 +29436,37 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>6adb14208783148b24ac1599</v>
+        <v>6adb14208783148b24ac159d</v>
       </c>
       <c r="B83" t="str">
-        <v>REC-202502-0172</v>
+        <v>REC-202404-0174</v>
       </c>
       <c r="C83" t="str">
-        <v>6adb14208783148b24ac1598</v>
+        <v>6adb14208783148b24ac159c</v>
       </c>
       <c r="D83" t="str">
-        <v>Anand</v>
+        <v>Altaf</v>
       </c>
       <c r="E83" t="str">
-        <v>6ada066dd7c483f46dca03ab</v>
+        <v>6ada066dd7c483f46dca03ae</v>
       </c>
       <c r="F83" t="str">
-        <v>Godown</v>
+        <v>Chira Bazar House</v>
       </c>
       <c r="G83" t="str">
-        <v>6ada066dd7c483f46dca0384</v>
+        <v>6ada066dd7c483f46dca0385</v>
       </c>
       <c r="H83" t="str">
-        <v>2025-02</v>
+        <v>2024-04</v>
       </c>
       <c r="I83">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="J83" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K83" t="str">
-        <v>Godown Anand</v>
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="L83" t="str">
         <v>23/10/2026</v>
@@ -30671,13 +29477,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>6adb14208783148b24ac159b</v>
+        <v>6adb14208783148b24ac159f</v>
       </c>
       <c r="B84" t="str">
-        <v>REC-202403-0173</v>
+        <v>REC-202407-0175</v>
       </c>
       <c r="C84" t="str">
-        <v>6adb14208783148b24ac159a</v>
+        <v>6adb14208783148b24ac159e</v>
       </c>
       <c r="D84" t="str">
         <v>Altaf</v>
@@ -30692,13 +29498,13 @@
         <v>6ada066dd7c483f46dca0385</v>
       </c>
       <c r="H84" t="str">
-        <v>2024-03</v>
+        <v>2024-07</v>
       </c>
       <c r="I84">
-        <v>22000</v>
+        <v>66000</v>
       </c>
       <c r="J84" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K84" t="str">
         <v>Chira Bazar House Altaf</v>
@@ -30712,13 +29518,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>6adb14208783148b24ac159d</v>
+        <v>6adb14208783148b24ac15a1</v>
       </c>
       <c r="B85" t="str">
-        <v>REC-202404-0174</v>
+        <v>REC-202408-0176</v>
       </c>
       <c r="C85" t="str">
-        <v>6adb14208783148b24ac159c</v>
+        <v>6adb14208783148b24ac15a0</v>
       </c>
       <c r="D85" t="str">
         <v>Altaf</v>
@@ -30733,13 +29539,13 @@
         <v>6ada066dd7c483f46dca0385</v>
       </c>
       <c r="H85" t="str">
-        <v>2024-04</v>
+        <v>2024-08</v>
       </c>
       <c r="I85">
         <v>22000</v>
       </c>
       <c r="J85" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K85" t="str">
         <v>Chira Bazar House Altaf</v>
@@ -30753,13 +29559,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>6adb14208783148b24ac159f</v>
+        <v>6adb14208783148b24ac15a3</v>
       </c>
       <c r="B86" t="str">
-        <v>REC-202407-0175</v>
+        <v>REC-202502-0177</v>
       </c>
       <c r="C86" t="str">
-        <v>6adb14208783148b24ac159e</v>
+        <v>6adb14208783148b24ac15a2</v>
       </c>
       <c r="D86" t="str">
         <v>Altaf</v>
@@ -30774,13 +29580,13 @@
         <v>6ada066dd7c483f46dca0385</v>
       </c>
       <c r="H86" t="str">
-        <v>2024-07</v>
+        <v>2025-02</v>
       </c>
       <c r="I86">
         <v>66000</v>
       </c>
       <c r="J86" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K86" t="str">
         <v>Chira Bazar House Altaf</v>
@@ -30794,37 +29600,37 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>6adb14208783148b24ac15a1</v>
+        <v>6adb14208783148b24ac15a5</v>
       </c>
       <c r="B87" t="str">
-        <v>REC-202408-0176</v>
+        <v>REC-202403-0178</v>
       </c>
       <c r="C87" t="str">
-        <v>6adb14208783148b24ac15a0</v>
+        <v>6adb14208783148b24ac15a4</v>
       </c>
       <c r="D87" t="str">
-        <v>Altaf</v>
+        <v>Bengali</v>
       </c>
       <c r="E87" t="str">
-        <v>6ada066dd7c483f46dca03ae</v>
+        <v>6ada066dd7c483f46dca03b1</v>
       </c>
       <c r="F87" t="str">
-        <v>Chira Bazar House</v>
+        <v>Ennas Room</v>
       </c>
       <c r="G87" t="str">
-        <v>6ada066dd7c483f46dca0385</v>
+        <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H87" t="str">
-        <v>2024-08</v>
+        <v>2024-03</v>
       </c>
       <c r="I87">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="J87" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K87" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="L87" t="str">
         <v>23/10/2026</v>
@@ -30835,37 +29641,37 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>6adb14208783148b24ac15a3</v>
+        <v>6adb14208783148b24ac15a7</v>
       </c>
       <c r="B88" t="str">
-        <v>REC-202502-0177</v>
+        <v>REC-202404-0179</v>
       </c>
       <c r="C88" t="str">
-        <v>6adb14208783148b24ac15a2</v>
+        <v>6adb14208783148b24ac15a6</v>
       </c>
       <c r="D88" t="str">
-        <v>Altaf</v>
+        <v>Bengali</v>
       </c>
       <c r="E88" t="str">
-        <v>6ada066dd7c483f46dca03ae</v>
+        <v>6ada066dd7c483f46dca03b1</v>
       </c>
       <c r="F88" t="str">
-        <v>Chira Bazar House</v>
+        <v>Ennas Room</v>
       </c>
       <c r="G88" t="str">
-        <v>6ada066dd7c483f46dca0385</v>
+        <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H88" t="str">
-        <v>2025-02</v>
+        <v>2024-04</v>
       </c>
       <c r="I88">
-        <v>66000</v>
+        <v>20000</v>
       </c>
       <c r="J88" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K88" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="L88" t="str">
         <v>23/10/2026</v>
@@ -30876,13 +29682,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>6adb14208783148b24ac15a5</v>
+        <v>6adb14208783148b24ac15a9</v>
       </c>
       <c r="B89" t="str">
-        <v>REC-202403-0178</v>
+        <v>REC-202405-0180</v>
       </c>
       <c r="C89" t="str">
-        <v>6adb14208783148b24ac15a4</v>
+        <v>6adb14208783148b24ac15a8</v>
       </c>
       <c r="D89" t="str">
         <v>Bengali</v>
@@ -30897,13 +29703,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H89" t="str">
-        <v>2024-03</v>
+        <v>2024-05</v>
       </c>
       <c r="I89">
         <v>20000</v>
       </c>
       <c r="J89" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K89" t="str">
         <v>Ennas Room Bengali</v>
@@ -30917,13 +29723,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>6adb14208783148b24ac15a7</v>
+        <v>6adb14208783148b24ac15ab</v>
       </c>
       <c r="B90" t="str">
-        <v>REC-202404-0179</v>
+        <v>REC-202406-0181</v>
       </c>
       <c r="C90" t="str">
-        <v>6adb14208783148b24ac15a6</v>
+        <v>6adb14208783148b24ac15aa</v>
       </c>
       <c r="D90" t="str">
         <v>Bengali</v>
@@ -30938,13 +29744,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H90" t="str">
-        <v>2024-04</v>
+        <v>2024-06</v>
       </c>
       <c r="I90">
         <v>20000</v>
       </c>
       <c r="J90" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K90" t="str">
         <v>Ennas Room Bengali</v>
@@ -30958,13 +29764,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>6adb14208783148b24ac15a9</v>
+        <v>6adb14208783148b24ac15ad</v>
       </c>
       <c r="B91" t="str">
-        <v>REC-202405-0180</v>
+        <v>REC-202408-0182</v>
       </c>
       <c r="C91" t="str">
-        <v>6adb14208783148b24ac15a8</v>
+        <v>6adb14208783148b24ac15ac</v>
       </c>
       <c r="D91" t="str">
         <v>Bengali</v>
@@ -30979,13 +29785,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H91" t="str">
-        <v>2024-05</v>
+        <v>2024-08</v>
       </c>
       <c r="I91">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="J91" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K91" t="str">
         <v>Ennas Room Bengali</v>
@@ -30999,13 +29805,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>6adb14208783148b24ac15ab</v>
+        <v>6adb14208783148b24ac15af</v>
       </c>
       <c r="B92" t="str">
-        <v>REC-202406-0181</v>
+        <v>REC-202409-0183</v>
       </c>
       <c r="C92" t="str">
-        <v>6adb14208783148b24ac15aa</v>
+        <v>6adb14208783148b24ac15ae</v>
       </c>
       <c r="D92" t="str">
         <v>Bengali</v>
@@ -31020,13 +29826,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H92" t="str">
-        <v>2024-06</v>
+        <v>2024-09</v>
       </c>
       <c r="I92">
         <v>20000</v>
       </c>
       <c r="J92" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K92" t="str">
         <v>Ennas Room Bengali</v>
@@ -31040,13 +29846,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>6adb14208783148b24ac15ad</v>
+        <v>6adb14208783148b24ac15b1</v>
       </c>
       <c r="B93" t="str">
-        <v>REC-202408-0182</v>
+        <v>REC-202410-0184</v>
       </c>
       <c r="C93" t="str">
-        <v>6adb14208783148b24ac15ac</v>
+        <v>6adb14208783148b24ac15b0</v>
       </c>
       <c r="D93" t="str">
         <v>Bengali</v>
@@ -31061,13 +29867,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H93" t="str">
-        <v>2024-08</v>
+        <v>2024-10</v>
       </c>
       <c r="I93">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="J93" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K93" t="str">
         <v>Ennas Room Bengali</v>
@@ -31081,13 +29887,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>6adb14208783148b24ac15af</v>
+        <v>6adb14208783148b24ac15b3</v>
       </c>
       <c r="B94" t="str">
-        <v>REC-202409-0183</v>
+        <v>REC-202411-0185</v>
       </c>
       <c r="C94" t="str">
-        <v>6adb14208783148b24ac15ae</v>
+        <v>6adb14208783148b24ac15b2</v>
       </c>
       <c r="D94" t="str">
         <v>Bengali</v>
@@ -31102,13 +29908,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H94" t="str">
-        <v>2024-09</v>
+        <v>2024-11</v>
       </c>
       <c r="I94">
         <v>20000</v>
       </c>
       <c r="J94" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K94" t="str">
         <v>Ennas Room Bengali</v>
@@ -31122,13 +29928,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>6adb14208783148b24ac15b1</v>
+        <v>6adb14208783148b24ac15b5</v>
       </c>
       <c r="B95" t="str">
-        <v>REC-202410-0184</v>
+        <v>REC-202412-0186</v>
       </c>
       <c r="C95" t="str">
-        <v>6adb14208783148b24ac15b0</v>
+        <v>6adb14208783148b24ac15b4</v>
       </c>
       <c r="D95" t="str">
         <v>Bengali</v>
@@ -31143,13 +29949,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H95" t="str">
-        <v>2024-10</v>
+        <v>2024-12</v>
       </c>
       <c r="I95">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="J95" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K95" t="str">
         <v>Ennas Room Bengali</v>
@@ -31163,13 +29969,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>6adb14208783148b24ac15b3</v>
+        <v>6adb14208783148b24ac15b7</v>
       </c>
       <c r="B96" t="str">
-        <v>REC-202411-0185</v>
+        <v>REC-202501-0187</v>
       </c>
       <c r="C96" t="str">
-        <v>6adb14208783148b24ac15b2</v>
+        <v>6adb14208783148b24ac15b6</v>
       </c>
       <c r="D96" t="str">
         <v>Bengali</v>
@@ -31184,13 +29990,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H96" t="str">
-        <v>2024-11</v>
+        <v>2025-01</v>
       </c>
       <c r="I96">
         <v>20000</v>
       </c>
       <c r="J96" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K96" t="str">
         <v>Ennas Room Bengali</v>
@@ -31204,13 +30010,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>6adb14208783148b24ac15b5</v>
+        <v>6adb14208783148b24ac15b9</v>
       </c>
       <c r="B97" t="str">
-        <v>REC-202412-0186</v>
+        <v>REC-202502-0188</v>
       </c>
       <c r="C97" t="str">
-        <v>6adb14208783148b24ac15b4</v>
+        <v>6adb14208783148b24ac15b8</v>
       </c>
       <c r="D97" t="str">
         <v>Bengali</v>
@@ -31225,13 +30031,13 @@
         <v>6ada066dd7c483f46dca0386</v>
       </c>
       <c r="H97" t="str">
-        <v>2024-12</v>
+        <v>2025-02</v>
       </c>
       <c r="I97">
         <v>20000</v>
       </c>
       <c r="J97" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K97" t="str">
         <v>Ennas Room Bengali</v>
@@ -31245,37 +30051,37 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>6adb14208783148b24ac15b7</v>
+        <v>6adb14208783148b24ac15bb</v>
       </c>
       <c r="B98" t="str">
-        <v>REC-202501-0187</v>
+        <v>REC-202403-0189</v>
       </c>
       <c r="C98" t="str">
-        <v>6adb14208783148b24ac15b6</v>
+        <v>6adb14208783148b24ac15ba</v>
       </c>
       <c r="D98" t="str">
-        <v>Bengali</v>
+        <v>Aswini Derad Monga</v>
       </c>
       <c r="E98" t="str">
-        <v>6ada066dd7c483f46dca03b1</v>
+        <v>6ada066dd7c483f46dca03bc</v>
       </c>
       <c r="F98" t="str">
-        <v>Ennas Room</v>
+        <v>Mani Mansion -Room 1</v>
       </c>
       <c r="G98" t="str">
-        <v>6ada066dd7c483f46dca0386</v>
+        <v>6ada066dd7c483f46dca0387</v>
       </c>
       <c r="H98" t="str">
-        <v>2025-01</v>
+        <v>2024-03</v>
       </c>
       <c r="I98">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="J98" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K98" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>Mani Mansion Room 1 Aswini</v>
       </c>
       <c r="L98" t="str">
         <v>23/10/2026</v>
@@ -31286,37 +30092,37 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>6adb14208783148b24ac15b9</v>
+        <v>6adb14208783148b24ac15bd</v>
       </c>
       <c r="B99" t="str">
-        <v>REC-202502-0188</v>
+        <v>REC-202404-0190</v>
       </c>
       <c r="C99" t="str">
-        <v>6adb14208783148b24ac15b8</v>
+        <v>6adb14208783148b24ac15bc</v>
       </c>
       <c r="D99" t="str">
-        <v>Bengali</v>
+        <v>Aswini Derad Monga</v>
       </c>
       <c r="E99" t="str">
-        <v>6ada066dd7c483f46dca03b1</v>
+        <v>6ada066dd7c483f46dca03bc</v>
       </c>
       <c r="F99" t="str">
-        <v>Ennas Room</v>
+        <v>Mani Mansion -Room 1</v>
       </c>
       <c r="G99" t="str">
-        <v>6ada066dd7c483f46dca0386</v>
+        <v>6ada066dd7c483f46dca0387</v>
       </c>
       <c r="H99" t="str">
-        <v>2025-02</v>
+        <v>2024-04</v>
       </c>
       <c r="I99">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="J99" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K99" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>Mani Mansion Room 1 Aswini</v>
       </c>
       <c r="L99" t="str">
         <v>23/10/2026</v>
@@ -31327,13 +30133,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>6adb14208783148b24ac15bb</v>
+        <v>6adb14208783148b24ac15bf</v>
       </c>
       <c r="B100" t="str">
-        <v>REC-202403-0189</v>
+        <v>REC-202405-0191</v>
       </c>
       <c r="C100" t="str">
-        <v>6adb14208783148b24ac15ba</v>
+        <v>6adb14208783148b24ac15be</v>
       </c>
       <c r="D100" t="str">
         <v>Aswini Derad Monga</v>
@@ -31348,13 +30154,13 @@
         <v>6ada066dd7c483f46dca0387</v>
       </c>
       <c r="H100" t="str">
-        <v>2024-03</v>
+        <v>2024-05</v>
       </c>
       <c r="I100">
         <v>15000</v>
       </c>
       <c r="J100" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K100" t="str">
         <v>Mani Mansion Room 1 Aswini</v>
@@ -31368,13 +30174,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>6adb14208783148b24ac15bd</v>
+        <v>6adb14208783148b24ac15c1</v>
       </c>
       <c r="B101" t="str">
-        <v>REC-202404-0190</v>
+        <v>REC-202406-0192</v>
       </c>
       <c r="C101" t="str">
-        <v>6adb14208783148b24ac15bc</v>
+        <v>6adb14208783148b24ac15c0</v>
       </c>
       <c r="D101" t="str">
         <v>Aswini Derad Monga</v>
@@ -31389,13 +30195,13 @@
         <v>6ada066dd7c483f46dca0387</v>
       </c>
       <c r="H101" t="str">
-        <v>2024-04</v>
+        <v>2024-06</v>
       </c>
       <c r="I101">
         <v>15000</v>
       </c>
       <c r="J101" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K101" t="str">
         <v>Mani Mansion Room 1 Aswini</v>
@@ -31409,13 +30215,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>6adb14208783148b24ac15bf</v>
+        <v>6adb14208783148b24ac15c3</v>
       </c>
       <c r="B102" t="str">
-        <v>REC-202405-0191</v>
+        <v>REC-202407-0193</v>
       </c>
       <c r="C102" t="str">
-        <v>6adb14208783148b24ac15be</v>
+        <v>6adb14208783148b24ac15c2</v>
       </c>
       <c r="D102" t="str">
         <v>Aswini Derad Monga</v>
@@ -31430,13 +30236,13 @@
         <v>6ada066dd7c483f46dca0387</v>
       </c>
       <c r="H102" t="str">
-        <v>2024-05</v>
+        <v>2024-07</v>
       </c>
       <c r="I102">
         <v>15000</v>
       </c>
       <c r="J102" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="K102" t="str">
         <v>Mani Mansion Room 1 Aswini</v>

--- a/Property_Rent_Data_Model.xlsx
+++ b/Property_Rent_Data_Model.xlsx
@@ -576,7 +576,7 @@
         <v>Actual money received (receipt header)</v>
       </c>
       <c r="C15" t="str">
-        <v>receiptNumber, receiptDate, totalAmount, paymentMode, bankName, referenceNumber, contractNo</v>
+        <v>receiptNumber, receiptDate, totalAmount, paymentMode, bankName, contractNo</v>
       </c>
       <c r="D15" t="str">
         <v>→ Tenants, Units, PaymentAllocations</v>
@@ -837,7 +837,7 @@
         <v>PaymentReceipts</v>
       </c>
       <c r="B39">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="40">
@@ -845,7 +845,7 @@
         <v>PaymentAllocations</v>
       </c>
       <c r="B40">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>TOTAL</v>
       </c>
       <c r="B46">
-        <v>2906</v>
+        <v>2908</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:R102"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -963,27 +963,24 @@
         <v>Payment Mode</v>
       </c>
       <c r="L1" t="str">
-        <v>Reference Number</v>
+        <v>Vendor / Payee</v>
       </c>
       <c r="M1" t="str">
-        <v>Vendor / Payee</v>
+        <v>Description</v>
       </c>
       <c r="N1" t="str">
-        <v>Description</v>
+        <v>Legacy Code</v>
       </c>
       <c r="O1" t="str">
-        <v>Legacy Code</v>
+        <v>Is Reversed</v>
       </c>
       <c r="P1" t="str">
-        <v>Is Reversed</v>
+        <v>Reversal Reason</v>
       </c>
       <c r="Q1" t="str">
-        <v>Reversal Reason</v>
+        <v>Created At</v>
       </c>
       <c r="R1" t="str">
-        <v>Created At</v>
-      </c>
-      <c r="S1" t="str">
         <v>Updated At</v>
       </c>
     </row>
@@ -1023,25 +1020,22 @@
       <c r="J3">
         <v>11700</v>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="M3" t="str">
+        <v>Payment of 3 electric meters</v>
       </c>
       <c r="N3" t="str">
-        <v>Payment of 3 electric meters</v>
+        <v>Goe2</v>
       </c>
       <c r="O3" t="str">
-        <v>Goe2</v>
+        <v>No</v>
       </c>
       <c r="P3" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="R3" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="S3" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1076,25 +1070,22 @@
       <c r="J4">
         <v>27000</v>
       </c>
-      <c r="L4" t="str">
-        <v/>
+      <c r="M4" t="str">
+        <v>Returned security deposit</v>
       </c>
       <c r="N4" t="str">
-        <v>Returned security deposit</v>
+        <v>Toe1</v>
       </c>
       <c r="O4" t="str">
-        <v>Toe1</v>
+        <v>No</v>
       </c>
       <c r="P4" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="R4" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="S4" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1129,25 +1120,22 @@
       <c r="J5">
         <v>122000</v>
       </c>
-      <c r="L5" t="str">
-        <v/>
+      <c r="M5" t="str">
+        <v>Byculla club ground rent from April 25 to March 26</v>
       </c>
       <c r="N5" t="str">
-        <v>Byculla club ground rent from April 25 to March 26</v>
+        <v>Bye2</v>
       </c>
       <c r="O5" t="str">
-        <v>Bye2</v>
+        <v>No</v>
       </c>
       <c r="P5" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="R5" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="S5" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1182,25 +1170,22 @@
       <c r="J6">
         <v>3650</v>
       </c>
-      <c r="L6" t="str">
-        <v/>
+      <c r="M6" t="str">
+        <v>Mom treatment medicine</v>
       </c>
       <c r="N6" t="str">
-        <v>Mom treatment medicine</v>
+        <v>R96</v>
       </c>
       <c r="O6" t="str">
-        <v>R96</v>
+        <v>No</v>
       </c>
       <c r="P6" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="R6" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="S6" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1235,25 +1220,22 @@
       <c r="J7">
         <v>810000</v>
       </c>
-      <c r="L7" t="str">
-        <v/>
+      <c r="M7" t="str">
+        <v>Akbar payment (Note: Marked as zakat in source file)</v>
       </c>
       <c r="N7" t="str">
-        <v>Akbar payment (Note: Marked as zakat in source file)</v>
+        <v>Koe3</v>
       </c>
       <c r="O7" t="str">
-        <v>Koe3</v>
+        <v>No</v>
       </c>
       <c r="P7" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="R7" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="S7" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1288,25 +1270,22 @@
       <c r="J8">
         <v>1900000</v>
       </c>
-      <c r="L8" t="str">
-        <v>EXP-REF-777</v>
+      <c r="M8" t="str">
+        <v>Company payment (Note: Marked as zakat in source file)</v>
       </c>
       <c r="N8" t="str">
-        <v>Company payment (Note: Marked as zakat in source file)</v>
+        <v>R51</v>
       </c>
       <c r="O8" t="str">
-        <v>R51</v>
+        <v>No</v>
       </c>
       <c r="P8" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="R8" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="S8" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1341,22 +1320,19 @@
       <c r="J9">
         <v>273535</v>
       </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
+      <c r="M9" t="str">
         <v>Kotak Godaown: Maintainance</v>
       </c>
+      <c r="O9" t="str">
+        <v>No</v>
+      </c>
       <c r="P9" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R9" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S9" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1391,22 +1367,19 @@
       <c r="J10">
         <v>174512</v>
       </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
+      <c r="M10" t="str">
         <v>Kotak Godaown: Rent</v>
       </c>
+      <c r="O10" t="str">
+        <v>No</v>
+      </c>
       <c r="P10" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R10" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S10" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1441,22 +1414,19 @@
       <c r="J11">
         <v>2800</v>
       </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
+      <c r="M11" t="str">
         <v>65 Godown, Barankar,dinesh: Maintainance</v>
       </c>
+      <c r="O11" t="str">
+        <v>No</v>
+      </c>
       <c r="P11" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R11" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S11" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1491,22 +1461,19 @@
       <c r="J12">
         <v>3000</v>
       </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
+      <c r="M12" t="str">
         <v>65 Godown, Barankar,dinesh: Other expenses</v>
       </c>
+      <c r="O12" t="str">
+        <v>No</v>
+      </c>
       <c r="P12" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R12" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S12" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1541,22 +1508,19 @@
       <c r="J13">
         <v>14772</v>
       </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
+      <c r="M13" t="str">
         <v>65 Godown, Barankar,dinesh: Other expenses</v>
       </c>
+      <c r="O13" t="str">
+        <v>No</v>
+      </c>
       <c r="P13" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R13" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S13" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1591,22 +1555,19 @@
       <c r="J14">
         <v>15000</v>
       </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
+      <c r="M14" t="str">
         <v>Garage snip: Electricity</v>
       </c>
+      <c r="O14" t="str">
+        <v>No</v>
+      </c>
       <c r="P14" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R14" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S14" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1641,22 +1602,19 @@
       <c r="J15">
         <v>3000</v>
       </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
+      <c r="M15" t="str">
         <v>Goa Flat: Maintainance</v>
       </c>
+      <c r="O15" t="str">
+        <v>No</v>
+      </c>
       <c r="P15" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R15" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S15" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1691,22 +1649,19 @@
       <c r="J16">
         <v>550000</v>
       </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
+      <c r="M16" t="str">
         <v>Goa Flat: Maintainance</v>
       </c>
+      <c r="O16" t="str">
+        <v>No</v>
+      </c>
       <c r="P16" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R16" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S16" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1741,22 +1696,19 @@
       <c r="J17">
         <v>10000</v>
       </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
+      <c r="M17" t="str">
         <v>Tonys room: maintainance</v>
       </c>
+      <c r="O17" t="str">
+        <v>No</v>
+      </c>
       <c r="P17" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R17" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S17" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1791,22 +1743,19 @@
       <c r="J18">
         <v>10000</v>
       </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
+      <c r="M18" t="str">
         <v>Tonys room: maintainance</v>
       </c>
+      <c r="O18" t="str">
+        <v>No</v>
+      </c>
       <c r="P18" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R18" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S18" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1841,22 +1790,19 @@
       <c r="J19">
         <v>20000</v>
       </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
+      <c r="M19" t="str">
         <v>Tonys room: maintainance</v>
       </c>
+      <c r="O19" t="str">
+        <v>No</v>
+      </c>
       <c r="P19" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R19" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S19" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1891,22 +1837,19 @@
       <c r="J20">
         <v>5000</v>
       </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="N20" t="str">
+      <c r="M20" t="str">
         <v>Tonys room: Other expenses</v>
       </c>
+      <c r="O20" t="str">
+        <v>No</v>
+      </c>
       <c r="P20" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R20" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S20" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1941,22 +1884,19 @@
       <c r="J21">
         <v>96000</v>
       </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
+      <c r="M21" t="str">
         <v>Buyculla club: Rent</v>
       </c>
+      <c r="O21" t="str">
+        <v>No</v>
+      </c>
       <c r="P21" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R21" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S21" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -1991,22 +1931,19 @@
       <c r="J22">
         <v>5500</v>
       </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
+      <c r="M22" t="str">
         <v>Buyculla club: Maitainance</v>
       </c>
+      <c r="O22" t="str">
+        <v>No</v>
+      </c>
       <c r="P22" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R22" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S22" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2041,22 +1978,19 @@
       <c r="J23">
         <v>21500</v>
       </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
+      <c r="M23" t="str">
         <v>Buyculla club: Maitainance</v>
       </c>
+      <c r="O23" t="str">
+        <v>No</v>
+      </c>
       <c r="P23" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R23" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S23" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2091,22 +2025,19 @@
       <c r="J24">
         <v>5000</v>
       </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
+      <c r="M24" t="str">
         <v>Buyculla club: Maitainance</v>
       </c>
+      <c r="O24" t="str">
+        <v>No</v>
+      </c>
       <c r="P24" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q24" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R24" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S24" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2141,22 +2072,19 @@
       <c r="J25">
         <v>19000</v>
       </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
+      <c r="M25" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O25" t="str">
+        <v>No</v>
+      </c>
       <c r="P25" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R25" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S25" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2191,22 +2119,19 @@
       <c r="J26">
         <v>5000</v>
       </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
+      <c r="M26" t="str">
         <v>Other Expenses: Donations</v>
       </c>
+      <c r="O26" t="str">
+        <v>No</v>
+      </c>
       <c r="P26" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q26" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R26" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S26" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2241,22 +2166,19 @@
       <c r="J27">
         <v>8000</v>
       </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
+      <c r="M27" t="str">
         <v>Other Expenses: Donations</v>
       </c>
+      <c r="O27" t="str">
+        <v>No</v>
+      </c>
       <c r="P27" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R27" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S27" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2291,22 +2213,19 @@
       <c r="J28">
         <v>2000</v>
       </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
+      <c r="M28" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O28" t="str">
+        <v>No</v>
+      </c>
       <c r="P28" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R28" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S28" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2341,22 +2260,19 @@
       <c r="J29">
         <v>1600</v>
       </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
+      <c r="M29" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O29" t="str">
+        <v>No</v>
+      </c>
       <c r="P29" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R29" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S29" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2391,22 +2307,19 @@
       <c r="J30">
         <v>6900</v>
       </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
+      <c r="M30" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O30" t="str">
+        <v>No</v>
+      </c>
       <c r="P30" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q30" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R30" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S30" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2441,22 +2354,19 @@
       <c r="J31">
         <v>17000</v>
       </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
+      <c r="M31" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O31" t="str">
+        <v>No</v>
+      </c>
       <c r="P31" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R31" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S31" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2491,22 +2401,19 @@
       <c r="J32">
         <v>16500</v>
       </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
+      <c r="M32" t="str">
         <v>Other Expenses: Margaret</v>
       </c>
+      <c r="O32" t="str">
+        <v>No</v>
+      </c>
       <c r="P32" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q32" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R32" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S32" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2541,22 +2448,19 @@
       <c r="J33">
         <v>16500</v>
       </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
+      <c r="M33" t="str">
         <v>Other Expenses: Margaret</v>
       </c>
+      <c r="O33" t="str">
+        <v>No</v>
+      </c>
       <c r="P33" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q33" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R33" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S33" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2591,22 +2495,19 @@
       <c r="J34">
         <v>16500</v>
       </c>
-      <c r="L34" t="str">
-        <v/>
-      </c>
-      <c r="N34" t="str">
+      <c r="M34" t="str">
         <v>Other Expenses: Margaret</v>
       </c>
+      <c r="O34" t="str">
+        <v>No</v>
+      </c>
       <c r="P34" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R34" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S34" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2641,22 +2542,19 @@
       <c r="J35">
         <v>16500</v>
       </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
+      <c r="M35" t="str">
         <v>Other Expenses: Margaret</v>
       </c>
+      <c r="O35" t="str">
+        <v>No</v>
+      </c>
       <c r="P35" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R35" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S35" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2691,22 +2589,19 @@
       <c r="J36">
         <v>150000</v>
       </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
+      <c r="M36" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O36" t="str">
+        <v>No</v>
+      </c>
       <c r="P36" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q36" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R36" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S36" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2741,22 +2636,19 @@
       <c r="J37">
         <v>8840</v>
       </c>
-      <c r="L37" t="str">
-        <v/>
-      </c>
-      <c r="N37" t="str">
+      <c r="M37" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O37" t="str">
+        <v>No</v>
+      </c>
       <c r="P37" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q37" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R37" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S37" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2791,22 +2683,19 @@
       <c r="J38">
         <v>18500</v>
       </c>
-      <c r="L38" t="str">
-        <v/>
-      </c>
-      <c r="N38" t="str">
+      <c r="M38" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O38" t="str">
+        <v>No</v>
+      </c>
       <c r="P38" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q38" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R38" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S38" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2841,22 +2730,19 @@
       <c r="J39">
         <v>10000</v>
       </c>
-      <c r="L39" t="str">
-        <v/>
-      </c>
-      <c r="N39" t="str">
+      <c r="M39" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O39" t="str">
+        <v>No</v>
+      </c>
       <c r="P39" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q39" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R39" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S39" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2891,22 +2777,19 @@
       <c r="J40">
         <v>30000</v>
       </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
+      <c r="M40" t="str">
         <v>Other Expenses: Micellaneous Expenses</v>
       </c>
+      <c r="O40" t="str">
+        <v>No</v>
+      </c>
       <c r="P40" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q40" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R40" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S40" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2941,22 +2824,19 @@
       <c r="J41">
         <v>46338</v>
       </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
+      <c r="M41" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O41" t="str">
+        <v>No</v>
+      </c>
       <c r="P41" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q41" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R41" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S41" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -2991,22 +2871,19 @@
       <c r="J42">
         <v>700000</v>
       </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
+      <c r="M42" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O42" t="str">
+        <v>No</v>
+      </c>
       <c r="P42" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q42" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R42" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S42" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3041,22 +2918,19 @@
       <c r="J43">
         <v>13001</v>
       </c>
-      <c r="L43" t="str">
-        <v/>
-      </c>
-      <c r="N43" t="str">
+      <c r="M43" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O43" t="str">
+        <v>No</v>
+      </c>
       <c r="P43" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q43" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R43" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S43" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3091,22 +2965,19 @@
       <c r="J44">
         <v>12190</v>
       </c>
-      <c r="L44" t="str">
-        <v/>
-      </c>
-      <c r="N44" t="str">
+      <c r="M44" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O44" t="str">
+        <v>No</v>
+      </c>
       <c r="P44" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q44" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R44" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S44" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3141,22 +3012,19 @@
       <c r="J45">
         <v>7292</v>
       </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
+      <c r="M45" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O45" t="str">
+        <v>No</v>
+      </c>
       <c r="P45" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R45" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S45" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3191,22 +3059,19 @@
       <c r="J46">
         <v>38163</v>
       </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
-      <c r="N46" t="str">
+      <c r="M46" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O46" t="str">
+        <v>No</v>
+      </c>
       <c r="P46" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q46" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R46" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S46" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3241,22 +3106,19 @@
       <c r="J47">
         <v>8620</v>
       </c>
-      <c r="L47" t="str">
-        <v/>
-      </c>
-      <c r="N47" t="str">
+      <c r="M47" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O47" t="str">
+        <v>No</v>
+      </c>
       <c r="P47" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q47" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R47" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S47" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3291,22 +3153,19 @@
       <c r="J48">
         <v>8576</v>
       </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="N48" t="str">
+      <c r="M48" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O48" t="str">
+        <v>No</v>
+      </c>
       <c r="P48" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q48" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R48" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S48" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3341,22 +3200,19 @@
       <c r="J49">
         <v>9720</v>
       </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="N49" t="str">
+      <c r="M49" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O49" t="str">
+        <v>No</v>
+      </c>
       <c r="P49" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q49" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R49" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S49" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3391,22 +3247,19 @@
       <c r="J50">
         <v>10500</v>
       </c>
-      <c r="L50" t="str">
-        <v/>
-      </c>
-      <c r="N50" t="str">
+      <c r="M50" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O50" t="str">
+        <v>No</v>
+      </c>
       <c r="P50" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q50" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R50" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S50" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3441,22 +3294,19 @@
       <c r="J51">
         <v>5330</v>
       </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
+      <c r="M51" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O51" t="str">
+        <v>No</v>
+      </c>
       <c r="P51" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q51" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R51" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S51" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3491,22 +3341,19 @@
       <c r="J52">
         <v>4940</v>
       </c>
-      <c r="L52" t="str">
-        <v/>
-      </c>
-      <c r="N52" t="str">
+      <c r="M52" t="str">
         <v>Other Expenses: Mom</v>
       </c>
+      <c r="O52" t="str">
+        <v>No</v>
+      </c>
       <c r="P52" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q52" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R52" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S52" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3541,22 +3388,19 @@
       <c r="J53">
         <v>1000000</v>
       </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
-      <c r="N53" t="str">
+      <c r="M53" t="str">
         <v>Other Expenses: Islamic &amp; Zakat</v>
       </c>
+      <c r="O53" t="str">
+        <v>No</v>
+      </c>
       <c r="P53" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q53" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R53" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S53" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3591,22 +3435,19 @@
       <c r="J54">
         <v>823000</v>
       </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="N54" t="str">
+      <c r="M54" t="str">
         <v>Other Expenses: Akbar</v>
       </c>
+      <c r="O54" t="str">
+        <v>No</v>
+      </c>
       <c r="P54" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q54" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R54" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S54" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3641,22 +3482,19 @@
       <c r="J55">
         <v>2000000</v>
       </c>
-      <c r="L55" t="str">
-        <v/>
-      </c>
-      <c r="N55" t="str">
+      <c r="M55" t="str">
         <v>Other Expenses: Akbar</v>
       </c>
+      <c r="O55" t="str">
+        <v>No</v>
+      </c>
       <c r="P55" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q55" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R55" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S55" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3691,22 +3529,19 @@
       <c r="J56">
         <v>350000</v>
       </c>
-      <c r="L56" t="str">
-        <v/>
-      </c>
-      <c r="N56" t="str">
+      <c r="M56" t="str">
         <v>Other Expenses: Akbar</v>
       </c>
+      <c r="O56" t="str">
+        <v>No</v>
+      </c>
       <c r="P56" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q56" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R56" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S56" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3741,22 +3576,19 @@
       <c r="J57">
         <v>1500000</v>
       </c>
-      <c r="L57" t="str">
-        <v/>
-      </c>
-      <c r="N57" t="str">
+      <c r="M57" t="str">
         <v>Other Expenses: Loan</v>
       </c>
+      <c r="O57" t="str">
+        <v>No</v>
+      </c>
       <c r="P57" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q57" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R57" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S57" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3791,22 +3623,19 @@
       <c r="J58">
         <v>1400000</v>
       </c>
-      <c r="L58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
+      <c r="M58" t="str">
         <v>Other Expenses: Loan</v>
       </c>
+      <c r="O58" t="str">
+        <v>No</v>
+      </c>
       <c r="P58" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q58" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R58" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S58" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3841,22 +3670,19 @@
       <c r="J59">
         <v>20000</v>
       </c>
-      <c r="L59" t="str">
-        <v/>
-      </c>
-      <c r="N59" t="str">
+      <c r="M59" t="str">
         <v>65 no godown: Maintainance</v>
       </c>
+      <c r="O59" t="str">
+        <v>No</v>
+      </c>
       <c r="P59" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q59" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R59" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S59" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3891,22 +3717,19 @@
       <c r="J60">
         <v>9100</v>
       </c>
-      <c r="L60" t="str">
-        <v/>
-      </c>
-      <c r="N60" t="str">
+      <c r="M60" t="str">
         <v>65 no godown: Maintainance</v>
       </c>
+      <c r="O60" t="str">
+        <v>No</v>
+      </c>
       <c r="P60" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q60" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R60" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S60" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3941,22 +3764,19 @@
       <c r="J61">
         <v>75000</v>
       </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="N61" t="str">
+      <c r="M61" t="str">
         <v>65 no godown: Maintainance</v>
       </c>
+      <c r="O61" t="str">
+        <v>No</v>
+      </c>
       <c r="P61" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q61" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R61" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S61" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -3991,22 +3811,19 @@
       <c r="J62">
         <v>46248</v>
       </c>
-      <c r="L62" t="str">
-        <v/>
-      </c>
-      <c r="N62" t="str">
+      <c r="M62" t="str">
         <v>65 no godown: Maintainance</v>
       </c>
+      <c r="O62" t="str">
+        <v>No</v>
+      </c>
       <c r="P62" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q62" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R62" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S62" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4041,22 +3858,19 @@
       <c r="J63">
         <v>10000</v>
       </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
-      <c r="N63" t="str">
+      <c r="M63" t="str">
         <v>65 no godown: Maintainance</v>
       </c>
+      <c r="O63" t="str">
+        <v>No</v>
+      </c>
       <c r="P63" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q63" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R63" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S63" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4091,22 +3905,19 @@
       <c r="J64">
         <v>14561</v>
       </c>
-      <c r="L64" t="str">
-        <v/>
-      </c>
-      <c r="N64" t="str">
+      <c r="M64" t="str">
         <v>65 no godown: Maintainance</v>
       </c>
+      <c r="O64" t="str">
+        <v>No</v>
+      </c>
       <c r="P64" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q64" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R64" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S64" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4141,22 +3952,19 @@
       <c r="J65">
         <v>41433</v>
       </c>
-      <c r="L65" t="str">
-        <v/>
-      </c>
-      <c r="N65" t="str">
+      <c r="M65" t="str">
         <v>65 no godown: Rent</v>
       </c>
+      <c r="O65" t="str">
+        <v>No</v>
+      </c>
       <c r="P65" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q65" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R65" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S65" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4191,22 +3999,19 @@
       <c r="J66">
         <v>20000</v>
       </c>
-      <c r="L66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
+      <c r="M66" t="str">
         <v>65 no godown: Rent</v>
       </c>
+      <c r="O66" t="str">
+        <v>No</v>
+      </c>
       <c r="P66" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q66" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R66" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S66" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4241,22 +4046,19 @@
       <c r="J67">
         <v>20000</v>
       </c>
-      <c r="L67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
+      <c r="M67" t="str">
         <v>65 no godown: Other expenses</v>
       </c>
+      <c r="O67" t="str">
+        <v>No</v>
+      </c>
       <c r="P67" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q67" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R67" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S67" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4291,22 +4093,19 @@
       <c r="J68">
         <v>177044</v>
       </c>
-      <c r="L68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
+      <c r="M68" t="str">
         <v>Garage: Maintainance</v>
       </c>
+      <c r="O68" t="str">
+        <v>No</v>
+      </c>
       <c r="P68" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q68" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R68" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S68" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4341,22 +4140,19 @@
       <c r="J69">
         <v>20900</v>
       </c>
-      <c r="L69" t="str">
-        <v/>
-      </c>
-      <c r="N69" t="str">
+      <c r="M69" t="str">
         <v>Mani Mansion: Maintainance</v>
       </c>
+      <c r="O69" t="str">
+        <v>No</v>
+      </c>
       <c r="P69" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q69" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R69" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S69" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4391,22 +4187,19 @@
       <c r="J70">
         <v>3698</v>
       </c>
-      <c r="L70" t="str">
-        <v/>
-      </c>
-      <c r="N70" t="str">
+      <c r="M70" t="str">
         <v>Goa Flat: Rent</v>
       </c>
+      <c r="O70" t="str">
+        <v>No</v>
+      </c>
       <c r="P70" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q70" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R70" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S70" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4441,22 +4234,19 @@
       <c r="J71">
         <v>3000</v>
       </c>
-      <c r="L71" t="str">
-        <v/>
-      </c>
-      <c r="N71" t="str">
+      <c r="M71" t="str">
         <v>Byculla Club: Rent</v>
       </c>
+      <c r="O71" t="str">
+        <v>No</v>
+      </c>
       <c r="P71" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q71" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R71" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S71" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4491,22 +4281,19 @@
       <c r="J72">
         <v>9000</v>
       </c>
-      <c r="L72" t="str">
-        <v/>
-      </c>
-      <c r="N72" t="str">
+      <c r="M72" t="str">
         <v>Byculla Club: Maitainance</v>
       </c>
+      <c r="O72" t="str">
+        <v>No</v>
+      </c>
       <c r="P72" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q72" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R72" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S72" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4541,22 +4328,19 @@
       <c r="J73">
         <v>6300</v>
       </c>
-      <c r="L73" t="str">
-        <v/>
-      </c>
-      <c r="N73" t="str">
+      <c r="M73" t="str">
         <v>Micellaneous</v>
       </c>
+      <c r="O73" t="str">
+        <v>No</v>
+      </c>
       <c r="P73" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q73" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R73" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S73" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4591,22 +4375,19 @@
       <c r="J74">
         <v>3000</v>
       </c>
-      <c r="L74" t="str">
-        <v/>
-      </c>
-      <c r="N74" t="str">
+      <c r="M74" t="str">
         <v>Micellaneous</v>
       </c>
+      <c r="O74" t="str">
+        <v>No</v>
+      </c>
       <c r="P74" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q74" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R74" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S74" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4641,22 +4422,19 @@
       <c r="J75">
         <v>16500</v>
       </c>
-      <c r="L75" t="str">
-        <v/>
-      </c>
-      <c r="N75" t="str">
+      <c r="M75" t="str">
         <v>Margaret</v>
       </c>
+      <c r="O75" t="str">
+        <v>No</v>
+      </c>
       <c r="P75" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q75" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R75" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S75" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4691,22 +4469,19 @@
       <c r="J76">
         <v>16500</v>
       </c>
-      <c r="L76" t="str">
-        <v/>
-      </c>
-      <c r="N76" t="str">
+      <c r="M76" t="str">
         <v>Margaret</v>
       </c>
+      <c r="O76" t="str">
+        <v>No</v>
+      </c>
       <c r="P76" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q76" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R76" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S76" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4741,22 +4516,19 @@
       <c r="J77">
         <v>16500</v>
       </c>
-      <c r="L77" t="str">
-        <v/>
-      </c>
-      <c r="N77" t="str">
+      <c r="M77" t="str">
         <v>Margaret</v>
       </c>
+      <c r="O77" t="str">
+        <v>No</v>
+      </c>
       <c r="P77" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q77" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R77" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S77" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4791,22 +4563,19 @@
       <c r="J78">
         <v>600</v>
       </c>
-      <c r="L78" t="str">
-        <v/>
-      </c>
-      <c r="N78" t="str">
+      <c r="M78" t="str">
         <v>Margaret</v>
       </c>
+      <c r="O78" t="str">
+        <v>No</v>
+      </c>
       <c r="P78" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q78" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R78" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S78" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4841,22 +4610,19 @@
       <c r="J79">
         <v>22940</v>
       </c>
-      <c r="L79" t="str">
-        <v/>
-      </c>
-      <c r="N79" t="str">
+      <c r="M79" t="str">
         <v>Micellaneous</v>
       </c>
+      <c r="O79" t="str">
+        <v>No</v>
+      </c>
       <c r="P79" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q79" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R79" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S79" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4891,22 +4657,19 @@
       <c r="J80">
         <v>25300</v>
       </c>
-      <c r="L80" t="str">
-        <v/>
-      </c>
-      <c r="N80" t="str">
+      <c r="M80" t="str">
         <v>Micellaneous</v>
       </c>
+      <c r="O80" t="str">
+        <v>No</v>
+      </c>
       <c r="P80" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q80" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R80" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S80" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4941,22 +4704,19 @@
       <c r="J81">
         <v>30240</v>
       </c>
-      <c r="L81" t="str">
-        <v/>
-      </c>
-      <c r="N81" t="str">
+      <c r="M81" t="str">
         <v>Micellaneous</v>
       </c>
+      <c r="O81" t="str">
+        <v>No</v>
+      </c>
       <c r="P81" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q81" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R81" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S81" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -4991,22 +4751,19 @@
       <c r="J82">
         <v>4800</v>
       </c>
-      <c r="L82" t="str">
-        <v/>
-      </c>
-      <c r="N82" t="str">
+      <c r="M82" t="str">
         <v>Micellaneous</v>
       </c>
+      <c r="O82" t="str">
+        <v>No</v>
+      </c>
       <c r="P82" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q82" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R82" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S82" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5041,22 +4798,19 @@
       <c r="J83">
         <v>179283.26</v>
       </c>
-      <c r="L83" t="str">
-        <v/>
-      </c>
-      <c r="N83" t="str">
+      <c r="M83" t="str">
         <v>Mom</v>
       </c>
+      <c r="O83" t="str">
+        <v>No</v>
+      </c>
       <c r="P83" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q83" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R83" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S83" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5091,22 +4845,19 @@
       <c r="J84">
         <v>20000</v>
       </c>
-      <c r="L84" t="str">
-        <v/>
-      </c>
-      <c r="N84" t="str">
+      <c r="M84" t="str">
         <v>Mom</v>
       </c>
+      <c r="O84" t="str">
+        <v>No</v>
+      </c>
       <c r="P84" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q84" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R84" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S84" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5141,22 +4892,19 @@
       <c r="J85">
         <v>400</v>
       </c>
-      <c r="L85" t="str">
-        <v/>
-      </c>
-      <c r="N85" t="str">
+      <c r="M85" t="str">
         <v>Mom</v>
       </c>
+      <c r="O85" t="str">
+        <v>No</v>
+      </c>
       <c r="P85" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q85" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R85" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S85" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5191,22 +4939,19 @@
       <c r="J86">
         <v>4770</v>
       </c>
-      <c r="L86" t="str">
-        <v/>
-      </c>
-      <c r="N86" t="str">
+      <c r="M86" t="str">
         <v>Mom</v>
       </c>
+      <c r="O86" t="str">
+        <v>No</v>
+      </c>
       <c r="P86" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q86" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R86" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S86" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5241,22 +4986,19 @@
       <c r="J87">
         <v>2030000</v>
       </c>
-      <c r="L87" t="str">
-        <v/>
-      </c>
-      <c r="N87" t="str">
+      <c r="M87" t="str">
         <v>Islamic &amp; Zakat</v>
       </c>
+      <c r="O87" t="str">
+        <v>No</v>
+      </c>
       <c r="P87" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q87" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R87" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S87" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5291,22 +5033,19 @@
       <c r="J88">
         <v>2600000</v>
       </c>
-      <c r="L88" t="str">
-        <v/>
-      </c>
-      <c r="N88" t="str">
+      <c r="M88" t="str">
         <v>Send to dubai</v>
       </c>
+      <c r="O88" t="str">
+        <v>No</v>
+      </c>
       <c r="P88" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q88" t="str">
-        <v/>
+        <v>24/10/2026</v>
       </c>
       <c r="R88" t="str">
-        <v>24/10/2026</v>
-      </c>
-      <c r="S88" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5341,22 +5080,19 @@
       <c r="J89">
         <v>4800</v>
       </c>
-      <c r="L89" t="str">
-        <v/>
-      </c>
-      <c r="N89" t="str">
+      <c r="M89" t="str">
         <v>FY23 Summary: 65 Godown - Maintenance for 2023-04</v>
       </c>
+      <c r="O89" t="str">
+        <v>No</v>
+      </c>
       <c r="P89" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q89" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R89" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S89" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5391,22 +5127,19 @@
       <c r="J90">
         <v>2100</v>
       </c>
-      <c r="L90" t="str">
-        <v/>
-      </c>
-      <c r="N90" t="str">
+      <c r="M90" t="str">
         <v>FY23 Summary: 65 Godown - Rent for 2023-10</v>
       </c>
+      <c r="O90" t="str">
+        <v>No</v>
+      </c>
       <c r="P90" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q90" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R90" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S90" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5441,22 +5174,19 @@
       <c r="J91">
         <v>2800</v>
       </c>
-      <c r="L91" t="str">
-        <v/>
-      </c>
-      <c r="N91" t="str">
+      <c r="M91" t="str">
         <v>FY23 Summary: 65 Godown - Other expenses for 2023-09</v>
       </c>
+      <c r="O91" t="str">
+        <v>No</v>
+      </c>
       <c r="P91" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q91" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R91" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S91" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5491,22 +5221,19 @@
       <c r="J92">
         <v>184068</v>
       </c>
-      <c r="L92" t="str">
-        <v/>
-      </c>
-      <c r="N92" t="str">
+      <c r="M92" t="str">
         <v>FY23 Summary: Garage - Rent for 2023-09</v>
       </c>
+      <c r="O92" t="str">
+        <v>No</v>
+      </c>
       <c r="P92" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q92" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R92" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S92" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5541,22 +5268,19 @@
       <c r="J93">
         <v>50000</v>
       </c>
-      <c r="L93" t="str">
-        <v/>
-      </c>
-      <c r="N93" t="str">
+      <c r="M93" t="str">
         <v>FY23 Summary: Garage - Other expenses for 2023-12</v>
       </c>
+      <c r="O93" t="str">
+        <v>No</v>
+      </c>
       <c r="P93" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q93" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R93" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S93" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5591,22 +5315,19 @@
       <c r="J94">
         <v>2500</v>
       </c>
-      <c r="L94" t="str">
-        <v/>
-      </c>
-      <c r="N94" t="str">
+      <c r="M94" t="str">
         <v>FY23 Summary: Ennas Room - Rent for 2023-05</v>
       </c>
+      <c r="O94" t="str">
+        <v>No</v>
+      </c>
       <c r="P94" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q94" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R94" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S94" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5641,22 +5362,19 @@
       <c r="J95">
         <v>33000</v>
       </c>
-      <c r="L95" t="str">
-        <v/>
-      </c>
-      <c r="N95" t="str">
+      <c r="M95" t="str">
         <v>FY23 Summary: Mani Mansion - Maintenance for 2023-10</v>
       </c>
+      <c r="O95" t="str">
+        <v>No</v>
+      </c>
       <c r="P95" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q95" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R95" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S95" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5691,22 +5409,19 @@
       <c r="J96">
         <v>7500</v>
       </c>
-      <c r="L96" t="str">
-        <v/>
-      </c>
-      <c r="N96" t="str">
+      <c r="M96" t="str">
         <v>FY23 Summary: Mani Mansion - Other expenses for 2023-12</v>
       </c>
+      <c r="O96" t="str">
+        <v>No</v>
+      </c>
       <c r="P96" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q96" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R96" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S96" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5741,22 +5456,19 @@
       <c r="J97">
         <v>7000</v>
       </c>
-      <c r="L97" t="str">
-        <v/>
-      </c>
-      <c r="N97" t="str">
+      <c r="M97" t="str">
         <v>FY23 Summary: Goa Flat - Electricity for 2023-04</v>
       </c>
+      <c r="O97" t="str">
+        <v>No</v>
+      </c>
       <c r="P97" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q97" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R97" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S97" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5791,22 +5503,19 @@
       <c r="J98">
         <v>1338</v>
       </c>
-      <c r="L98" t="str">
-        <v/>
-      </c>
-      <c r="N98" t="str">
+      <c r="M98" t="str">
         <v>FY23 Summary: Tonys room - Maintenance for 2023-12</v>
       </c>
+      <c r="O98" t="str">
+        <v>No</v>
+      </c>
       <c r="P98" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q98" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R98" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S98" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5841,22 +5550,19 @@
       <c r="J99">
         <v>96940</v>
       </c>
-      <c r="L99" t="str">
-        <v/>
-      </c>
-      <c r="N99" t="str">
+      <c r="M99" t="str">
         <v>FY23 Summary: Byculla Club - Rent for 2023-04</v>
       </c>
+      <c r="O99" t="str">
+        <v>No</v>
+      </c>
       <c r="P99" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q99" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R99" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S99" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5891,22 +5597,19 @@
       <c r="J100">
         <v>11000</v>
       </c>
-      <c r="L100" t="str">
-        <v/>
-      </c>
-      <c r="N100" t="str">
+      <c r="M100" t="str">
         <v>FY23 Summary: Byculla Club - Maintenance Sep for 2023-09</v>
       </c>
+      <c r="O100" t="str">
+        <v>No</v>
+      </c>
       <c r="P100" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q100" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R100" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S100" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5941,22 +5644,19 @@
       <c r="J101">
         <v>2500</v>
       </c>
-      <c r="L101" t="str">
-        <v/>
-      </c>
-      <c r="N101" t="str">
+      <c r="M101" t="str">
         <v>FY23 Summary: Byculla Club - Maintenance Dec for 2023-12</v>
       </c>
+      <c r="O101" t="str">
+        <v>No</v>
+      </c>
       <c r="P101" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q101" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R101" t="str">
-        <v>25/10/2026</v>
-      </c>
-      <c r="S101" t="str">
         <v>25/10/2026</v>
       </c>
     </row>
@@ -5991,28 +5691,25 @@
       <c r="J102">
         <v>4600</v>
       </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="N102" t="str">
+      <c r="M102" t="str">
         <v>FY23 Summary: Misscellanous exp for 2023-12</v>
       </c>
+      <c r="O102" t="str">
+        <v>No</v>
+      </c>
       <c r="P102" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="Q102" t="str">
-        <v/>
+        <v>25/10/2026</v>
       </c>
       <c r="R102" t="str">
         <v>25/10/2026</v>
       </c>
-      <c r="S102" t="str">
-        <v>25/10/2026</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R102"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9195,16 +8892,16 @@
         <v>3399918.74</v>
       </c>
       <c r="D91">
-        <v>3187426</v>
+        <v>3262426</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>3187426</v>
+        <v>3262426</v>
       </c>
       <c r="G91">
-        <v>6587344.74</v>
+        <v>6662344.74</v>
       </c>
       <c r="H91" t="str">
         <v>Yes</v>
@@ -52324,7 +52021,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:P102"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -52377,30 +52074,27 @@
         <v>Payment Mode</v>
       </c>
       <c r="K1" t="str">
-        <v>Reference Number</v>
+        <v>Bank Name</v>
       </c>
       <c r="L1" t="str">
-        <v>Bank Name</v>
+        <v>Comments</v>
       </c>
       <c r="M1" t="str">
-        <v>Comments</v>
+        <v>Is Reversed</v>
       </c>
       <c r="N1" t="str">
-        <v>Is Reversed</v>
+        <v>Reversal Reason</v>
       </c>
       <c r="O1" t="str">
-        <v>Reversal Reason</v>
+        <v>Created At</v>
       </c>
       <c r="P1" t="str">
-        <v>Created At</v>
-      </c>
-      <c r="Q1" t="str">
         <v>Updated At</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 700 total records]</v>
+        <v>[Showing 100 of 701 total records]</v>
       </c>
     </row>
     <row r="3">
@@ -52431,22 +52125,19 @@
       <c r="I3">
         <v>75000</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
+      <c r="L3" t="str">
+        <v>Imported from MAR26 sheet: Paid till Mar 26</v>
       </c>
       <c r="M3" t="str">
-        <v>Imported from MAR26 sheet: Paid till Mar 26</v>
+        <v>No</v>
       </c>
       <c r="N3" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P3" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q3" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52478,22 +52169,19 @@
       <c r="I4">
         <v>32000</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
+      <c r="L4" t="str">
+        <v>Imported from MAR26 sheet: Paid Mar 26</v>
       </c>
       <c r="M4" t="str">
-        <v>Imported from MAR26 sheet: Paid Mar 26</v>
+        <v>No</v>
       </c>
       <c r="N4" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P4" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q4" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52525,22 +52213,19 @@
       <c r="I5">
         <v>22000</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
+      <c r="L5" t="str">
+        <v>Rent collection for Nov 2025</v>
       </c>
       <c r="M5" t="str">
-        <v>Rent collection for Nov 2025</v>
+        <v>No</v>
       </c>
       <c r="N5" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P5" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q5" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52572,22 +52257,19 @@
       <c r="I6">
         <v>15000</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
+      <c r="L6" t="str">
+        <v>Imported from MAR26 sheet: Paid Mar 26</v>
       </c>
       <c r="M6" t="str">
-        <v>Imported from MAR26 sheet: Paid Mar 26</v>
+        <v>No</v>
       </c>
       <c r="N6" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P6" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q6" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52619,22 +52301,19 @@
       <c r="I7">
         <v>10000</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
+      <c r="L7" t="str">
+        <v>Imported from MAR26 sheet: Paid till Mar 26 (she left)</v>
       </c>
       <c r="M7" t="str">
-        <v>Imported from MAR26 sheet: Paid till Mar 26 (she left)</v>
+        <v>No</v>
       </c>
       <c r="N7" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P7" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q7" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52666,22 +52345,19 @@
       <c r="I8">
         <v>40000</v>
       </c>
-      <c r="K8" t="str">
-        <v/>
+      <c r="L8" t="str">
+        <v>Imported from MAR26 sheet: Monthly cheque portion</v>
       </c>
       <c r="M8" t="str">
-        <v>Imported from MAR26 sheet: Monthly cheque portion</v>
+        <v>No</v>
       </c>
       <c r="N8" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P8" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q8" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52713,22 +52389,19 @@
       <c r="I9">
         <v>12000</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
+      <c r="L9" t="str">
+        <v>Imported from MAR26 sheet: Pd Feb 26</v>
       </c>
       <c r="M9" t="str">
-        <v>Imported from MAR26 sheet: Pd Feb 26</v>
+        <v>No</v>
       </c>
       <c r="N9" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O9" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P9" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q9" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52760,22 +52433,19 @@
       <c r="I10">
         <v>12000</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
+      <c r="L10" t="str">
+        <v>Imported from MAR26 sheet: Pd Feb 26</v>
       </c>
       <c r="M10" t="str">
-        <v>Imported from MAR26 sheet: Pd Feb 26</v>
+        <v>No</v>
       </c>
       <c r="N10" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P10" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q10" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52807,22 +52477,19 @@
       <c r="I11">
         <v>22000</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
+      <c r="L11" t="str">
+        <v>Imported from MAR26 sheet: Paid Mar 26</v>
       </c>
       <c r="M11" t="str">
-        <v>Imported from MAR26 sheet: Paid Mar 26</v>
+        <v>No</v>
       </c>
       <c r="N11" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O11" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P11" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q11" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52854,22 +52521,19 @@
       <c r="I12">
         <v>81561</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
+      <c r="L12" t="str">
+        <v>Kotak PG Rent</v>
       </c>
       <c r="M12" t="str">
-        <v>Kotak PG Rent</v>
+        <v>No</v>
       </c>
       <c r="N12" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P12" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q12" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52901,22 +52565,19 @@
       <c r="I13">
         <v>110462</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
+      <c r="L13" t="str">
+        <v>Kotak PG Rent</v>
       </c>
       <c r="M13" t="str">
-        <v>Kotak PG Rent</v>
+        <v>No</v>
       </c>
       <c r="N13" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P13" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q13" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52948,22 +52609,19 @@
       <c r="I14">
         <v>225573</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
+      <c r="L14" t="str">
+        <v>Kotak PG Rent</v>
       </c>
       <c r="M14" t="str">
-        <v>Kotak PG Rent</v>
+        <v>No</v>
       </c>
       <c r="N14" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P14" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q14" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -52995,22 +52653,19 @@
       <c r="I15">
         <v>79452</v>
       </c>
-      <c r="K15" t="str">
-        <v/>
+      <c r="L15" t="str">
+        <v>Kotak PG Rent</v>
       </c>
       <c r="M15" t="str">
-        <v>Kotak PG Rent</v>
+        <v>No</v>
       </c>
       <c r="N15" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P15" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q15" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53042,22 +52697,19 @@
       <c r="I16">
         <v>200000</v>
       </c>
-      <c r="K16" t="str">
-        <v/>
+      <c r="L16" t="str">
+        <v>Kotak PG Rent</v>
       </c>
       <c r="M16" t="str">
-        <v>Kotak PG Rent</v>
+        <v>No</v>
       </c>
       <c r="N16" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P16" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q16" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53089,22 +52741,19 @@
       <c r="I17">
         <v>179576</v>
       </c>
-      <c r="K17" t="str">
-        <v/>
+      <c r="L17" t="str">
+        <v>Kotak PG Rent</v>
       </c>
       <c r="M17" t="str">
-        <v>Kotak PG Rent</v>
+        <v>No</v>
       </c>
       <c r="N17" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P17" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q17" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53136,22 +52785,19 @@
       <c r="I18">
         <v>20250</v>
       </c>
-      <c r="K18" t="str">
-        <v/>
+      <c r="L18" t="str">
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="M18" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>No</v>
       </c>
       <c r="N18" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P18" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q18" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53183,22 +52829,19 @@
       <c r="I19">
         <v>20250</v>
       </c>
-      <c r="K19" t="str">
-        <v/>
+      <c r="L19" t="str">
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="M19" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>No</v>
       </c>
       <c r="N19" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P19" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q19" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53230,22 +52873,19 @@
       <c r="I20">
         <v>60750</v>
       </c>
-      <c r="K20" t="str">
-        <v/>
+      <c r="L20" t="str">
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="M20" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>No</v>
       </c>
       <c r="N20" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P20" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q20" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53277,22 +52917,19 @@
       <c r="I21">
         <v>20250</v>
       </c>
-      <c r="K21" t="str">
-        <v/>
+      <c r="L21" t="str">
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="M21" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>No</v>
       </c>
       <c r="N21" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P21" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q21" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53324,22 +52961,19 @@
       <c r="I22">
         <v>60750</v>
       </c>
-      <c r="K22" t="str">
-        <v/>
+      <c r="L22" t="str">
+        <v>Small Godown Water Wala</v>
       </c>
       <c r="M22" t="str">
-        <v>Small Godown Water Wala</v>
+        <v>No</v>
       </c>
       <c r="N22" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O22" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P22" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q22" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53371,22 +53005,19 @@
       <c r="I23">
         <v>100000</v>
       </c>
-      <c r="K23" t="str">
-        <v/>
+      <c r="L23" t="str">
+        <v>65 Large Godown Mahendra Bhai</v>
       </c>
       <c r="M23" t="str">
-        <v>65 Large Godown Mahendra Bhai</v>
+        <v>No</v>
       </c>
       <c r="N23" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O23" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P23" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q23" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53418,22 +53049,19 @@
       <c r="I24">
         <v>100000</v>
       </c>
-      <c r="K24" t="str">
-        <v/>
+      <c r="L24" t="str">
+        <v>65 Large Godown Mahendra Bhai</v>
       </c>
       <c r="M24" t="str">
-        <v>65 Large Godown Mahendra Bhai</v>
+        <v>No</v>
       </c>
       <c r="N24" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O24" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P24" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q24" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53465,22 +53093,19 @@
       <c r="I25">
         <v>100000</v>
       </c>
-      <c r="K25" t="str">
-        <v/>
+      <c r="L25" t="str">
+        <v>65 Large Godown Mahendra Bhai</v>
       </c>
       <c r="M25" t="str">
-        <v>65 Large Godown Mahendra Bhai</v>
+        <v>No</v>
       </c>
       <c r="N25" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O25" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P25" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q25" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53512,22 +53137,19 @@
       <c r="I26">
         <v>100000</v>
       </c>
-      <c r="K26" t="str">
-        <v/>
+      <c r="L26" t="str">
+        <v>65 Large Godown Mahendra Bhai</v>
       </c>
       <c r="M26" t="str">
-        <v>65 Large Godown Mahendra Bhai</v>
+        <v>No</v>
       </c>
       <c r="N26" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O26" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P26" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q26" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53559,22 +53181,19 @@
       <c r="I27">
         <v>41000</v>
       </c>
-      <c r="K27" t="str">
-        <v/>
+      <c r="L27" t="str">
+        <v>65 Small Godown Alka Industry</v>
       </c>
       <c r="M27" t="str">
-        <v>65 Small Godown Alka Industry</v>
+        <v>No</v>
       </c>
       <c r="N27" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O27" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P27" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q27" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53606,22 +53225,19 @@
       <c r="I28">
         <v>25000</v>
       </c>
-      <c r="K28" t="str">
-        <v/>
+      <c r="L28" t="str">
+        <v>65 Small Godown Alka Industry</v>
       </c>
       <c r="M28" t="str">
-        <v>65 Small Godown Alka Industry</v>
+        <v>No</v>
       </c>
       <c r="N28" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O28" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P28" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q28" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53653,22 +53269,19 @@
       <c r="I29">
         <v>20000</v>
       </c>
-      <c r="K29" t="str">
-        <v/>
+      <c r="L29" t="str">
+        <v>Baranker room direct receipt</v>
       </c>
       <c r="M29" t="str">
-        <v>Baranker room direct receipt</v>
+        <v>No</v>
       </c>
       <c r="N29" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O29" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P29" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q29" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53700,22 +53313,19 @@
       <c r="I30">
         <v>1650</v>
       </c>
-      <c r="K30" t="str">
-        <v/>
+      <c r="L30" t="str">
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="M30" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>No</v>
       </c>
       <c r="N30" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O30" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P30" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q30" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53747,22 +53357,19 @@
       <c r="I31">
         <v>16500</v>
       </c>
-      <c r="K31" t="str">
-        <v/>
+      <c r="L31" t="str">
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="M31" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>No</v>
       </c>
       <c r="N31" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O31" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P31" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q31" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53794,22 +53401,19 @@
       <c r="I32">
         <v>16500</v>
       </c>
-      <c r="K32" t="str">
-        <v/>
+      <c r="L32" t="str">
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="M32" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>No</v>
       </c>
       <c r="N32" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O32" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P32" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q32" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53841,22 +53445,19 @@
       <c r="I33">
         <v>16500</v>
       </c>
-      <c r="K33" t="str">
-        <v/>
+      <c r="L33" t="str">
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="M33" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>No</v>
       </c>
       <c r="N33" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O33" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P33" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q33" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53888,22 +53489,19 @@
       <c r="I34">
         <v>11000</v>
       </c>
-      <c r="K34" t="str">
-        <v/>
+      <c r="L34" t="str">
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="M34" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>No</v>
       </c>
       <c r="N34" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O34" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P34" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q34" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53935,22 +53533,19 @@
       <c r="I35">
         <v>5500</v>
       </c>
-      <c r="K35" t="str">
-        <v/>
+      <c r="L35" t="str">
+        <v>Baranker Mezzanine Uttam</v>
       </c>
       <c r="M35" t="str">
-        <v>Baranker Mezzanine Uttam</v>
+        <v>No</v>
       </c>
       <c r="N35" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O35" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P35" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q35" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -53982,22 +53577,19 @@
       <c r="I36">
         <v>7000</v>
       </c>
-      <c r="K36" t="str">
-        <v/>
+      <c r="L36" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M36" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N36" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O36" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P36" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q36" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54029,22 +53621,19 @@
       <c r="I37">
         <v>7000</v>
       </c>
-      <c r="K37" t="str">
-        <v/>
+      <c r="L37" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M37" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N37" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O37" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P37" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q37" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54076,22 +53665,19 @@
       <c r="I38">
         <v>7000</v>
       </c>
-      <c r="K38" t="str">
-        <v/>
+      <c r="L38" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M38" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N38" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O38" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P38" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q38" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54123,22 +53709,19 @@
       <c r="I39">
         <v>7000</v>
       </c>
-      <c r="K39" t="str">
-        <v/>
+      <c r="L39" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M39" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N39" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O39" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P39" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q39" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54170,22 +53753,19 @@
       <c r="I40">
         <v>7000</v>
       </c>
-      <c r="K40" t="str">
-        <v/>
+      <c r="L40" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M40" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N40" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O40" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P40" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q40" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54217,22 +53797,19 @@
       <c r="I41">
         <v>7000</v>
       </c>
-      <c r="K41" t="str">
-        <v/>
+      <c r="L41" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M41" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N41" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O41" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P41" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q41" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54264,22 +53841,19 @@
       <c r="I42">
         <v>7000</v>
       </c>
-      <c r="K42" t="str">
-        <v/>
+      <c r="L42" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M42" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N42" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O42" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P42" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q42" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54311,22 +53885,19 @@
       <c r="I43">
         <v>7000</v>
       </c>
-      <c r="K43" t="str">
-        <v/>
+      <c r="L43" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M43" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N43" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O43" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P43" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q43" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54358,22 +53929,19 @@
       <c r="I44">
         <v>7000</v>
       </c>
-      <c r="K44" t="str">
-        <v/>
+      <c r="L44" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M44" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N44" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O44" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P44" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q44" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54405,22 +53973,19 @@
       <c r="I45">
         <v>7000</v>
       </c>
-      <c r="K45" t="str">
-        <v/>
+      <c r="L45" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M45" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N45" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O45" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P45" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q45" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54452,22 +54017,19 @@
       <c r="I46">
         <v>7000</v>
       </c>
-      <c r="K46" t="str">
-        <v/>
+      <c r="L46" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M46" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N46" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O46" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P46" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q46" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54499,22 +54061,19 @@
       <c r="I47">
         <v>7000</v>
       </c>
-      <c r="K47" t="str">
-        <v/>
+      <c r="L47" t="str">
+        <v>1st Floor Anjana Ashok Salunke</v>
       </c>
       <c r="M47" t="str">
-        <v>1st Floor Anjana Ashok Salunke</v>
+        <v>No</v>
       </c>
       <c r="N47" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O47" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P47" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q47" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54546,22 +54105,19 @@
       <c r="I48">
         <v>10000</v>
       </c>
-      <c r="K48" t="str">
-        <v/>
+      <c r="L48" t="str">
+        <v>Room 10 Santosh</v>
       </c>
       <c r="M48" t="str">
-        <v>Room 10 Santosh</v>
+        <v>No</v>
       </c>
       <c r="N48" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O48" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P48" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q48" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54593,22 +54149,19 @@
       <c r="I49">
         <v>10000</v>
       </c>
-      <c r="K49" t="str">
-        <v/>
+      <c r="L49" t="str">
+        <v>Room 10 Santosh</v>
       </c>
       <c r="M49" t="str">
-        <v>Room 10 Santosh</v>
+        <v>No</v>
       </c>
       <c r="N49" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O49" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P49" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q49" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54640,22 +54193,19 @@
       <c r="I50">
         <v>10000</v>
       </c>
-      <c r="K50" t="str">
-        <v/>
+      <c r="L50" t="str">
+        <v>Room 10 Santosh</v>
       </c>
       <c r="M50" t="str">
-        <v>Room 10 Santosh</v>
+        <v>No</v>
       </c>
       <c r="N50" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O50" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P50" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q50" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54687,22 +54237,19 @@
       <c r="I51">
         <v>10000</v>
       </c>
-      <c r="K51" t="str">
-        <v/>
+      <c r="L51" t="str">
+        <v>Room 10 Santosh</v>
       </c>
       <c r="M51" t="str">
-        <v>Room 10 Santosh</v>
+        <v>No</v>
       </c>
       <c r="N51" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O51" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P51" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q51" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54734,22 +54281,19 @@
       <c r="I52">
         <v>10000</v>
       </c>
-      <c r="K52" t="str">
-        <v/>
+      <c r="L52" t="str">
+        <v>Room 10 Santosh</v>
       </c>
       <c r="M52" t="str">
-        <v>Room 10 Santosh</v>
+        <v>No</v>
       </c>
       <c r="N52" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O52" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P52" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q52" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54781,22 +54325,19 @@
       <c r="I53">
         <v>40000</v>
       </c>
-      <c r="K53" t="str">
-        <v/>
+      <c r="L53" t="str">
+        <v>Room 10 Kamlesh (4 months rent)</v>
       </c>
       <c r="M53" t="str">
-        <v>Room 10 Kamlesh (4 months rent)</v>
+        <v>No</v>
       </c>
       <c r="N53" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O53" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P53" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q53" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54828,22 +54369,19 @@
       <c r="I54">
         <v>10000</v>
       </c>
-      <c r="K54" t="str">
-        <v/>
+      <c r="L54" t="str">
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="M54" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>No</v>
       </c>
       <c r="N54" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O54" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P54" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q54" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54875,22 +54413,19 @@
       <c r="I55">
         <v>10000</v>
       </c>
-      <c r="K55" t="str">
-        <v/>
+      <c r="L55" t="str">
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="M55" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>No</v>
       </c>
       <c r="N55" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O55" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P55" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q55" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54922,22 +54457,19 @@
       <c r="I56">
         <v>10000</v>
       </c>
-      <c r="K56" t="str">
-        <v/>
+      <c r="L56" t="str">
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="M56" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>No</v>
       </c>
       <c r="N56" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O56" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P56" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q56" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -54969,22 +54501,19 @@
       <c r="I57">
         <v>10000</v>
       </c>
-      <c r="K57" t="str">
-        <v/>
+      <c r="L57" t="str">
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="M57" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>No</v>
       </c>
       <c r="N57" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O57" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P57" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q57" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55016,22 +54545,19 @@
       <c r="I58">
         <v>10000</v>
       </c>
-      <c r="K58" t="str">
-        <v/>
+      <c r="L58" t="str">
+        <v>Room 10 Kamlesh</v>
       </c>
       <c r="M58" t="str">
-        <v>Room 10 Kamlesh</v>
+        <v>No</v>
       </c>
       <c r="N58" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O58" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P58" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q58" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55063,22 +54589,19 @@
       <c r="I59">
         <v>30000</v>
       </c>
-      <c r="K59" t="str">
-        <v/>
+      <c r="L59" t="str">
+        <v>Garage commercial rent</v>
       </c>
       <c r="M59" t="str">
-        <v>Garage commercial rent</v>
+        <v>No</v>
       </c>
       <c r="N59" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O59" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P59" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q59" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55110,22 +54633,19 @@
       <c r="I60">
         <v>30000</v>
       </c>
-      <c r="K60" t="str">
-        <v/>
+      <c r="L60" t="str">
+        <v>Garage commercial rent</v>
       </c>
       <c r="M60" t="str">
-        <v>Garage commercial rent</v>
+        <v>No</v>
       </c>
       <c r="N60" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O60" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P60" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q60" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55157,22 +54677,19 @@
       <c r="I61">
         <v>30000</v>
       </c>
-      <c r="K61" t="str">
-        <v/>
+      <c r="L61" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M61" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N61" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O61" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P61" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q61" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55204,22 +54721,19 @@
       <c r="I62">
         <v>30000</v>
       </c>
-      <c r="K62" t="str">
-        <v/>
+      <c r="L62" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M62" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N62" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O62" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P62" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q62" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55251,22 +54765,19 @@
       <c r="I63">
         <v>30000</v>
       </c>
-      <c r="K63" t="str">
-        <v/>
+      <c r="L63" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M63" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N63" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O63" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P63" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q63" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55298,22 +54809,19 @@
       <c r="I64">
         <v>30000</v>
       </c>
-      <c r="K64" t="str">
-        <v/>
+      <c r="L64" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M64" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N64" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O64" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P64" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q64" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55345,22 +54853,19 @@
       <c r="I65">
         <v>30000</v>
       </c>
-      <c r="K65" t="str">
-        <v/>
+      <c r="L65" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M65" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N65" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O65" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P65" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q65" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55392,22 +54897,19 @@
       <c r="I66">
         <v>30000</v>
       </c>
-      <c r="K66" t="str">
-        <v/>
+      <c r="L66" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M66" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N66" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O66" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P66" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q66" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55439,22 +54941,19 @@
       <c r="I67">
         <v>30000</v>
       </c>
-      <c r="K67" t="str">
-        <v/>
+      <c r="L67" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M67" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N67" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O67" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P67" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q67" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55486,22 +54985,19 @@
       <c r="I68">
         <v>30000</v>
       </c>
-      <c r="K68" t="str">
-        <v/>
+      <c r="L68" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M68" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N68" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O68" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P68" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q68" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55533,22 +55029,19 @@
       <c r="I69">
         <v>30000</v>
       </c>
-      <c r="K69" t="str">
-        <v/>
+      <c r="L69" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M69" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N69" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O69" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P69" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q69" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55580,22 +55073,19 @@
       <c r="I70">
         <v>30000</v>
       </c>
-      <c r="K70" t="str">
-        <v/>
+      <c r="L70" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M70" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N70" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O70" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P70" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q70" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55627,22 +55117,19 @@
       <c r="I71">
         <v>30000</v>
       </c>
-      <c r="K71" t="str">
-        <v/>
+      <c r="L71" t="str">
+        <v>Shop 2 Snip Salon</v>
       </c>
       <c r="M71" t="str">
-        <v>Shop 2 Snip Salon</v>
+        <v>No</v>
       </c>
       <c r="N71" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O71" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P71" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q71" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55674,22 +55161,19 @@
       <c r="I72">
         <v>30000</v>
       </c>
-      <c r="K72" t="str">
-        <v/>
+      <c r="L72" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M72" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N72" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O72" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P72" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q72" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55721,22 +55205,19 @@
       <c r="I73">
         <v>30000</v>
       </c>
-      <c r="K73" t="str">
-        <v/>
+      <c r="L73" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M73" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N73" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O73" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P73" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q73" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55768,22 +55249,19 @@
       <c r="I74">
         <v>30000</v>
       </c>
-      <c r="K74" t="str">
-        <v/>
+      <c r="L74" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M74" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N74" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O74" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P74" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q74" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55815,22 +55293,19 @@
       <c r="I75">
         <v>60000</v>
       </c>
-      <c r="K75" t="str">
-        <v/>
+      <c r="L75" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M75" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N75" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O75" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P75" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q75" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55862,22 +55337,19 @@
       <c r="I76">
         <v>60000</v>
       </c>
-      <c r="K76" t="str">
-        <v/>
+      <c r="L76" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M76" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N76" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O76" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P76" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q76" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55909,22 +55381,19 @@
       <c r="I77">
         <v>35000</v>
       </c>
-      <c r="K77" t="str">
-        <v/>
+      <c r="L77" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M77" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N77" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O77" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P77" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q77" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -55956,22 +55425,19 @@
       <c r="I78">
         <v>35000</v>
       </c>
-      <c r="K78" t="str">
-        <v/>
+      <c r="L78" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M78" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N78" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O78" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P78" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q78" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56003,22 +55469,19 @@
       <c r="I79">
         <v>70000</v>
       </c>
-      <c r="K79" t="str">
-        <v/>
+      <c r="L79" t="str">
+        <v>Shop 1 DG Cable</v>
       </c>
       <c r="M79" t="str">
-        <v>Shop 1 DG Cable</v>
+        <v>No</v>
       </c>
       <c r="N79" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O79" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P79" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q79" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56050,22 +55513,19 @@
       <c r="I80">
         <v>10000</v>
       </c>
-      <c r="K80" t="str">
-        <v/>
+      <c r="L80" t="str">
+        <v>Godown Anand</v>
       </c>
       <c r="M80" t="str">
-        <v>Godown Anand</v>
+        <v>No</v>
       </c>
       <c r="N80" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O80" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P80" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q80" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56097,22 +55557,19 @@
       <c r="I81">
         <v>10000</v>
       </c>
-      <c r="K81" t="str">
-        <v/>
+      <c r="L81" t="str">
+        <v>Godown Anand</v>
       </c>
       <c r="M81" t="str">
-        <v>Godown Anand</v>
+        <v>No</v>
       </c>
       <c r="N81" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O81" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P81" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q81" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56144,22 +55601,19 @@
       <c r="I82">
         <v>30000</v>
       </c>
-      <c r="K82" t="str">
-        <v/>
+      <c r="L82" t="str">
+        <v>Godown Anand</v>
       </c>
       <c r="M82" t="str">
-        <v>Godown Anand</v>
+        <v>No</v>
       </c>
       <c r="N82" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O82" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P82" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q82" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56191,22 +55645,19 @@
       <c r="I83">
         <v>10000</v>
       </c>
-      <c r="K83" t="str">
-        <v/>
+      <c r="L83" t="str">
+        <v>Godown Anand</v>
       </c>
       <c r="M83" t="str">
-        <v>Godown Anand</v>
+        <v>No</v>
       </c>
       <c r="N83" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O83" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P83" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q83" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56238,22 +55689,19 @@
       <c r="I84">
         <v>30000</v>
       </c>
-      <c r="K84" t="str">
-        <v/>
+      <c r="L84" t="str">
+        <v>Godown Anand</v>
       </c>
       <c r="M84" t="str">
-        <v>Godown Anand</v>
+        <v>No</v>
       </c>
       <c r="N84" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O84" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P84" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q84" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56285,22 +55733,19 @@
       <c r="I85">
         <v>22000</v>
       </c>
-      <c r="K85" t="str">
-        <v/>
+      <c r="L85" t="str">
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="M85" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>No</v>
       </c>
       <c r="N85" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O85" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P85" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q85" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56332,22 +55777,19 @@
       <c r="I86">
         <v>22000</v>
       </c>
-      <c r="K86" t="str">
-        <v/>
+      <c r="L86" t="str">
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="M86" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>No</v>
       </c>
       <c r="N86" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O86" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P86" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q86" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56379,22 +55821,19 @@
       <c r="I87">
         <v>66000</v>
       </c>
-      <c r="K87" t="str">
-        <v/>
+      <c r="L87" t="str">
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="M87" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>No</v>
       </c>
       <c r="N87" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O87" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P87" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q87" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56426,22 +55865,19 @@
       <c r="I88">
         <v>22000</v>
       </c>
-      <c r="K88" t="str">
-        <v/>
+      <c r="L88" t="str">
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="M88" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>No</v>
       </c>
       <c r="N88" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O88" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P88" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q88" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56473,22 +55909,19 @@
       <c r="I89">
         <v>66000</v>
       </c>
-      <c r="K89" t="str">
-        <v/>
+      <c r="L89" t="str">
+        <v>Chira Bazar House Altaf</v>
       </c>
       <c r="M89" t="str">
-        <v>Chira Bazar House Altaf</v>
+        <v>No</v>
       </c>
       <c r="N89" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O89" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P89" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q89" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56520,22 +55953,19 @@
       <c r="I90">
         <v>20000</v>
       </c>
-      <c r="K90" t="str">
-        <v/>
+      <c r="L90" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M90" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N90" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O90" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P90" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q90" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56567,22 +55997,19 @@
       <c r="I91">
         <v>20000</v>
       </c>
-      <c r="K91" t="str">
-        <v/>
+      <c r="L91" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M91" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N91" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O91" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P91" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q91" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56614,22 +56041,19 @@
       <c r="I92">
         <v>20000</v>
       </c>
-      <c r="K92" t="str">
-        <v/>
+      <c r="L92" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M92" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N92" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O92" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P92" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q92" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56661,22 +56085,19 @@
       <c r="I93">
         <v>20000</v>
       </c>
-      <c r="K93" t="str">
-        <v/>
+      <c r="L93" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M93" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N93" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O93" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P93" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q93" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56708,22 +56129,19 @@
       <c r="I94">
         <v>40000</v>
       </c>
-      <c r="K94" t="str">
-        <v/>
+      <c r="L94" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M94" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N94" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O94" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P94" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q94" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56755,22 +56173,19 @@
       <c r="I95">
         <v>20000</v>
       </c>
-      <c r="K95" t="str">
-        <v/>
+      <c r="L95" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M95" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N95" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O95" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P95" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q95" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56802,22 +56217,19 @@
       <c r="I96">
         <v>30000</v>
       </c>
-      <c r="K96" t="str">
-        <v/>
+      <c r="L96" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M96" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N96" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O96" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P96" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q96" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56849,22 +56261,19 @@
       <c r="I97">
         <v>20000</v>
       </c>
-      <c r="K97" t="str">
-        <v/>
+      <c r="L97" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M97" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N97" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O97" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P97" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q97" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56896,22 +56305,19 @@
       <c r="I98">
         <v>20000</v>
       </c>
-      <c r="K98" t="str">
-        <v/>
+      <c r="L98" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M98" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N98" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O98" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P98" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q98" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56943,22 +56349,19 @@
       <c r="I99">
         <v>20000</v>
       </c>
-      <c r="K99" t="str">
-        <v/>
+      <c r="L99" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M99" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N99" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O99" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P99" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q99" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -56990,22 +56393,19 @@
       <c r="I100">
         <v>20000</v>
       </c>
-      <c r="K100" t="str">
-        <v/>
+      <c r="L100" t="str">
+        <v>Ennas Room Bengali</v>
       </c>
       <c r="M100" t="str">
-        <v>Ennas Room Bengali</v>
+        <v>No</v>
       </c>
       <c r="N100" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O100" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P100" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q100" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -57037,22 +56437,19 @@
       <c r="I101">
         <v>15000</v>
       </c>
-      <c r="K101" t="str">
-        <v/>
+      <c r="L101" t="str">
+        <v>Mani Mansion Room 1 Aswini</v>
       </c>
       <c r="M101" t="str">
-        <v>Mani Mansion Room 1 Aswini</v>
+        <v>No</v>
       </c>
       <c r="N101" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O101" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P101" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q101" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
@@ -57084,28 +56481,25 @@
       <c r="I102">
         <v>15000</v>
       </c>
-      <c r="K102" t="str">
-        <v/>
+      <c r="L102" t="str">
+        <v>Mani Mansion Room 1 Aswini</v>
       </c>
       <c r="M102" t="str">
-        <v>Mani Mansion Room 1 Aswini</v>
+        <v>No</v>
       </c>
       <c r="N102" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="O102" t="str">
-        <v/>
+        <v>23/10/2026</v>
       </c>
       <c r="P102" t="str">
-        <v>23/10/2026</v>
-      </c>
-      <c r="Q102" t="str">
         <v>27/10/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P102"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -57172,7 +56566,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 702 total records]</v>
+        <v>[Showing 100 of 703 total records]</v>
       </c>
     </row>
     <row r="3">

--- a/Property_Rent_Data_Model.xlsx
+++ b/Property_Rent_Data_Model.xlsx
@@ -8717,16 +8717,16 @@
         <v>3399918.74</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G86">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="H86" t="str">
         <v>Yes</v>
@@ -8749,7 +8749,7 @@
         <v>2026-06</v>
       </c>
       <c r="C87">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="H87" t="str">
         <v>Yes</v>
@@ -8784,7 +8784,7 @@
         <v>2026-07</v>
       </c>
       <c r="C88">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="H88" t="str">
         <v>Yes</v>
@@ -8819,7 +8819,7 @@
         <v>2026-08</v>
       </c>
       <c r="C89">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="H89" t="str">
         <v>Yes</v>
@@ -8854,7 +8854,7 @@
         <v>2026-09</v>
       </c>
       <c r="C90">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="H90" t="str">
         <v>Yes</v>
@@ -8889,7 +8889,7 @@
         <v>2026-10</v>
       </c>
       <c r="C91">
-        <v>3399918.74</v>
+        <v>3419918.74</v>
       </c>
       <c r="D91">
         <v>3262426</v>
@@ -8901,7 +8901,7 @@
         <v>3262426</v>
       </c>
       <c r="G91">
-        <v>6662344.74</v>
+        <v>6682344.74</v>
       </c>
       <c r="H91" t="str">
         <v>Yes</v>

--- a/Property_Rent_Data_Model.xlsx
+++ b/Property_Rent_Data_Model.xlsx
@@ -837,7 +837,7 @@
         <v>PaymentReceipts</v>
       </c>
       <c r="B39">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="40">
@@ -845,7 +845,7 @@
         <v>PaymentAllocations</v>
       </c>
       <c r="B40">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>TOTAL</v>
       </c>
       <c r="B46">
-        <v>2908</v>
+        <v>2915</v>
       </c>
     </row>
   </sheetData>
@@ -8472,16 +8472,16 @@
         <v>2545021.74</v>
       </c>
       <c r="D79">
-        <v>348016</v>
+        <v>316016</v>
       </c>
       <c r="E79">
         <v>71548</v>
       </c>
       <c r="F79">
-        <v>276468</v>
+        <v>244468</v>
       </c>
       <c r="G79">
-        <v>2821489.74</v>
+        <v>2789489.74</v>
       </c>
       <c r="H79" t="str">
         <v>Yes</v>
@@ -8504,7 +8504,7 @@
         <v>2025-11</v>
       </c>
       <c r="C80">
-        <v>2821489.74</v>
+        <v>2789489.74</v>
       </c>
       <c r="D80">
         <v>185000</v>
@@ -8516,7 +8516,7 @@
         <v>118500</v>
       </c>
       <c r="G80">
-        <v>2939989.74</v>
+        <v>2907989.74</v>
       </c>
       <c r="H80" t="str">
         <v>Yes</v>
@@ -8539,7 +8539,7 @@
         <v>2025-12</v>
       </c>
       <c r="C81">
-        <v>2939989.74</v>
+        <v>2907989.74</v>
       </c>
       <c r="D81">
         <v>715000</v>
@@ -8551,7 +8551,7 @@
         <v>670199</v>
       </c>
       <c r="G81">
-        <v>3610188.74</v>
+        <v>3578188.74</v>
       </c>
       <c r="H81" t="str">
         <v>Yes</v>
@@ -8577,16 +8577,16 @@
         <v>5643188.74</v>
       </c>
       <c r="D82">
-        <v>581050</v>
+        <v>549050</v>
       </c>
       <c r="E82">
         <v>13670</v>
       </c>
       <c r="F82">
-        <v>567380</v>
+        <v>535380</v>
       </c>
       <c r="G82">
-        <v>6210568.74</v>
+        <v>6178568.74</v>
       </c>
       <c r="H82" t="str">
         <v>Yes</v>
@@ -8609,7 +8609,7 @@
         <v>2026-02</v>
       </c>
       <c r="C83">
-        <v>6210568.74</v>
+        <v>6178568.74</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -8621,7 +8621,7 @@
         <v>-4800</v>
       </c>
       <c r="G83">
-        <v>6205768.74</v>
+        <v>6173768.74</v>
       </c>
       <c r="H83" t="str">
         <v>Yes</v>
@@ -8644,19 +8644,19 @@
         <v>2026-03</v>
       </c>
       <c r="C84">
-        <v>6205768.74</v>
+        <v>6173768.74</v>
       </c>
       <c r="D84">
-        <v>240000</v>
+        <v>258000</v>
       </c>
       <c r="E84">
         <v>2874350</v>
       </c>
       <c r="F84">
-        <v>-2634350</v>
+        <v>-2616350</v>
       </c>
       <c r="G84">
-        <v>3571418.74</v>
+        <v>3557418.74</v>
       </c>
       <c r="H84" t="str">
         <v>Yes</v>
@@ -8679,7 +8679,7 @@
         <v>2026-04</v>
       </c>
       <c r="C85">
-        <v>3571418.74</v>
+        <v>3557418.74</v>
       </c>
       <c r="D85">
         <v>28500</v>
@@ -8691,7 +8691,7 @@
         <v>-171500</v>
       </c>
       <c r="G85">
-        <v>3399918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="H85" t="str">
         <v>Yes</v>
@@ -8714,19 +8714,19 @@
         <v>2026-05</v>
       </c>
       <c r="C86">
-        <v>3399918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="D86">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="H86" t="str">
         <v>Yes</v>
@@ -8749,7 +8749,7 @@
         <v>2026-06</v>
       </c>
       <c r="C87">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="H87" t="str">
         <v>Yes</v>
@@ -8784,7 +8784,7 @@
         <v>2026-07</v>
       </c>
       <c r="C88">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="H88" t="str">
         <v>Yes</v>
@@ -8819,7 +8819,7 @@
         <v>2026-08</v>
       </c>
       <c r="C89">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="H89" t="str">
         <v>Yes</v>
@@ -8854,7 +8854,7 @@
         <v>2026-09</v>
       </c>
       <c r="C90">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="H90" t="str">
         <v>Yes</v>
@@ -8889,19 +8889,19 @@
         <v>2026-10</v>
       </c>
       <c r="C91">
-        <v>3419918.74</v>
+        <v>3385918.74</v>
       </c>
       <c r="D91">
-        <v>3262426</v>
+        <v>3412426</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>3262426</v>
+        <v>3412426</v>
       </c>
       <c r="G91">
-        <v>6682344.74</v>
+        <v>6798344.74</v>
       </c>
       <c r="H91" t="str">
         <v>Yes</v>
@@ -52094,7 +52094,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 701 total records]</v>
+        <v>[Showing 100 of 703 total records]</v>
       </c>
     </row>
     <row r="3">
@@ -56566,7 +56566,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 703 total records]</v>
+        <v>[Showing 100 of 708 total records]</v>
       </c>
     </row>
     <row r="3">

--- a/Property_Rent_Data_Model.xlsx
+++ b/Property_Rent_Data_Model.xlsx
@@ -845,7 +845,7 @@
         <v>PaymentAllocations</v>
       </c>
       <c r="B40">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>TOTAL</v>
       </c>
       <c r="B46">
-        <v>2915</v>
+        <v>2918</v>
       </c>
     </row>
   </sheetData>
@@ -8892,16 +8892,16 @@
         <v>3385918.74</v>
       </c>
       <c r="D91">
-        <v>3412426</v>
+        <v>3487426</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>3412426</v>
+        <v>3487426</v>
       </c>
       <c r="G91">
-        <v>6798344.74</v>
+        <v>6873344.74</v>
       </c>
       <c r="H91" t="str">
         <v>Yes</v>
@@ -56566,7 +56566,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[Showing 100 of 708 total records]</v>
+        <v>[Showing 100 of 711 total records]</v>
       </c>
     </row>
     <row r="3">
